--- a/complete_with_offsets_and_PA.xlsx
+++ b/complete_with_offsets_and_PA.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>1.285714285714286</v>
+        <v>1.174603174603175</v>
       </c>
     </row>
     <row r="3">
@@ -610,7 +610,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>0.8</v>
+        <v>0.8133333333333332</v>
       </c>
     </row>
     <row r="4">
@@ -657,7 +657,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.9275362318840579</v>
       </c>
     </row>
     <row r="5">
@@ -704,7 +704,7 @@
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>1.130434782608696</v>
+        <v>1.057971014492754</v>
       </c>
     </row>
     <row r="6">
@@ -753,7 +753,7 @@
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="n">
-        <v>0.8076923076923077</v>
+        <v>0.8717948717948718</v>
       </c>
     </row>
     <row r="7">
@@ -806,7 +806,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.178571428571429</v>
+        <v>1.142857142857143</v>
       </c>
     </row>
     <row r="8">
@@ -859,7 +859,7 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9047619047619048</v>
       </c>
     </row>
     <row r="9">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8518518518518517</v>
       </c>
     </row>
     <row r="13">
@@ -1074,7 +1074,7 @@
         <v>0.6470588235294118</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0.9819819819819821</v>
       </c>
     </row>
     <row r="14">
@@ -1127,7 +1127,7 @@
         <v>0.5333333333333333</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8857142857142857</v>
       </c>
     </row>
     <row r="15">
@@ -1180,7 +1180,7 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.90625</v>
+        <v>0.9270833333333333</v>
       </c>
     </row>
     <row r="16">
@@ -1233,7 +1233,7 @@
         <v>0.6875</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.066666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1286,7 +1286,7 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.924731182795699</v>
       </c>
     </row>
     <row r="18">
@@ -1339,7 +1339,7 @@
         <v>0.8823529411764706</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0.9655172413793104</v>
       </c>
     </row>
     <row r="19">
@@ -1388,7 +1388,7 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.9247311827956989</v>
       </c>
     </row>
     <row r="20">
@@ -1435,7 +1435,7 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="n">
-        <v>0.9</v>
+        <v>0.9111111111111112</v>
       </c>
     </row>
     <row r="21">
@@ -1480,7 +1480,7 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="n">
-        <v>1.058823529411765</v>
+        <v>1.088235294117647</v>
       </c>
     </row>
     <row r="22">
@@ -1525,7 +1525,7 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9074074074074073</v>
       </c>
     </row>
     <row r="23">
@@ -1570,7 +1570,7 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="n">
-        <v>0.8125</v>
+        <v>0.8645833333333333</v>
       </c>
     </row>
     <row r="24">
@@ -1615,7 +1615,7 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="n">
-        <v>1.096774193548387</v>
+        <v>1.086021505376344</v>
       </c>
     </row>
     <row r="25">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="n">
-        <v>1.088235294117647</v>
+        <v>1.107843137254902</v>
       </c>
     </row>
     <row r="27">
@@ -1752,7 +1752,7 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="n">
-        <v>1.025</v>
+        <v>0.9916666666666666</v>
       </c>
     </row>
     <row r="28">
@@ -1799,7 +1799,7 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="n">
-        <v>0.9534883720930233</v>
+        <v>0.9612403100775194</v>
       </c>
     </row>
     <row r="29">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="n">
-        <v>0.8297872340425532</v>
+        <v>0.8652482269503545</v>
       </c>
     </row>
     <row r="30">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="n">
-        <v>0.8913043478260869</v>
+        <v>0.8768115942028986</v>
       </c>
     </row>
     <row r="31">
@@ -2001,7 +2001,7 @@
         <v>0.55</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.975609756097561</v>
+        <v>0.9593495934959351</v>
       </c>
     </row>
     <row r="33">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="n">
-        <v>0.9318181818181818</v>
+        <v>0.9242424242424242</v>
       </c>
     </row>
     <row r="37">
@@ -2216,7 +2216,7 @@
         <v>0.7083333333333334</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.9621212121212122</v>
       </c>
     </row>
     <row r="38">
@@ -2269,7 +2269,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.9767441860465116</v>
+        <v>0.9534883720930233</v>
       </c>
     </row>
     <row r="39">
@@ -2322,7 +2322,7 @@
         <v>0.4482758620689655</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.6938775510204082</v>
+        <v>0.7074829931972788</v>
       </c>
     </row>
     <row r="40">
@@ -2428,7 +2428,7 @@
         <v>0.5483870967741935</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.9710144927536232</v>
       </c>
     </row>
     <row r="42">
@@ -2530,7 +2530,7 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="44">
@@ -2577,7 +2577,7 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="n">
-        <v>0.9615384615384616</v>
+        <v>0.9487179487179488</v>
       </c>
     </row>
     <row r="45">
@@ -2622,7 +2622,7 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="n">
-        <v>0.9803921568627451</v>
+        <v>0.9934640522875816</v>
       </c>
     </row>
     <row r="46">
@@ -2667,7 +2667,7 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="n">
-        <v>1.072727272727273</v>
+        <v>1.054545454545454</v>
       </c>
     </row>
     <row r="47">
@@ -2712,7 +2712,7 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="n">
-        <v>0.9298245614035088</v>
+        <v>0.976608187134503</v>
       </c>
     </row>
     <row r="48">
@@ -2757,7 +2757,7 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="n">
-        <v>0.9682539682539683</v>
+        <v>0.9576719576719576</v>
       </c>
     </row>
     <row r="49">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="n">
-        <v>0.8727272727272727</v>
+        <v>0.8424242424242425</v>
       </c>
     </row>
     <row r="51">
@@ -2898,7 +2898,7 @@
         <v>0.5</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.9387755102040817</v>
+        <v>0.9523809523809524</v>
       </c>
     </row>
     <row r="52">
@@ -2951,7 +2951,7 @@
         <v>0.7837837837837838</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.101694915254237</v>
+        <v>1.084745762711864</v>
       </c>
     </row>
     <row r="53">
@@ -3004,7 +3004,7 @@
         <v>0.7804878048780488</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.015151515151515</v>
+        <v>1.005050505050505</v>
       </c>
     </row>
     <row r="54">
@@ -3057,7 +3057,7 @@
         <v>1.060606060606061</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.8376068376068375</v>
       </c>
     </row>
     <row r="55">
@@ -3110,7 +3110,7 @@
         <v>0.8627450980392157</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.875</v>
+        <v>0.8842592592592593</v>
       </c>
     </row>
     <row r="56">
@@ -3163,7 +3163,7 @@
         <v>0.9137931034482759</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.9036144578313253</v>
+        <v>0.8915662650602409</v>
       </c>
     </row>
     <row r="57">
@@ -3216,7 +3216,7 @@
         <v>0.84375</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.9325842696629213</v>
+        <v>0.9438202247191011</v>
       </c>
     </row>
     <row r="58">
@@ -3269,7 +3269,7 @@
         <v>0.7540983606557377</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.9574468085106383</v>
+        <v>0.9858156028368795</v>
       </c>
     </row>
     <row r="59">
@@ -3322,7 +3322,7 @@
         <v>0.7213114754098361</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9079365079365079</v>
       </c>
     </row>
     <row r="60">
@@ -3375,7 +3375,7 @@
         <v>0.6515151515151515</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.875</v>
+        <v>0.8846153846153846</v>
       </c>
     </row>
     <row r="61">
@@ -3428,7 +3428,7 @@
         <v>0.55</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.875</v>
+        <v>0.9198717948717949</v>
       </c>
     </row>
     <row r="62">
@@ -3481,7 +3481,7 @@
         <v>0.5409836065573771</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.9896907216494846</v>
+        <v>0.9621993127147768</v>
       </c>
     </row>
     <row r="63">
@@ -3534,7 +3534,7 @@
         <v>0.5084745762711864</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.031914893617021</v>
+        <v>1.014184397163121</v>
       </c>
     </row>
     <row r="64">
@@ -3587,7 +3587,7 @@
         <v>0.6923076923076923</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.8585858585858586</v>
+        <v>0.8754208754208754</v>
       </c>
     </row>
     <row r="65">
@@ -3640,7 +3640,7 @@
         <v>0.8205128205128205</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.9879518072289156</v>
+        <v>0.9799196787148595</v>
       </c>
     </row>
     <row r="66">
@@ -3693,7 +3693,7 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.9866666666666667</v>
+        <v>0.9688888888888889</v>
       </c>
     </row>
     <row r="67">
@@ -3742,7 +3742,7 @@
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9007936507936508</v>
       </c>
     </row>
     <row r="68">
@@ -3789,7 +3789,7 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="n">
-        <v>0.898876404494382</v>
+        <v>0.9288389513108615</v>
       </c>
     </row>
     <row r="69">
@@ -3834,7 +3834,7 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="n">
-        <v>1.056179775280899</v>
+        <v>1.029962546816479</v>
       </c>
     </row>
     <row r="70">
@@ -3879,7 +3879,7 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="n">
-        <v>0.8681318681318682</v>
+        <v>0.8864468864468865</v>
       </c>
     </row>
     <row r="71">
@@ -3924,7 +3924,7 @@
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="n">
-        <v>0.9761904761904762</v>
+        <v>0.9682539682539681</v>
       </c>
     </row>
     <row r="72">
@@ -3969,7 +3969,7 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="n">
-        <v>0.9213483146067416</v>
+        <v>0.9400749063670413</v>
       </c>
     </row>
     <row r="73">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="n">
-        <v>0.9642857142857143</v>
+        <v>0.9714285714285714</v>
       </c>
     </row>
     <row r="75">
@@ -4106,7 +4106,7 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="n">
-        <v>0.9586206896551724</v>
+        <v>0.9678160919540231</v>
       </c>
     </row>
     <row r="76">
@@ -4153,7 +4153,7 @@
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="n">
-        <v>0.9281045751633987</v>
+        <v>0.9302832244008715</v>
       </c>
     </row>
     <row r="77">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="n">
-        <v>0.9931972789115646</v>
+        <v>1.009070294784581</v>
       </c>
     </row>
     <row r="78">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="n">
-        <v>0.9503546099290781</v>
+        <v>0.9432624113475178</v>
       </c>
     </row>
     <row r="79">
@@ -4302,7 +4302,7 @@
         <v>0.6853932584269663</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.8918918918918919</v>
+        <v>0.8896396396396395</v>
       </c>
     </row>
     <row r="80">
@@ -4355,7 +4355,7 @@
         <v>0.7333333333333333</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.9115646258503401</v>
+        <v>0.9183673469387755</v>
       </c>
     </row>
     <row r="81">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="n">
-        <v>0.8671875</v>
+        <v>0.9088541666666667</v>
       </c>
     </row>
     <row r="85">
@@ -4570,7 +4570,7 @@
         <v>1.035087719298246</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.9921259842519685</v>
+        <v>0.9816272965879265</v>
       </c>
     </row>
     <row r="86">
@@ -4623,7 +4623,7 @@
         <v>0.9024390243902439</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.9495798319327731</v>
+        <v>0.9607843137254902</v>
       </c>
     </row>
     <row r="87">
@@ -4676,7 +4676,7 @@
         <v>0.8589743589743589</v>
       </c>
       <c r="Q87" t="n">
-        <v>1.088</v>
+        <v>1.061333333333333</v>
       </c>
     </row>
     <row r="88">
@@ -4782,7 +4782,7 @@
         <v>0.6842105263157895</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.021276595744681</v>
+        <v>1.009456264775414</v>
       </c>
     </row>
     <row r="90">
@@ -4835,7 +4835,7 @@
         <v>1.048387096774194</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.9337748344370861</v>
+        <v>0.9470198675496688</v>
       </c>
     </row>
     <row r="91">
@@ -4884,7 +4884,7 @@
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="n">
-        <v>0.927536231884058</v>
+        <v>0.9541062801932366</v>
       </c>
     </row>
     <row r="92">
@@ -4931,7 +4931,7 @@
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="n">
-        <v>1.014925373134328</v>
+        <v>1.009950248756219</v>
       </c>
     </row>
     <row r="93">
@@ -4976,7 +4976,7 @@
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="n">
-        <v>1.085106382978723</v>
+        <v>1.047281323877068</v>
       </c>
     </row>
     <row r="94">
@@ -5021,7 +5021,7 @@
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.9041394335511983</v>
       </c>
     </row>
     <row r="95">
@@ -5066,7 +5066,7 @@
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="n">
-        <v>1.02158273381295</v>
+        <v>1.019184652278177</v>
       </c>
     </row>
     <row r="96">
@@ -5111,7 +5111,7 @@
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="n">
-        <v>0.9934640522875817</v>
+        <v>1.002178649237473</v>
       </c>
     </row>
     <row r="97">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="n">
-        <v>0.8817204301075269</v>
+        <v>0.8960573476702508</v>
       </c>
     </row>
     <row r="99">
@@ -5248,7 +5248,7 @@
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="n">
-        <v>1.020833333333333</v>
+        <v>1.010416666666667</v>
       </c>
     </row>
     <row r="100">
@@ -5295,7 +5295,7 @@
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="n">
-        <v>1.017699115044248</v>
+        <v>0.9970501474926253</v>
       </c>
     </row>
     <row r="101">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="n">
-        <v>0.8267716535433071</v>
+        <v>0.8530183727034122</v>
       </c>
     </row>
     <row r="102">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="n">
-        <v>0.8934426229508197</v>
+        <v>0.9016393442622951</v>
       </c>
     </row>
     <row r="103">
@@ -5444,7 +5444,7 @@
         <v>0.7125</v>
       </c>
       <c r="Q103" t="n">
-        <v>0.9140625</v>
+        <v>0.921875</v>
       </c>
     </row>
     <row r="104">
@@ -5497,7 +5497,7 @@
         <v>0.7303370786516854</v>
       </c>
       <c r="Q104" t="n">
-        <v>0.9069767441860465</v>
+        <v>0.9018087855297159</v>
       </c>
     </row>
     <row r="105">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="n">
-        <v>0.88</v>
+        <v>0.9066666666666666</v>
       </c>
     </row>
     <row r="109">
@@ -5712,7 +5712,7 @@
         <v>0.8225806451612904</v>
       </c>
       <c r="Q109" t="n">
-        <v>0.927536231884058</v>
+        <v>0.9347826086956522</v>
       </c>
     </row>
     <row r="110">
@@ -5765,7 +5765,7 @@
         <v>0.7758620689655172</v>
       </c>
       <c r="Q110" t="n">
-        <v>1.062992125984252</v>
+        <v>1.044619422572178</v>
       </c>
     </row>
     <row r="111">
@@ -5818,7 +5818,7 @@
         <v>0.7166666666666667</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.9389312977099237</v>
+        <v>0.9541984732824428</v>
       </c>
     </row>
     <row r="112">
@@ -5871,7 +5871,7 @@
         <v>0.6</v>
       </c>
       <c r="Q112" t="n">
-        <v>0.983739837398374</v>
+        <v>0.970189701897019</v>
       </c>
     </row>
     <row r="113">
@@ -5924,7 +5924,7 @@
         <v>0.9491525423728814</v>
       </c>
       <c r="Q113" t="n">
-        <v>1.0078125</v>
+        <v>1.010416666666667</v>
       </c>
     </row>
     <row r="114">
@@ -5977,7 +5977,7 @@
         <v>1.176470588235294</v>
       </c>
       <c r="Q114" t="n">
-        <v>1.083333333333333</v>
+        <v>1.077777777777778</v>
       </c>
     </row>
     <row r="115">
@@ -6026,7 +6026,7 @@
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="n">
-        <v>1.016666666666667</v>
+        <v>1.002777777777778</v>
       </c>
     </row>
     <row r="116">
@@ -6073,7 +6073,7 @@
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="n">
-        <v>0.96875</v>
+        <v>0.9713541666666667</v>
       </c>
     </row>
     <row r="117">
@@ -6118,7 +6118,7 @@
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="n">
-        <v>0.9777777777777777</v>
+        <v>0.982716049382716</v>
       </c>
     </row>
     <row r="118">
@@ -6163,7 +6163,7 @@
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="n">
-        <v>0.9770992366412213</v>
+        <v>0.9669211195928753</v>
       </c>
     </row>
     <row r="119">
@@ -6208,7 +6208,7 @@
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="n">
-        <v>0.8613138686131386</v>
+        <v>0.9002433090024332</v>
       </c>
     </row>
     <row r="120">
@@ -6253,7 +6253,7 @@
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="n">
-        <v>1.061538461538462</v>
+        <v>1.041025641025641</v>
       </c>
     </row>
     <row r="121">
@@ -6716,7 +6716,7 @@
         <v>0.875</v>
       </c>
       <c r="Q133" t="n">
-        <v>0.90625</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="134">
@@ -6769,7 +6769,7 @@
         <v>0.9473684210526315</v>
       </c>
       <c r="Q134" t="n">
-        <v>1.033333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -6822,7 +6822,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="Q135" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8666666666666667</v>
       </c>
     </row>
     <row r="136">
@@ -6928,7 +6928,7 @@
         <v>0.5</v>
       </c>
       <c r="Q137" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9230769230769231</v>
       </c>
     </row>
     <row r="138">
@@ -6981,7 +6981,7 @@
         <v>0.5135135135135135</v>
       </c>
       <c r="Q138" t="n">
-        <v>0.7021276595744681</v>
+        <v>0.7517730496453902</v>
       </c>
     </row>
     <row r="139">
@@ -7030,7 +7030,7 @@
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="n">
-        <v>0.9318181818181818</v>
+        <v>0.9090909090909091</v>
       </c>
     </row>
     <row r="140">
@@ -7122,7 +7122,7 @@
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="n">
-        <v>1</v>
+        <v>0.9935897435897435</v>
       </c>
     </row>
     <row r="142">
@@ -7212,7 +7212,7 @@
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="n">
-        <v>0.8793103448275862</v>
+        <v>0.9022988505747127</v>
       </c>
     </row>
     <row r="144">
@@ -7257,7 +7257,7 @@
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
       <c r="Q144" t="n">
-        <v>1.017857142857143</v>
+        <v>1.011904761904762</v>
       </c>
     </row>
     <row r="145">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="n">
-        <v>0.8767123287671232</v>
+        <v>0.8995433789954339</v>
       </c>
     </row>
     <row r="147">
@@ -7394,7 +7394,7 @@
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="n">
-        <v>0.9772727272727273</v>
+        <v>0.9886363636363636</v>
       </c>
     </row>
     <row r="148">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="n">
-        <v>1.041237113402062</v>
+        <v>1.010309278350515</v>
       </c>
     </row>
     <row r="149">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="n">
-        <v>0.9133858267716536</v>
+        <v>0.916010498687664</v>
       </c>
     </row>
     <row r="150">
@@ -7545,7 +7545,7 @@
         <v>0.7</v>
       </c>
       <c r="Q150" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.8991596638655462</v>
       </c>
     </row>
     <row r="151">
@@ -7598,7 +7598,7 @@
         <v>0.9148936170212766</v>
       </c>
       <c r="Q151" t="n">
-        <v>0.8870967741935484</v>
+        <v>0.8844086021505376</v>
       </c>
     </row>
     <row r="152">
@@ -7651,7 +7651,7 @@
         <v>0.7321428571428571</v>
       </c>
       <c r="Q152" t="n">
-        <v>0.8260869565217391</v>
+        <v>0.8463768115942029</v>
       </c>
     </row>
     <row r="153">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="P155" t="inlineStr"/>
       <c r="Q155" t="n">
-        <v>0.9615384615384616</v>
+        <v>0.9326923076923077</v>
       </c>
     </row>
     <row r="156">
@@ -7835,7 +7835,7 @@
         <v>0.6219512195121951</v>
       </c>
       <c r="Q156" t="n">
-        <v>0.8440366972477065</v>
+        <v>0.8746177370030581</v>
       </c>
     </row>
     <row r="157">
@@ -7888,7 +7888,7 @@
         <v>0.6111111111111112</v>
       </c>
       <c r="Q157" t="n">
-        <v>1.019047619047619</v>
+        <v>0.9968253968253967</v>
       </c>
     </row>
     <row r="158">
@@ -7941,7 +7941,7 @@
         <v>0.6506024096385542</v>
       </c>
       <c r="Q158" t="n">
-        <v>1</v>
+        <v>0.9867724867724869</v>
       </c>
     </row>
     <row r="159">
@@ -7994,7 +7994,7 @@
         <v>0.7837837837837838</v>
       </c>
       <c r="Q159" t="n">
-        <v>0.8656716417910447</v>
+        <v>0.8781094527363184</v>
       </c>
     </row>
     <row r="160">
@@ -8100,7 +8100,7 @@
         <v>0.8428571428571429</v>
       </c>
       <c r="Q161" t="n">
-        <v>0.9236641221374046</v>
+        <v>0.9414758269720103</v>
       </c>
     </row>
     <row r="162">
@@ -8153,7 +8153,7 @@
         <v>0.6790123456790124</v>
       </c>
       <c r="Q162" t="n">
-        <v>1.030769230769231</v>
+        <v>1.025641025641026</v>
       </c>
     </row>
     <row r="163">
@@ -8202,7 +8202,7 @@
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
       <c r="Q163" t="n">
-        <v>0.8776978417266187</v>
+        <v>0.8752997601918464</v>
       </c>
     </row>
     <row r="164">
@@ -8249,7 +8249,7 @@
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="n">
-        <v>0.8780487804878049</v>
+        <v>0.8834688346883469</v>
       </c>
     </row>
     <row r="165">
@@ -8294,7 +8294,7 @@
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="n">
-        <v>1.064220183486239</v>
+        <v>1.073394495412844</v>
       </c>
     </row>
     <row r="166">
@@ -8339,7 +8339,7 @@
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="n">
-        <v>1.025423728813559</v>
+        <v>1.011299435028249</v>
       </c>
     </row>
     <row r="167">
@@ -8384,7 +8384,7 @@
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="n">
-        <v>0.8760330578512396</v>
+        <v>0.8842975206611571</v>
       </c>
     </row>
     <row r="168">
@@ -8429,7 +8429,7 @@
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="n">
-        <v>1</v>
+        <v>0.9941520467836258</v>
       </c>
     </row>
     <row r="169">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="P194" t="inlineStr"/>
       <c r="Q194" t="n">
-        <v>0.8</v>
+        <v>0.7833333333333334</v>
       </c>
     </row>
     <row r="195">
@@ -9166,7 +9166,7 @@
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
       <c r="Q195" t="n">
-        <v>1.03030303030303</v>
+        <v>1.070707070707071</v>
       </c>
     </row>
     <row r="196">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="P196" t="inlineStr"/>
       <c r="Q196" t="n">
-        <v>0.75</v>
+        <v>0.7727272727272727</v>
       </c>
     </row>
     <row r="197">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="P197" t="inlineStr"/>
       <c r="Q197" t="n">
-        <v>1.84375</v>
+        <v>1.739583333333333</v>
       </c>
     </row>
     <row r="198">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="P198" t="inlineStr"/>
       <c r="Q198" t="n">
-        <v>1.84375</v>
+        <v>1.739583333333333</v>
       </c>
     </row>
     <row r="199">
@@ -9366,7 +9366,7 @@
         <v>0.3611111111111111</v>
       </c>
       <c r="Q199" t="n">
-        <v>0.8032786885245902</v>
+        <v>0.8251366120218578</v>
       </c>
     </row>
     <row r="200">
@@ -9419,7 +9419,7 @@
         <v>0.3611111111111111</v>
       </c>
       <c r="Q200" t="n">
-        <v>0.8032786885245902</v>
+        <v>0.8251366120218578</v>
       </c>
     </row>
     <row r="201">
@@ -9472,7 +9472,7 @@
         <v>0.4358974358974359</v>
       </c>
       <c r="Q201" t="n">
-        <v>0.9552238805970149</v>
+        <v>0.9701492537313433</v>
       </c>
     </row>
     <row r="202">
@@ -9525,7 +9525,7 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="Q202" t="n">
-        <v>0.8985507246376812</v>
+        <v>0.8792270531400966</v>
       </c>
     </row>
     <row r="203">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="P205" t="inlineStr"/>
       <c r="Q205" t="n">
-        <v>0.9655172413793104</v>
+        <v>0.9540229885057471</v>
       </c>
     </row>
     <row r="206">
@@ -9709,7 +9709,7 @@
         <v>0.5238095238095238</v>
       </c>
       <c r="Q206" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.851851851851852</v>
       </c>
     </row>
     <row r="207">
@@ -9762,7 +9762,7 @@
         <v>0.4897959183673469</v>
       </c>
       <c r="Q207" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8686868686868686</v>
       </c>
     </row>
     <row r="208">
@@ -9815,7 +9815,7 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="Q208" t="n">
-        <v>0.9027777777777778</v>
+        <v>0.8935185185185185</v>
       </c>
     </row>
     <row r="209">
@@ -9868,7 +9868,7 @@
         <v>0.4042553191489361</v>
       </c>
       <c r="Q209" t="n">
-        <v>1</v>
+        <v>1.014925373134328</v>
       </c>
     </row>
     <row r="210">
@@ -9921,7 +9921,7 @@
         <v>0.5897435897435898</v>
       </c>
       <c r="Q210" t="n">
-        <v>0.9324324324324325</v>
+        <v>0.9144144144144145</v>
       </c>
     </row>
     <row r="211">
@@ -9974,7 +9974,7 @@
         <v>0.75</v>
       </c>
       <c r="Q211" t="n">
-        <v>1.014285714285714</v>
+        <v>1.033333333333333</v>
       </c>
     </row>
     <row r="212">
@@ -10027,7 +10027,7 @@
         <v>1</v>
       </c>
       <c r="Q212" t="n">
-        <v>1.027397260273973</v>
+        <v>0.995433789954338</v>
       </c>
     </row>
     <row r="213">
@@ -10076,7 +10076,7 @@
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr"/>
       <c r="Q213" t="n">
-        <v>0.9726027397260274</v>
+        <v>0.995433789954338</v>
       </c>
     </row>
     <row r="214">
@@ -10123,7 +10123,7 @@
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="inlineStr"/>
       <c r="Q214" t="n">
-        <v>1.012820512820513</v>
+        <v>1.004273504273504</v>
       </c>
     </row>
     <row r="215">
@@ -10168,7 +10168,7 @@
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr"/>
       <c r="Q215" t="n">
-        <v>0.7951807228915663</v>
+        <v>0.7791164658634538</v>
       </c>
     </row>
     <row r="216">
@@ -10213,7 +10213,7 @@
       <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr"/>
       <c r="Q216" t="n">
-        <v>0.8846153846153846</v>
+        <v>0.9273504273504273</v>
       </c>
     </row>
     <row r="217">
@@ -10258,7 +10258,7 @@
       <c r="O217" t="inlineStr"/>
       <c r="P217" t="inlineStr"/>
       <c r="Q217" t="n">
-        <v>0.925</v>
+        <v>0.9166666666666666</v>
       </c>
     </row>
     <row r="218">
@@ -10303,7 +10303,7 @@
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr"/>
       <c r="Q218" t="n">
-        <v>1.011764705882353</v>
+        <v>0.992156862745098</v>
       </c>
     </row>
     <row r="219">
@@ -10575,7 +10575,7 @@
         <v>0.1714285714285714</v>
       </c>
       <c r="Q224" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.7222222222222223</v>
       </c>
     </row>
     <row r="225">
@@ -10628,7 +10628,7 @@
         <v>0.2307692307692308</v>
       </c>
       <c r="Q225" t="n">
-        <v>0.7073170731707317</v>
+        <v>0.7317073170731707</v>
       </c>
     </row>
     <row r="226">
@@ -10681,7 +10681,7 @@
         <v>0.225</v>
       </c>
       <c r="Q226" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.7629629629629631</v>
       </c>
     </row>
     <row r="227">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="P229" t="inlineStr"/>
       <c r="Q229" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="230">
@@ -10865,7 +10865,7 @@
         <v>0.4444444444444444</v>
       </c>
       <c r="Q230" t="n">
-        <v>1.03030303030303</v>
+        <v>1.01010101010101</v>
       </c>
     </row>
     <row r="231">
@@ -10918,7 +10918,7 @@
         <v>0.3571428571428572</v>
       </c>
       <c r="Q231" t="n">
-        <v>0.4390243902439024</v>
+        <v>0.4715447154471544</v>
       </c>
     </row>
     <row r="232">
@@ -10971,7 +10971,7 @@
         <v>0.4117647058823529</v>
       </c>
       <c r="Q232" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.5632183908045978</v>
       </c>
     </row>
     <row r="233">
@@ -11024,7 +11024,7 @@
         <v>0.4</v>
       </c>
       <c r="Q233" t="n">
-        <v>1.291666666666667</v>
+        <v>1.319444444444444</v>
       </c>
     </row>
     <row r="234">
@@ -11130,7 +11130,7 @@
         <v>0.375</v>
       </c>
       <c r="Q235" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5686274509803922</v>
       </c>
     </row>
     <row r="236">
@@ -11183,7 +11183,7 @@
         <v>0.5666666666666667</v>
       </c>
       <c r="Q236" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.9404761904761906</v>
       </c>
     </row>
     <row r="237">
@@ -11232,7 +11232,7 @@
       <c r="O237" t="inlineStr"/>
       <c r="P237" t="inlineStr"/>
       <c r="Q237" t="n">
-        <v>0.8125</v>
+        <v>0.8020833333333333</v>
       </c>
     </row>
     <row r="238">
@@ -11279,7 +11279,7 @@
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="inlineStr"/>
       <c r="Q238" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8777777777777779</v>
       </c>
     </row>
     <row r="239">
@@ -11324,7 +11324,7 @@
       <c r="O239" t="inlineStr"/>
       <c r="P239" t="inlineStr"/>
       <c r="Q239" t="n">
-        <v>0.9655172413793104</v>
+        <v>0.9310344827586207</v>
       </c>
     </row>
     <row r="240">
@@ -11369,7 +11369,7 @@
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="inlineStr"/>
       <c r="Q240" t="n">
-        <v>0.8</v>
+        <v>0.7777777777777779</v>
       </c>
     </row>
     <row r="241">
@@ -11414,7 +11414,7 @@
       <c r="O241" t="inlineStr"/>
       <c r="P241" t="inlineStr"/>
       <c r="Q241" t="n">
-        <v>1.03448275862069</v>
+        <v>1.080459770114943</v>
       </c>
     </row>
     <row r="242">
@@ -11459,7 +11459,7 @@
       <c r="O242" t="inlineStr"/>
       <c r="P242" t="inlineStr"/>
       <c r="Q242" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9705882352941176</v>
       </c>
     </row>
     <row r="243">
@@ -12095,7 +12095,7 @@
       <c r="O264" t="inlineStr"/>
       <c r="P264" t="inlineStr"/>
       <c r="Q264" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.2619047619047619</v>
       </c>
     </row>
     <row r="265">
@@ -12185,7 +12185,7 @@
       <c r="O266" t="inlineStr"/>
       <c r="P266" t="inlineStr"/>
       <c r="Q266" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.738095238095238</v>
       </c>
     </row>
     <row r="267">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="P268" t="inlineStr"/>
       <c r="Q268" t="n">
-        <v>1.220588235294118</v>
+        <v>1.200980392156863</v>
       </c>
     </row>
     <row r="269">
@@ -12322,7 +12322,7 @@
       <c r="O269" t="inlineStr"/>
       <c r="P269" t="inlineStr"/>
       <c r="Q269" t="n">
-        <v>0.9390243902439024</v>
+        <v>0.9308943089430893</v>
       </c>
     </row>
     <row r="270">
@@ -12369,7 +12369,7 @@
       <c r="O270" t="inlineStr"/>
       <c r="P270" t="inlineStr"/>
       <c r="Q270" t="n">
-        <v>0.9342105263157895</v>
+        <v>0.9385964912280701</v>
       </c>
     </row>
     <row r="271">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="P271" t="inlineStr"/>
       <c r="Q271" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8927203065134101</v>
       </c>
     </row>
     <row r="272">
@@ -12465,7 +12465,7 @@
       </c>
       <c r="P272" t="inlineStr"/>
       <c r="Q272" t="n">
-        <v>0.8555555555555555</v>
+        <v>0.8777777777777778</v>
       </c>
     </row>
     <row r="273">
@@ -12518,7 +12518,7 @@
         <v>0.6</v>
       </c>
       <c r="Q273" t="n">
-        <v>0.9787234042553191</v>
+        <v>0.9503546099290779</v>
       </c>
     </row>
     <row r="274">
@@ -12571,7 +12571,7 @@
         <v>0.7377049180327869</v>
       </c>
       <c r="Q274" t="n">
-        <v>0.7888888888888889</v>
+        <v>0.8259259259259258</v>
       </c>
     </row>
     <row r="275">
@@ -12733,7 +12733,7 @@
       </c>
       <c r="P278" t="inlineStr"/>
       <c r="Q278" t="n">
-        <v>0.967741935483871</v>
+        <v>0.9749103942652331</v>
       </c>
     </row>
     <row r="279">
@@ -12786,7 +12786,7 @@
         <v>0.7818181818181819</v>
       </c>
       <c r="Q279" t="n">
-        <v>0.9326923076923077</v>
+        <v>0.9487179487179488</v>
       </c>
     </row>
     <row r="280">
@@ -12839,7 +12839,7 @@
         <v>0.8627450980392157</v>
       </c>
       <c r="Q280" t="n">
-        <v>0.9339622641509434</v>
+        <v>0.949685534591195</v>
       </c>
     </row>
     <row r="281">
@@ -12892,7 +12892,7 @@
         <v>0.9767441860465116</v>
       </c>
       <c r="Q281" t="n">
-        <v>1.063829787234043</v>
+        <v>1.035460992907802</v>
       </c>
     </row>
     <row r="282">
@@ -12945,7 +12945,7 @@
         <v>1</v>
       </c>
       <c r="Q282" t="n">
-        <v>0.9787234042553191</v>
+        <v>0.975177304964539</v>
       </c>
     </row>
     <row r="283">
@@ -12998,7 +12998,7 @@
         <v>1.085106382978723</v>
       </c>
       <c r="Q283" t="n">
-        <v>0.9901960784313726</v>
+        <v>0.9869281045751634</v>
       </c>
     </row>
     <row r="284">
@@ -13051,7 +13051,7 @@
         <v>0.9056603773584906</v>
       </c>
       <c r="Q284" t="n">
-        <v>0.9207920792079208</v>
+        <v>0.9504950495049505</v>
       </c>
     </row>
     <row r="285">
@@ -13100,7 +13100,7 @@
       <c r="O285" t="inlineStr"/>
       <c r="P285" t="inlineStr"/>
       <c r="Q285" t="n">
-        <v>1.048543689320388</v>
+        <v>1.032362459546926</v>
       </c>
     </row>
     <row r="286">
@@ -13147,7 +13147,7 @@
       <c r="O286" t="inlineStr"/>
       <c r="P286" t="inlineStr"/>
       <c r="Q286" t="n">
-        <v>0.9732142857142857</v>
+        <v>0.9642857142857143</v>
       </c>
     </row>
     <row r="287">
@@ -13192,7 +13192,7 @@
       <c r="O287" t="inlineStr"/>
       <c r="P287" t="inlineStr"/>
       <c r="Q287" t="n">
-        <v>0.9158878504672897</v>
+        <v>0.9345794392523364</v>
       </c>
     </row>
     <row r="288">
@@ -13237,7 +13237,7 @@
       <c r="O288" t="inlineStr"/>
       <c r="P288" t="inlineStr"/>
       <c r="Q288" t="n">
-        <v>0.9603960396039604</v>
+        <v>0.9636963696369638</v>
       </c>
     </row>
     <row r="289">
@@ -13282,7 +13282,7 @@
       <c r="O289" t="inlineStr"/>
       <c r="P289" t="inlineStr"/>
       <c r="Q289" t="n">
-        <v>1.019230769230769</v>
+        <v>1.012820512820513</v>
       </c>
     </row>
     <row r="290">
@@ -13327,7 +13327,7 @@
       <c r="O290" t="inlineStr"/>
       <c r="P290" t="inlineStr"/>
       <c r="Q290" t="n">
-        <v>0.9910714285714286</v>
+        <v>0.9851190476190476</v>
       </c>
     </row>
     <row r="291">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="P292" t="inlineStr"/>
       <c r="Q292" t="n">
-        <v>1.048192771084337</v>
+        <v>1.032128514056225</v>
       </c>
     </row>
     <row r="293">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="P294" t="inlineStr"/>
       <c r="Q294" t="n">
-        <v>1.10752688172043</v>
+        <v>1.118279569892473</v>
       </c>
     </row>
     <row r="295">
@@ -13562,7 +13562,7 @@
       </c>
       <c r="P295" t="inlineStr"/>
       <c r="Q295" t="n">
-        <v>0.711864406779661</v>
+        <v>0.6949152542372882</v>
       </c>
     </row>
     <row r="296">
@@ -13615,7 +13615,7 @@
         <v>1.156862745098039</v>
       </c>
       <c r="Q296" t="n">
-        <v>1</v>
+        <v>1.022727272727273</v>
       </c>
     </row>
     <row r="297">
@@ -13721,7 +13721,7 @@
         <v>1.348837209302326</v>
       </c>
       <c r="Q298" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9015873015873016</v>
       </c>
     </row>
     <row r="299">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="P301" t="inlineStr"/>
       <c r="Q301" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8384615384615385</v>
       </c>
     </row>
     <row r="302">
@@ -13905,7 +13905,7 @@
         <v>0.8767123287671232</v>
       </c>
       <c r="Q302" t="n">
-        <v>1.017699115044248</v>
+        <v>1.058997050147493</v>
       </c>
     </row>
     <row r="303">
@@ -13958,7 +13958,7 @@
         <v>1.046153846153846</v>
       </c>
       <c r="Q303" t="n">
-        <v>1.111111111111111</v>
+        <v>1.066137566137566</v>
       </c>
     </row>
     <row r="304">
@@ -14011,7 +14011,7 @@
         <v>1.015151515151515</v>
       </c>
       <c r="Q304" t="n">
-        <v>0.8863636363636364</v>
+        <v>0.9065656565656565</v>
       </c>
     </row>
     <row r="305">
@@ -14064,7 +14064,7 @@
         <v>1.035087719298246</v>
       </c>
       <c r="Q305" t="n">
-        <v>0.84251968503937</v>
+        <v>0.8766404199475065</v>
       </c>
     </row>
     <row r="306">
@@ -14117,7 +14117,7 @@
         <v>0.7936507936507936</v>
       </c>
       <c r="Q306" t="n">
-        <v>1.221153846153846</v>
+        <v>1.189102564102564</v>
       </c>
     </row>
     <row r="307">
@@ -14170,7 +14170,7 @@
         <v>0.6486486486486487</v>
       </c>
       <c r="Q307" t="n">
-        <v>0.8677685950413223</v>
+        <v>0.8622589531680441</v>
       </c>
     </row>
     <row r="308">
@@ -14223,7 +14223,7 @@
         <v>0.7471264367816092</v>
       </c>
       <c r="Q308" t="n">
-        <v>0.991304347826087</v>
+        <v>0.9971014492753623</v>
       </c>
     </row>
     <row r="309">
@@ -14272,7 +14272,7 @@
       <c r="O309" t="inlineStr"/>
       <c r="P309" t="inlineStr"/>
       <c r="Q309" t="n">
-        <v>0.926829268292683</v>
+        <v>0.937669376693767</v>
       </c>
     </row>
     <row r="310">
@@ -14319,7 +14319,7 @@
       <c r="O310" t="inlineStr"/>
       <c r="P310" t="inlineStr"/>
       <c r="Q310" t="n">
-        <v>0.84</v>
+        <v>0.8213333333333332</v>
       </c>
     </row>
     <row r="311">
@@ -14364,7 +14364,7 @@
       <c r="O311" t="inlineStr"/>
       <c r="P311" t="inlineStr"/>
       <c r="Q311" t="n">
-        <v>1.168421052631579</v>
+        <v>1.150877192982456</v>
       </c>
     </row>
     <row r="312">
@@ -14409,7 +14409,7 @@
       <c r="O312" t="inlineStr"/>
       <c r="P312" t="inlineStr"/>
       <c r="Q312" t="n">
-        <v>0.9306930693069307</v>
+        <v>0.9405940594059405</v>
       </c>
     </row>
     <row r="313">
@@ -14499,7 +14499,7 @@
       <c r="O314" t="inlineStr"/>
       <c r="P314" t="inlineStr"/>
       <c r="Q314" t="n">
-        <v>0.7923076923076923</v>
+        <v>0.8282051282051281</v>
       </c>
     </row>
     <row r="315">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="P316" t="inlineStr"/>
       <c r="Q316" t="n">
-        <v>0.7027027027027027</v>
+        <v>0.7072072072072071</v>
       </c>
     </row>
     <row r="317">
@@ -14636,7 +14636,7 @@
       <c r="O317" t="inlineStr"/>
       <c r="P317" t="inlineStr"/>
       <c r="Q317" t="n">
-        <v>0.746268656716418</v>
+        <v>0.7412935323383084</v>
       </c>
     </row>
     <row r="318">
@@ -14953,7 +14953,7 @@
       <c r="O324" t="inlineStr"/>
       <c r="P324" t="inlineStr"/>
       <c r="Q324" t="n">
-        <v>1.060240963855422</v>
+        <v>1.06425702811245</v>
       </c>
     </row>
     <row r="325">
@@ -14998,7 +14998,7 @@
       <c r="O325" t="inlineStr"/>
       <c r="P325" t="inlineStr"/>
       <c r="Q325" t="n">
-        <v>1.060240963855422</v>
+        <v>1.06425702811245</v>
       </c>
     </row>
     <row r="326">
@@ -15566,7 +15566,7 @@
       <c r="O339" t="inlineStr"/>
       <c r="P339" t="inlineStr"/>
       <c r="Q339" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7587719298245614</v>
       </c>
     </row>
     <row r="340">
@@ -15611,7 +15611,7 @@
       <c r="O340" t="inlineStr"/>
       <c r="P340" t="inlineStr"/>
       <c r="Q340" t="n">
-        <v>0.8970588235294118</v>
+        <v>0.9019607843137254</v>
       </c>
     </row>
     <row r="341">
@@ -15656,7 +15656,7 @@
       <c r="O341" t="inlineStr"/>
       <c r="P341" t="inlineStr"/>
       <c r="Q341" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.8194444444444444</v>
       </c>
     </row>
     <row r="342">
@@ -15701,7 +15701,7 @@
       <c r="O342" t="inlineStr"/>
       <c r="P342" t="inlineStr"/>
       <c r="Q342" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.7474747474747475</v>
       </c>
     </row>
     <row r="343">
@@ -15789,7 +15789,7 @@
       </c>
       <c r="P344" t="inlineStr"/>
       <c r="Q344" t="n">
-        <v>0.7547169811320755</v>
+        <v>0.7295597484276729</v>
       </c>
     </row>
     <row r="345">
@@ -15838,7 +15838,7 @@
       <c r="O345" t="inlineStr"/>
       <c r="P345" t="inlineStr"/>
       <c r="Q345" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9206349206349206</v>
       </c>
     </row>
     <row r="346">
@@ -15885,7 +15885,7 @@
       <c r="O346" t="inlineStr"/>
       <c r="P346" t="inlineStr"/>
       <c r="Q346" t="n">
-        <v>1.017241379310345</v>
+        <v>0.9942528735632185</v>
       </c>
     </row>
     <row r="347">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="P347" t="inlineStr"/>
       <c r="Q347" t="n">
-        <v>0.84375</v>
+        <v>0.8489583333333333</v>
       </c>
     </row>
     <row r="348">
@@ -15981,7 +15981,7 @@
       </c>
       <c r="P348" t="inlineStr"/>
       <c r="Q348" t="n">
-        <v>0.8615384615384616</v>
+        <v>0.882051282051282</v>
       </c>
     </row>
     <row r="349">
@@ -16034,7 +16034,7 @@
         <v>0.7297297297297297</v>
       </c>
       <c r="Q349" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8941798941798941</v>
       </c>
     </row>
     <row r="350">
@@ -16087,7 +16087,7 @@
         <v>0.9705882352941176</v>
       </c>
       <c r="Q350" t="n">
-        <v>0.9393939393939394</v>
+        <v>0.9191919191919192</v>
       </c>
     </row>
     <row r="351">
@@ -16249,7 +16249,7 @@
       </c>
       <c r="P354" t="inlineStr"/>
       <c r="Q354" t="n">
-        <v>0.7702702702702703</v>
+        <v>0.8153153153153152</v>
       </c>
     </row>
     <row r="355">
@@ -16302,7 +16302,7 @@
         <v>0.5892857142857143</v>
       </c>
       <c r="Q355" t="n">
-        <v>1</v>
+        <v>0.9780701754385964</v>
       </c>
     </row>
     <row r="356">
@@ -16355,7 +16355,7 @@
         <v>0.723404255319149</v>
       </c>
       <c r="Q356" t="n">
-        <v>1.05</v>
+        <v>1.054166666666667</v>
       </c>
     </row>
     <row r="357">
@@ -16408,7 +16408,7 @@
         <v>0.7692307692307693</v>
       </c>
       <c r="Q357" t="n">
-        <v>0.9259259259259259</v>
+        <v>0.9176954732510287</v>
       </c>
     </row>
     <row r="358">
@@ -16461,7 +16461,7 @@
         <v>1.038461538461539</v>
       </c>
       <c r="Q358" t="n">
-        <v>0.975</v>
+        <v>0.9958333333333333</v>
       </c>
     </row>
     <row r="359">
@@ -16514,7 +16514,7 @@
         <v>1.111111111111111</v>
       </c>
       <c r="Q359" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.9244444444444444</v>
       </c>
     </row>
     <row r="360">
@@ -16567,7 +16567,7 @@
         <v>1.523809523809524</v>
       </c>
       <c r="Q360" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.9641025641025642</v>
       </c>
     </row>
     <row r="361">
@@ -16616,7 +16616,7 @@
       <c r="O361" t="inlineStr"/>
       <c r="P361" t="inlineStr"/>
       <c r="Q361" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6931216931216932</v>
       </c>
     </row>
     <row r="362">
@@ -16663,7 +16663,7 @@
       <c r="O362" t="inlineStr"/>
       <c r="P362" t="inlineStr"/>
       <c r="Q362" t="n">
-        <v>1.466666666666667</v>
+        <v>1.422222222222222</v>
       </c>
     </row>
     <row r="363">
@@ -16708,7 +16708,7 @@
       <c r="O363" t="inlineStr"/>
       <c r="P363" t="inlineStr"/>
       <c r="Q363" t="n">
-        <v>0.921875</v>
+        <v>0.90625</v>
       </c>
     </row>
     <row r="364">
@@ -16753,7 +16753,7 @@
       <c r="O364" t="inlineStr"/>
       <c r="P364" t="inlineStr"/>
       <c r="Q364" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.8709677419354839</v>
       </c>
     </row>
     <row r="365">
@@ -16843,7 +16843,7 @@
       <c r="O366" t="inlineStr"/>
       <c r="P366" t="inlineStr"/>
       <c r="Q366" t="n">
-        <v>1.140350877192982</v>
+        <v>1.116959064327485</v>
       </c>
     </row>
     <row r="367">
@@ -16931,7 +16931,7 @@
       </c>
       <c r="P368" t="inlineStr"/>
       <c r="Q368" t="n">
-        <v>1.147058823529412</v>
+        <v>1.186274509803922</v>
       </c>
     </row>
     <row r="369">
@@ -16980,7 +16980,7 @@
       <c r="O369" t="inlineStr"/>
       <c r="P369" t="inlineStr"/>
       <c r="Q369" t="n">
-        <v>1.162162162162162</v>
+        <v>1.117117117117117</v>
       </c>
     </row>
     <row r="370">
@@ -17027,7 +17027,7 @@
       <c r="O370" t="inlineStr"/>
       <c r="P370" t="inlineStr"/>
       <c r="Q370" t="n">
-        <v>0.8648648648648649</v>
+        <v>0.8918918918918919</v>
       </c>
     </row>
     <row r="371">
@@ -17074,7 +17074,7 @@
       </c>
       <c r="P371" t="inlineStr"/>
       <c r="Q371" t="n">
-        <v>0.8717948717948718</v>
+        <v>0.8547008547008548</v>
       </c>
     </row>
     <row r="372">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="P372" t="inlineStr"/>
       <c r="Q372" t="n">
-        <v>0.9117647058823529</v>
+        <v>0.8921568627450981</v>
       </c>
     </row>
     <row r="373">
@@ -17176,7 +17176,7 @@
         <v>0.7027027027027027</v>
       </c>
       <c r="Q373" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.7017543859649122</v>
       </c>
     </row>
     <row r="374">
@@ -17229,7 +17229,7 @@
         <v>0.5531914893617021</v>
       </c>
       <c r="Q374" t="n">
-        <v>0.9361702127659575</v>
+        <v>0.9290780141843971</v>
       </c>
     </row>
     <row r="375">
@@ -17391,7 +17391,7 @@
       </c>
       <c r="P378" t="inlineStr"/>
       <c r="Q378" t="n">
-        <v>0.9074074074074074</v>
+        <v>0.9320987654320987</v>
       </c>
     </row>
     <row r="379">
@@ -17497,7 +17497,7 @@
         <v>0.9285714285714286</v>
       </c>
       <c r="Q380" t="n">
-        <v>1.017857142857143</v>
+        <v>0.9940476190476192</v>
       </c>
     </row>
     <row r="381">
@@ -17550,7 +17550,7 @@
         <v>0.8461538461538461</v>
       </c>
       <c r="Q381" t="n">
-        <v>0.9433962264150944</v>
+        <v>0.9748427672955975</v>
       </c>
     </row>
     <row r="382">
@@ -17603,7 +17603,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="Q382" t="n">
-        <v>1.035714285714286</v>
+        <v>1.005952380952381</v>
       </c>
     </row>
     <row r="383">
@@ -17656,7 +17656,7 @@
         <v>0.6551724137931034</v>
       </c>
       <c r="Q383" t="n">
-        <v>1.017857142857143</v>
+        <v>1.023809523809524</v>
       </c>
     </row>
     <row r="384">
@@ -17709,7 +17709,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="Q384" t="n">
-        <v>0.8983050847457628</v>
+        <v>0.9322033898305084</v>
       </c>
     </row>
     <row r="385">
@@ -17758,7 +17758,7 @@
       <c r="O385" t="inlineStr"/>
       <c r="P385" t="inlineStr"/>
       <c r="Q385" t="n">
-        <v>1</v>
+        <v>0.9811320754716981</v>
       </c>
     </row>
     <row r="386">
@@ -17805,7 +17805,7 @@
       <c r="O386" t="inlineStr"/>
       <c r="P386" t="inlineStr"/>
       <c r="Q386" t="n">
-        <v>1.155555555555555</v>
+        <v>1.103703703703704</v>
       </c>
     </row>
     <row r="387">
@@ -17850,7 +17850,7 @@
       <c r="O387" t="inlineStr"/>
       <c r="P387" t="inlineStr"/>
       <c r="Q387" t="n">
-        <v>0.8269230769230769</v>
+        <v>0.8653846153846154</v>
       </c>
     </row>
     <row r="388">
@@ -17895,7 +17895,7 @@
       <c r="O388" t="inlineStr"/>
       <c r="P388" t="inlineStr"/>
       <c r="Q388" t="n">
-        <v>1.090909090909091</v>
+        <v>1.045454545454545</v>
       </c>
     </row>
     <row r="389">
@@ -17940,7 +17940,7 @@
       <c r="O389" t="inlineStr"/>
       <c r="P389" t="inlineStr"/>
       <c r="Q389" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.7361111111111112</v>
       </c>
     </row>
     <row r="390">
@@ -17985,7 +17985,7 @@
       <c r="O390" t="inlineStr"/>
       <c r="P390" t="inlineStr"/>
       <c r="Q390" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.9487179487179487</v>
       </c>
     </row>
     <row r="391">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="P392" t="inlineStr"/>
       <c r="Q392" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="393">
@@ -18126,7 +18126,7 @@
         <v>0.2941176470588235</v>
       </c>
       <c r="Q393" t="n">
-        <v>1.058823529411765</v>
+        <v>1.03921568627451</v>
       </c>
     </row>
     <row r="394">
@@ -18179,7 +18179,7 @@
         <v>0.4</v>
       </c>
       <c r="Q394" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.9722222222222222</v>
       </c>
     </row>
     <row r="395">
@@ -18232,7 +18232,7 @@
         <v>0.375</v>
       </c>
       <c r="Q395" t="n">
-        <v>0.75</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="396">
@@ -18285,7 +18285,7 @@
         <v>0.5</v>
       </c>
       <c r="Q396" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.893939393939394</v>
       </c>
     </row>
     <row r="397">
@@ -18338,7 +18338,7 @@
         <v>0.3846153846153846</v>
       </c>
       <c r="Q397" t="n">
-        <v>0.8846153846153846</v>
+        <v>0.8717948717948717</v>
       </c>
     </row>
     <row r="398">
@@ -18391,7 +18391,7 @@
         <v>0.6</v>
       </c>
       <c r="Q398" t="n">
-        <v>0.9</v>
+        <v>0.888888888888889</v>
       </c>
     </row>
     <row r="399">
@@ -18444,7 +18444,7 @@
         <v>0.6842105263157895</v>
       </c>
       <c r="Q399" t="n">
-        <v>1.166666666666667</v>
+        <v>1.177777777777778</v>
       </c>
     </row>
     <row r="400">
@@ -18497,7 +18497,7 @@
         <v>1</v>
       </c>
       <c r="Q400" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.4298245614035087</v>
       </c>
     </row>
     <row r="401">
@@ -18550,7 +18550,7 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="Q401" t="n">
-        <v>1.764705882352941</v>
+        <v>1.725490196078431</v>
       </c>
     </row>
     <row r="402">
@@ -18603,7 +18603,7 @@
         <v>0.4375</v>
       </c>
       <c r="Q402" t="n">
-        <v>0.8125</v>
+        <v>0.8541666666666667</v>
       </c>
     </row>
     <row r="403">
@@ -18656,7 +18656,7 @@
         <v>0.25</v>
       </c>
       <c r="Q403" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.8989898989898989</v>
       </c>
     </row>
     <row r="404">
@@ -18709,7 +18709,7 @@
         <v>0.2727272727272727</v>
       </c>
       <c r="Q404" t="n">
-        <v>0.90625</v>
+        <v>0.9270833333333333</v>
       </c>
     </row>
     <row r="405">
@@ -18762,7 +18762,7 @@
         <v>0.4</v>
       </c>
       <c r="Q405" t="n">
-        <v>0.96875</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="406">
@@ -18868,7 +18868,7 @@
         <v>0.5</v>
       </c>
       <c r="Q407" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.9242424242424242</v>
       </c>
     </row>
     <row r="408">
@@ -18921,7 +18921,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="Q408" t="n">
-        <v>0.72</v>
+        <v>0.7466666666666667</v>
       </c>
     </row>
     <row r="409">
@@ -18970,7 +18970,7 @@
       <c r="O409" t="inlineStr"/>
       <c r="P409" t="inlineStr"/>
       <c r="Q409" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.5873015873015872</v>
       </c>
     </row>
     <row r="410">
@@ -19017,7 +19017,7 @@
       <c r="O410" t="inlineStr"/>
       <c r="P410" t="inlineStr"/>
       <c r="Q410" t="n">
-        <v>1.1</v>
+        <v>1.116666666666667</v>
       </c>
     </row>
     <row r="411">
@@ -19062,7 +19062,7 @@
       <c r="O411" t="inlineStr"/>
       <c r="P411" t="inlineStr"/>
       <c r="Q411" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.8076923076923077</v>
       </c>
     </row>
     <row r="412">
@@ -19107,7 +19107,7 @@
       <c r="O412" t="inlineStr"/>
       <c r="P412" t="inlineStr"/>
       <c r="Q412" t="n">
-        <v>0.92</v>
+        <v>0.8933333333333334</v>
       </c>
     </row>
     <row r="413">
@@ -19152,7 +19152,7 @@
       <c r="O413" t="inlineStr"/>
       <c r="P413" t="inlineStr"/>
       <c r="Q413" t="n">
-        <v>0.8846153846153846</v>
+        <v>0.8461538461538461</v>
       </c>
     </row>
     <row r="414">
@@ -19197,7 +19197,7 @@
       <c r="O414" t="inlineStr"/>
       <c r="P414" t="inlineStr"/>
       <c r="Q414" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.9130434782608695</v>
       </c>
     </row>
     <row r="415">
@@ -19285,7 +19285,7 @@
       </c>
       <c r="P416" t="inlineStr"/>
       <c r="Q416" t="n">
-        <v>0.8320610687022901</v>
+        <v>0.8269720101781172</v>
       </c>
     </row>
     <row r="417">
@@ -19334,7 +19334,7 @@
       <c r="O417" t="inlineStr"/>
       <c r="P417" t="inlineStr"/>
       <c r="Q417" t="n">
-        <v>0.9180327868852459</v>
+        <v>0.9289617486338798</v>
       </c>
     </row>
     <row r="418">
@@ -19383,7 +19383,7 @@
       </c>
       <c r="P418" t="inlineStr"/>
       <c r="Q418" t="n">
-        <v>0.904</v>
+        <v>0.9226666666666667</v>
       </c>
     </row>
     <row r="419">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="P419" t="inlineStr"/>
       <c r="Q419" t="n">
-        <v>1.015748031496063</v>
+        <v>0.9973753280839894</v>
       </c>
     </row>
     <row r="420">
@@ -19485,7 +19485,7 @@
         <v>0.5</v>
       </c>
       <c r="Q420" t="n">
-        <v>0.9361702127659575</v>
+        <v>0.9314420803782506</v>
       </c>
     </row>
     <row r="421">
@@ -19538,7 +19538,7 @@
         <v>0.5903614457831325</v>
       </c>
       <c r="Q421" t="n">
-        <v>0.8896103896103896</v>
+        <v>0.9004329004329004</v>
       </c>
     </row>
     <row r="422">
@@ -19591,7 +19591,7 @@
         <v>0.6025641025641025</v>
       </c>
       <c r="Q422" t="n">
-        <v>0.7394366197183099</v>
+        <v>0.7417840375586855</v>
       </c>
     </row>
     <row r="423">
@@ -19722,7 +19722,7 @@
       </c>
       <c r="P425" t="inlineStr"/>
       <c r="Q425" t="n">
-        <v>0.9044117647058824</v>
+        <v>0.9240196078431372</v>
       </c>
     </row>
     <row r="426">
@@ -19775,7 +19775,7 @@
         <v>0.7397260273972602</v>
       </c>
       <c r="Q426" t="n">
-        <v>1</v>
+        <v>0.9953379953379954</v>
       </c>
     </row>
     <row r="427">
@@ -19828,7 +19828,7 @@
         <v>0.7272727272727273</v>
       </c>
       <c r="Q427" t="n">
-        <v>0.8811188811188811</v>
+        <v>0.8717948717948717</v>
       </c>
     </row>
     <row r="428">
@@ -19881,7 +19881,7 @@
         <v>0.7361111111111112</v>
       </c>
       <c r="Q428" t="n">
-        <v>0.9485294117647058</v>
+        <v>0.9583333333333334</v>
       </c>
     </row>
     <row r="429">
@@ -19934,7 +19934,7 @@
         <v>0.6707317073170732</v>
       </c>
       <c r="Q429" t="n">
-        <v>0.9436619718309859</v>
+        <v>0.9413145539906103</v>
       </c>
     </row>
     <row r="430">
@@ -19987,7 +19987,7 @@
         <v>0.6375</v>
       </c>
       <c r="Q430" t="n">
-        <v>0.9657534246575342</v>
+        <v>0.9748858447488585</v>
       </c>
     </row>
     <row r="431">
@@ -20040,7 +20040,7 @@
         <v>0.6941176470588235</v>
       </c>
       <c r="Q431" t="n">
-        <v>1.04</v>
+        <v>1.037777777777778</v>
       </c>
     </row>
     <row r="432">
@@ -20093,7 +20093,7 @@
         <v>0.7333333333333333</v>
       </c>
       <c r="Q432" t="n">
-        <v>0.9520958083832335</v>
+        <v>0.9441117764471058</v>
       </c>
     </row>
     <row r="433">
@@ -20142,7 +20142,7 @@
       <c r="O433" t="inlineStr"/>
       <c r="P433" t="inlineStr"/>
       <c r="Q433" t="n">
-        <v>0.8735632183908046</v>
+        <v>0.8869731800766284</v>
       </c>
     </row>
     <row r="434">
@@ -20189,7 +20189,7 @@
       <c r="O434" t="inlineStr"/>
       <c r="P434" t="inlineStr"/>
       <c r="Q434" t="n">
-        <v>0.9695121951219512</v>
+        <v>0.9573170731707317</v>
       </c>
     </row>
     <row r="435">
@@ -20234,7 +20234,7 @@
       <c r="O435" t="inlineStr"/>
       <c r="P435" t="inlineStr"/>
       <c r="Q435" t="n">
-        <v>0.9753086419753086</v>
+        <v>0.977366255144033</v>
       </c>
     </row>
     <row r="436">
@@ -20279,7 +20279,7 @@
       <c r="O436" t="inlineStr"/>
       <c r="P436" t="inlineStr"/>
       <c r="Q436" t="n">
-        <v>0.9570552147239264</v>
+        <v>0.9591002044989776</v>
       </c>
     </row>
     <row r="437">
@@ -20324,7 +20324,7 @@
       <c r="O437" t="inlineStr"/>
       <c r="P437" t="inlineStr"/>
       <c r="Q437" t="n">
-        <v>0.8323699421965318</v>
+        <v>0.8439306358381503</v>
       </c>
     </row>
     <row r="438">
@@ -20920,7 +20920,7 @@
       <c r="O457" t="inlineStr"/>
       <c r="P457" t="inlineStr"/>
       <c r="Q457" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9305555555555557</v>
       </c>
     </row>
     <row r="458">
@@ -20967,7 +20967,7 @@
       <c r="O458" t="inlineStr"/>
       <c r="P458" t="inlineStr"/>
       <c r="Q458" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.8172043010752688</v>
       </c>
     </row>
     <row r="459">
@@ -21102,7 +21102,7 @@
       <c r="O461" t="inlineStr"/>
       <c r="P461" t="inlineStr"/>
       <c r="Q461" t="n">
-        <v>0.875</v>
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="462">
@@ -21235,7 +21235,7 @@
       </c>
       <c r="P464" t="inlineStr"/>
       <c r="Q464" t="n">
-        <v>1.388888888888889</v>
+        <v>1.296296296296296</v>
       </c>
     </row>
     <row r="465">
@@ -21284,7 +21284,7 @@
       <c r="O465" t="inlineStr"/>
       <c r="P465" t="inlineStr"/>
       <c r="Q465" t="n">
-        <v>0.75</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="466">
@@ -21333,7 +21333,7 @@
       </c>
       <c r="P466" t="inlineStr"/>
       <c r="Q466" t="n">
-        <v>1.1</v>
+        <v>1.033333333333333</v>
       </c>
     </row>
     <row r="467">
@@ -21382,7 +21382,7 @@
       </c>
       <c r="P467" t="inlineStr"/>
       <c r="Q467" t="n">
-        <v>0.9565217391304348</v>
+        <v>1</v>
       </c>
     </row>
     <row r="468">
@@ -21435,7 +21435,7 @@
         <v>0.6521739130434783</v>
       </c>
       <c r="Q468" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="469">
@@ -21488,7 +21488,7 @@
         <v>0.6363636363636364</v>
       </c>
       <c r="Q469" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.619047619047619</v>
       </c>
     </row>
     <row r="470">
@@ -21541,7 +21541,7 @@
         <v>0.8</v>
       </c>
       <c r="Q470" t="n">
-        <v>1.315789473684211</v>
+        <v>1.192982456140351</v>
       </c>
     </row>
     <row r="471">
@@ -21672,7 +21672,7 @@
       </c>
       <c r="P473" t="inlineStr"/>
       <c r="Q473" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="474">
@@ -21725,7 +21725,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="Q474" t="n">
-        <v>1.185185185185185</v>
+        <v>1.148148148148148</v>
       </c>
     </row>
     <row r="475">
@@ -21778,7 +21778,7 @@
         <v>0.7826086956521739</v>
       </c>
       <c r="Q475" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9313725490196078</v>
       </c>
     </row>
     <row r="476">
@@ -21831,7 +21831,7 @@
         <v>0.6</v>
       </c>
       <c r="Q476" t="n">
-        <v>0.8421052631578947</v>
+        <v>0.8947368421052632</v>
       </c>
     </row>
     <row r="477">
@@ -21884,7 +21884,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="Q477" t="n">
-        <v>0.9714285714285714</v>
+        <v>0.9428571428571428</v>
       </c>
     </row>
     <row r="478">
@@ -21937,7 +21937,7 @@
         <v>0.5</v>
       </c>
       <c r="Q478" t="n">
-        <v>1.033333333333333</v>
+        <v>0.9777777777777779</v>
       </c>
     </row>
     <row r="479">
@@ -21990,7 +21990,7 @@
         <v>1</v>
       </c>
       <c r="Q479" t="n">
-        <v>0.78125</v>
+        <v>0.8229166666666666</v>
       </c>
     </row>
     <row r="480">
@@ -22043,7 +22043,7 @@
         <v>1.25</v>
       </c>
       <c r="Q480" t="n">
-        <v>0.9615384615384616</v>
+        <v>0.9743589743589745</v>
       </c>
     </row>
     <row r="481">
@@ -22092,7 +22092,7 @@
       <c r="O481" t="inlineStr"/>
       <c r="P481" t="inlineStr"/>
       <c r="Q481" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.9710144927536233</v>
       </c>
     </row>
     <row r="482">
@@ -22139,7 +22139,7 @@
       <c r="O482" t="inlineStr"/>
       <c r="P482" t="inlineStr"/>
       <c r="Q482" t="n">
-        <v>1.142857142857143</v>
+        <v>1.063492063492064</v>
       </c>
     </row>
     <row r="483">
@@ -22184,7 +22184,7 @@
       <c r="O483" t="inlineStr"/>
       <c r="P483" t="inlineStr"/>
       <c r="Q483" t="n">
-        <v>0.96</v>
+        <v>0.9733333333333333</v>
       </c>
     </row>
     <row r="484">
@@ -22229,7 +22229,7 @@
       <c r="O484" t="inlineStr"/>
       <c r="P484" t="inlineStr"/>
       <c r="Q484" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.9710144927536232</v>
       </c>
     </row>
     <row r="485">
@@ -22274,7 +22274,7 @@
       <c r="O485" t="inlineStr"/>
       <c r="P485" t="inlineStr"/>
       <c r="Q485" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9545454545454546</v>
       </c>
     </row>
     <row r="486">
@@ -22319,7 +22319,7 @@
       <c r="O486" t="inlineStr"/>
       <c r="P486" t="inlineStr"/>
       <c r="Q486" t="n">
-        <v>1.090909090909091</v>
+        <v>1.045454545454545</v>
       </c>
     </row>
     <row r="487">
@@ -22407,7 +22407,7 @@
       </c>
       <c r="P488" t="inlineStr"/>
       <c r="Q488" t="n">
-        <v>1.107142857142857</v>
+        <v>1.119047619047619</v>
       </c>
     </row>
     <row r="489">
@@ -22456,7 +22456,7 @@
       <c r="O489" t="inlineStr"/>
       <c r="P489" t="inlineStr"/>
       <c r="Q489" t="n">
-        <v>1.176470588235294</v>
+        <v>1.166666666666667</v>
       </c>
     </row>
     <row r="490">
@@ -22505,7 +22505,7 @@
       </c>
       <c r="P490" t="inlineStr"/>
       <c r="Q490" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8518518518518517</v>
       </c>
     </row>
     <row r="491">
@@ -22607,7 +22607,7 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="Q492" t="n">
-        <v>1.051282051282051</v>
+        <v>1.042735042735043</v>
       </c>
     </row>
     <row r="493">
@@ -22660,7 +22660,7 @@
         <v>0.7826086956521739</v>
       </c>
       <c r="Q493" t="n">
-        <v>0.9512195121951219</v>
+        <v>0.983739837398374</v>
       </c>
     </row>
     <row r="494">
@@ -22713,7 +22713,7 @@
         <v>1.133333333333333</v>
       </c>
       <c r="Q494" t="n">
-        <v>0.8837209302325582</v>
+        <v>0.8449612403100776</v>
       </c>
     </row>
     <row r="495">
@@ -22844,7 +22844,7 @@
       </c>
       <c r="P497" t="inlineStr"/>
       <c r="Q497" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8444444444444446</v>
       </c>
     </row>
     <row r="498">
@@ -22897,7 +22897,7 @@
         <v>0.9583333333333334</v>
       </c>
       <c r="Q498" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.946236559139785</v>
       </c>
     </row>
     <row r="499">
@@ -22950,7 +22950,7 @@
         <v>0.9629629629629629</v>
       </c>
       <c r="Q499" t="n">
-        <v>1</v>
+        <v>1.010416666666667</v>
       </c>
     </row>
     <row r="500">
@@ -23003,7 +23003,7 @@
         <v>1</v>
       </c>
       <c r="Q500" t="n">
-        <v>1.114285714285714</v>
+        <v>1.085714285714286</v>
       </c>
     </row>
     <row r="501">
@@ -23056,7 +23056,7 @@
         <v>1.115384615384615</v>
       </c>
       <c r="Q501" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.6666666666666667</v>
       </c>
     </row>
     <row r="502">
@@ -23109,7 +23109,7 @@
         <v>0.76</v>
       </c>
       <c r="Q502" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9666666666666667</v>
       </c>
     </row>
     <row r="503">
@@ -23162,7 +23162,7 @@
         <v>0.8333333333333334</v>
       </c>
       <c r="Q503" t="n">
-        <v>1.428571428571429</v>
+        <v>1.369047619047619</v>
       </c>
     </row>
     <row r="504">
@@ -23264,7 +23264,7 @@
       <c r="O505" t="inlineStr"/>
       <c r="P505" t="inlineStr"/>
       <c r="Q505" t="n">
-        <v>0.7441860465116279</v>
+        <v>0.806201550387597</v>
       </c>
     </row>
     <row r="506">
@@ -23311,7 +23311,7 @@
       <c r="O506" t="inlineStr"/>
       <c r="P506" t="inlineStr"/>
       <c r="Q506" t="n">
-        <v>1.147058823529412</v>
+        <v>1.068627450980392</v>
       </c>
     </row>
     <row r="507">
@@ -23356,7 +23356,7 @@
       <c r="O507" t="inlineStr"/>
       <c r="P507" t="inlineStr"/>
       <c r="Q507" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.7222222222222222</v>
       </c>
     </row>
     <row r="508">
@@ -23401,7 +23401,7 @@
       <c r="O508" t="inlineStr"/>
       <c r="P508" t="inlineStr"/>
       <c r="Q508" t="n">
-        <v>1</v>
+        <v>0.9404761904761906</v>
       </c>
     </row>
     <row r="509">
@@ -23446,7 +23446,7 @@
       <c r="O509" t="inlineStr"/>
       <c r="P509" t="inlineStr"/>
       <c r="Q509" t="n">
-        <v>1.142857142857143</v>
+        <v>1.178571428571429</v>
       </c>
     </row>
     <row r="510">
@@ -23491,7 +23491,7 @@
       <c r="O510" t="inlineStr"/>
       <c r="P510" t="inlineStr"/>
       <c r="Q510" t="n">
-        <v>0.8780487804878049</v>
+        <v>0.8861788617886179</v>
       </c>
     </row>
     <row r="511">
@@ -23610,7 +23610,7 @@
       <c r="O513" t="inlineStr"/>
       <c r="P513" t="inlineStr"/>
       <c r="Q513" t="n">
-        <v>1</v>
+        <v>0.9583333333333333</v>
       </c>
     </row>
     <row r="514">
@@ -23811,7 +23811,7 @@
       </c>
       <c r="P518" t="inlineStr"/>
       <c r="Q518" t="n">
-        <v>1.066666666666667</v>
+        <v>1.022222222222222</v>
       </c>
     </row>
     <row r="519">
@@ -23942,7 +23942,7 @@
       </c>
       <c r="P521" t="inlineStr"/>
       <c r="Q521" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.746031746031746</v>
       </c>
     </row>
     <row r="522">
@@ -24073,7 +24073,7 @@
       </c>
       <c r="P524" t="inlineStr"/>
       <c r="Q524" t="n">
-        <v>1.133333333333333</v>
+        <v>1.177777777777778</v>
       </c>
     </row>
     <row r="525">
@@ -24179,7 +24179,7 @@
         <v>0.625</v>
       </c>
       <c r="Q526" t="n">
-        <v>0.75</v>
+        <v>0.6875</v>
       </c>
     </row>
     <row r="527">
@@ -24232,7 +24232,7 @@
         <v>1.75</v>
       </c>
       <c r="Q527" t="n">
-        <v>0.5</v>
+        <v>0.5833333333333334</v>
       </c>
     </row>
     <row r="528">
@@ -24281,7 +24281,7 @@
       <c r="O528" t="inlineStr"/>
       <c r="P528" t="inlineStr"/>
       <c r="Q528" t="n">
-        <v>1.666666666666667</v>
+        <v>1.555555555555556</v>
       </c>
     </row>
     <row r="529">
@@ -24328,7 +24328,7 @@
       <c r="O529" t="inlineStr"/>
       <c r="P529" t="inlineStr"/>
       <c r="Q529" t="n">
-        <v>1.571428571428571</v>
+        <v>1.619047619047619</v>
       </c>
     </row>
     <row r="530">
@@ -24463,7 +24463,7 @@
       <c r="O532" t="inlineStr"/>
       <c r="P532" t="inlineStr"/>
       <c r="Q532" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5185185185185185</v>
       </c>
     </row>
     <row r="533">
@@ -24508,7 +24508,7 @@
       <c r="O533" t="inlineStr"/>
       <c r="P533" t="inlineStr"/>
       <c r="Q533" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="534">
@@ -24721,7 +24721,7 @@
       </c>
       <c r="P538" t="inlineStr"/>
       <c r="Q538" t="n">
-        <v>1.044117647058824</v>
+        <v>1.029411764705882</v>
       </c>
     </row>
     <row r="539">
@@ -24770,7 +24770,7 @@
       </c>
       <c r="P539" t="inlineStr"/>
       <c r="Q539" t="n">
-        <v>0.9397590361445783</v>
+        <v>0.9437751004016064</v>
       </c>
     </row>
     <row r="540">
@@ -24823,7 +24823,7 @@
         <v>0.6545454545454545</v>
       </c>
       <c r="Q540" t="n">
-        <v>0.8736842105263158</v>
+        <v>0.8842105263157894</v>
       </c>
     </row>
     <row r="541">
@@ -24876,7 +24876,7 @@
         <v>0.8666666666666667</v>
       </c>
       <c r="Q541" t="n">
-        <v>0.9555555555555556</v>
+        <v>0.9740740740740741</v>
       </c>
     </row>
     <row r="542">
@@ -24929,7 +24929,7 @@
         <v>1.097560975609756</v>
       </c>
       <c r="Q542" t="n">
-        <v>0.9770114942528736</v>
+        <v>0.9693486590038314</v>
       </c>
     </row>
     <row r="543">
@@ -25060,7 +25060,7 @@
       </c>
       <c r="P545" t="inlineStr"/>
       <c r="Q545" t="n">
-        <v>0.9069767441860465</v>
+        <v>0.8953488372093024</v>
       </c>
     </row>
     <row r="546">
@@ -25113,7 +25113,7 @@
         <v>1.022222222222222</v>
       </c>
       <c r="Q546" t="n">
-        <v>0.9629629629629629</v>
+        <v>0.9876543209876543</v>
       </c>
     </row>
     <row r="547">
@@ -25272,7 +25272,7 @@
         <v>0.86</v>
       </c>
       <c r="Q549" t="n">
-        <v>1.024691358024691</v>
+        <v>1.004115226337448</v>
       </c>
     </row>
     <row r="550">
@@ -25325,7 +25325,7 @@
         <v>1</v>
       </c>
       <c r="Q550" t="n">
-        <v>0.9647058823529412</v>
+        <v>0.9803921568627451</v>
       </c>
     </row>
     <row r="551">
@@ -25378,7 +25378,7 @@
         <v>0.8974358974358975</v>
       </c>
       <c r="Q551" t="n">
-        <v>0.9518072289156626</v>
+        <v>0.9477911646586346</v>
       </c>
     </row>
     <row r="552">
@@ -25431,7 +25431,7 @@
         <v>0.8055555555555556</v>
       </c>
       <c r="Q552" t="n">
-        <v>0.9605263157894737</v>
+        <v>0.9868421052631579</v>
       </c>
     </row>
     <row r="553">
@@ -25480,7 +25480,7 @@
       <c r="O553" t="inlineStr"/>
       <c r="P553" t="inlineStr"/>
       <c r="Q553" t="n">
-        <v>1.135135135135135</v>
+        <v>1.103603603603603</v>
       </c>
     </row>
     <row r="554">
@@ -25527,7 +25527,7 @@
       <c r="O554" t="inlineStr"/>
       <c r="P554" t="inlineStr"/>
       <c r="Q554" t="n">
-        <v>0.8831168831168831</v>
+        <v>0.8961038961038961</v>
       </c>
     </row>
     <row r="555">
@@ -25572,7 +25572,7 @@
       <c r="O555" t="inlineStr"/>
       <c r="P555" t="inlineStr"/>
       <c r="Q555" t="n">
-        <v>0.9848484848484849</v>
+        <v>0.9898989898989898</v>
       </c>
     </row>
     <row r="556">
@@ -25617,7 +25617,7 @@
       <c r="O556" t="inlineStr"/>
       <c r="P556" t="inlineStr"/>
       <c r="Q556" t="n">
-        <v>1.073529411764706</v>
+        <v>1.049019607843137</v>
       </c>
     </row>
     <row r="557">
@@ -25662,7 +25662,7 @@
       <c r="O557" t="inlineStr"/>
       <c r="P557" t="inlineStr"/>
       <c r="Q557" t="n">
-        <v>1</v>
+        <v>0.9861111111111112</v>
       </c>
     </row>
     <row r="558">
@@ -25707,7 +25707,7 @@
       <c r="O558" t="inlineStr"/>
       <c r="P558" t="inlineStr"/>
       <c r="Q558" t="n">
-        <v>0.9367088607594937</v>
+        <v>0.9451476793248946</v>
       </c>
     </row>
     <row r="559">
@@ -25795,7 +25795,7 @@
       </c>
       <c r="P560" t="inlineStr"/>
       <c r="Q560" t="n">
-        <v>0.8076923076923077</v>
+        <v>0.8205128205128205</v>
       </c>
     </row>
     <row r="561">
@@ -25938,7 +25938,7 @@
       </c>
       <c r="P563" t="inlineStr"/>
       <c r="Q563" t="n">
-        <v>1</v>
+        <v>1.007575757575758</v>
       </c>
     </row>
     <row r="564">
@@ -25987,7 +25987,7 @@
       </c>
       <c r="P564" t="inlineStr"/>
       <c r="Q564" t="n">
-        <v>1.041666666666667</v>
+        <v>1.027777777777778</v>
       </c>
     </row>
     <row r="565">
@@ -26093,7 +26093,7 @@
         <v>1.818181818181818</v>
       </c>
       <c r="Q566" t="n">
-        <v>0.96</v>
+        <v>0.9733333333333333</v>
       </c>
     </row>
     <row r="567">
@@ -26255,7 +26255,7 @@
       </c>
       <c r="P570" t="inlineStr"/>
       <c r="Q570" t="n">
-        <v>0.9411764705882353</v>
+        <v>1.156862745098039</v>
       </c>
     </row>
     <row r="571">
@@ -26308,7 +26308,7 @@
         <v>0.5925925925925926</v>
       </c>
       <c r="Q571" t="n">
-        <v>1.785714285714286</v>
+        <v>1.678571428571429</v>
       </c>
     </row>
     <row r="572">
@@ -26361,7 +26361,7 @@
         <v>0.4594594594594595</v>
       </c>
       <c r="Q572" t="n">
-        <v>0.8125</v>
+        <v>0.8055555555555555</v>
       </c>
     </row>
     <row r="573">
@@ -26414,7 +26414,7 @@
         <v>0.4857142857142857</v>
       </c>
       <c r="Q573" t="n">
-        <v>0.8936170212765957</v>
+        <v>0.9219858156028369</v>
       </c>
     </row>
     <row r="574">
@@ -26467,7 +26467,7 @@
         <v>0.3783783783783784</v>
       </c>
       <c r="Q574" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.6862745098039216</v>
       </c>
     </row>
     <row r="575">
@@ -26520,7 +26520,7 @@
         <v>0.4186046511627907</v>
       </c>
       <c r="Q575" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.9603174603174603</v>
       </c>
     </row>
     <row r="576">
@@ -26573,7 +26573,7 @@
         <v>0.3061224489795918</v>
       </c>
       <c r="Q576" t="n">
-        <v>1.037037037037037</v>
+        <v>1.04320987654321</v>
       </c>
     </row>
     <row r="577">
@@ -26622,7 +26622,7 @@
       <c r="O577" t="inlineStr"/>
       <c r="P577" t="inlineStr"/>
       <c r="Q577" t="n">
-        <v>0.8840579710144928</v>
+        <v>0.8792270531400966</v>
       </c>
     </row>
     <row r="578">
@@ -26669,7 +26669,7 @@
       <c r="O578" t="inlineStr"/>
       <c r="P578" t="inlineStr"/>
       <c r="Q578" t="n">
-        <v>0.7702702702702703</v>
+        <v>0.7747747747747747</v>
       </c>
     </row>
     <row r="579">
@@ -26759,7 +26759,7 @@
       <c r="O580" t="inlineStr"/>
       <c r="P580" t="inlineStr"/>
       <c r="Q580" t="n">
-        <v>0.8055555555555556</v>
+        <v>0.7870370370370371</v>
       </c>
     </row>
     <row r="581">
@@ -26804,7 +26804,7 @@
       <c r="O581" t="inlineStr"/>
       <c r="P581" t="inlineStr"/>
       <c r="Q581" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.888888888888889</v>
       </c>
     </row>
     <row r="582">
@@ -26849,7 +26849,7 @@
       <c r="O582" t="inlineStr"/>
       <c r="P582" t="inlineStr"/>
       <c r="Q582" t="n">
-        <v>0.9253731343283582</v>
+        <v>0.8905472636815921</v>
       </c>
     </row>
     <row r="583">
@@ -26937,7 +26937,7 @@
       </c>
       <c r="P584" t="inlineStr"/>
       <c r="Q584" t="n">
-        <v>0.9318181818181818</v>
+        <v>0.9393939393939394</v>
       </c>
     </row>
     <row r="585">
@@ -26990,7 +26990,7 @@
         <v>0.6153846153846154</v>
       </c>
       <c r="Q585" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9555555555555556</v>
       </c>
     </row>
     <row r="586">
@@ -27096,7 +27096,7 @@
         <v>1.055555555555556</v>
       </c>
       <c r="Q587" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.888888888888889</v>
       </c>
     </row>
     <row r="588">
@@ -27149,7 +27149,7 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="Q588" t="n">
-        <v>1.145833333333333</v>
+        <v>1.111111111111111</v>
       </c>
     </row>
     <row r="589">
@@ -27202,7 +27202,7 @@
         <v>0.59375</v>
       </c>
       <c r="Q589" t="n">
-        <v>0.819672131147541</v>
+        <v>0.8306010928961748</v>
       </c>
     </row>
     <row r="590">
@@ -27255,7 +27255,7 @@
         <v>0.5862068965517241</v>
       </c>
       <c r="Q590" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.896969696969697</v>
       </c>
     </row>
     <row r="591">
@@ -27308,7 +27308,7 @@
         <v>1</v>
       </c>
       <c r="Q591" t="n">
-        <v>0.9038461538461539</v>
+        <v>0.9358974358974359</v>
       </c>
     </row>
     <row r="592">
@@ -27361,7 +27361,7 @@
         <v>0.6363636363636364</v>
       </c>
       <c r="Q592" t="n">
-        <v>0.9824561403508771</v>
+        <v>0.9649122807017544</v>
       </c>
     </row>
     <row r="593">
@@ -27414,7 +27414,7 @@
         <v>0.4878048780487805</v>
       </c>
       <c r="Q593" t="n">
-        <v>0.8032786885245902</v>
+        <v>0.808743169398907</v>
       </c>
     </row>
     <row r="594">
@@ -27467,7 +27467,7 @@
         <v>0.3043478260869565</v>
       </c>
       <c r="Q594" t="n">
-        <v>0.9661016949152542</v>
+        <v>0.9435028248587571</v>
       </c>
     </row>
     <row r="595">
@@ -27520,7 +27520,7 @@
         <v>0.5454545454545454</v>
       </c>
       <c r="Q595" t="n">
-        <v>0.8840579710144928</v>
+        <v>0.927536231884058</v>
       </c>
     </row>
     <row r="596">
@@ -27573,7 +27573,7 @@
         <v>0.625</v>
       </c>
       <c r="Q596" t="n">
-        <v>1.028571428571428</v>
+        <v>0.9952380952380953</v>
       </c>
     </row>
     <row r="597">
@@ -27626,7 +27626,7 @@
         <v>0.7878787878787878</v>
       </c>
       <c r="Q597" t="n">
-        <v>0.875</v>
+        <v>0.9166666666666666</v>
       </c>
     </row>
     <row r="598">
@@ -27679,7 +27679,7 @@
         <v>0.5</v>
       </c>
       <c r="Q598" t="n">
-        <v>1</v>
+        <v>0.9571428571428572</v>
       </c>
     </row>
     <row r="599">
@@ -27732,7 +27732,7 @@
         <v>0.5</v>
       </c>
       <c r="Q599" t="n">
-        <v>0.9466666666666667</v>
+        <v>0.9422222222222223</v>
       </c>
     </row>
     <row r="600">
@@ -27785,7 +27785,7 @@
         <v>0.5102040816326531</v>
       </c>
       <c r="Q600" t="n">
-        <v>0.7738095238095238</v>
+        <v>0.7896825396825397</v>
       </c>
     </row>
     <row r="601">
@@ -27834,7 +27834,7 @@
       <c r="O601" t="inlineStr"/>
       <c r="P601" t="inlineStr"/>
       <c r="Q601" t="n">
-        <v>1.013157894736842</v>
+        <v>1.043859649122807</v>
       </c>
     </row>
     <row r="602">
@@ -27881,7 +27881,7 @@
       <c r="O602" t="inlineStr"/>
       <c r="P602" t="inlineStr"/>
       <c r="Q602" t="n">
-        <v>1.060975609756098</v>
+        <v>1.020325203252033</v>
       </c>
     </row>
     <row r="603">
@@ -27926,7 +27926,7 @@
       <c r="O603" t="inlineStr"/>
       <c r="P603" t="inlineStr"/>
       <c r="Q603" t="n">
-        <v>0.9550561797752809</v>
+        <v>0.9700374531835205</v>
       </c>
     </row>
     <row r="604">
@@ -28016,7 +28016,7 @@
       <c r="O605" t="inlineStr"/>
       <c r="P605" t="inlineStr"/>
       <c r="Q605" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8851851851851852</v>
       </c>
     </row>
     <row r="606">
@@ -28061,7 +28061,7 @@
       <c r="O606" t="inlineStr"/>
       <c r="P606" t="inlineStr"/>
       <c r="Q606" t="n">
-        <v>0.8734177215189873</v>
+        <v>0.8860759493670886</v>
       </c>
     </row>
     <row r="607">
@@ -28182,7 +28182,7 @@
       <c r="O609" t="inlineStr"/>
       <c r="P609" t="inlineStr"/>
       <c r="Q609" t="n">
-        <v>0.8928571428571429</v>
+        <v>0.8452380952380951</v>
       </c>
     </row>
     <row r="610">
@@ -28229,7 +28229,7 @@
       <c r="O610" t="inlineStr"/>
       <c r="P610" t="inlineStr"/>
       <c r="Q610" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7111111111111111</v>
       </c>
     </row>
     <row r="611">
@@ -28276,7 +28276,7 @@
       </c>
       <c r="P611" t="inlineStr"/>
       <c r="Q611" t="n">
-        <v>0.96875</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="612">
@@ -28325,7 +28325,7 @@
       </c>
       <c r="P612" t="inlineStr"/>
       <c r="Q612" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.8461538461538461</v>
       </c>
     </row>
     <row r="613">
@@ -28378,7 +28378,7 @@
         <v>0.6060606060606061</v>
       </c>
       <c r="Q613" t="n">
-        <v>1</v>
+        <v>0.9682539682539681</v>
       </c>
     </row>
     <row r="614">
@@ -28431,7 +28431,7 @@
         <v>0.6896551724137931</v>
       </c>
       <c r="Q614" t="n">
-        <v>0.8</v>
+        <v>0.837037037037037</v>
       </c>
     </row>
     <row r="615">
@@ -28593,7 +28593,7 @@
       </c>
       <c r="P618" t="inlineStr"/>
       <c r="Q618" t="n">
-        <v>1</v>
+        <v>1.006802721088435</v>
       </c>
     </row>
     <row r="619">
@@ -28646,7 +28646,7 @@
         <v>0.896551724137931</v>
       </c>
       <c r="Q619" t="n">
-        <v>0.9387755102040817</v>
+        <v>0.9183673469387755</v>
       </c>
     </row>
     <row r="620">
@@ -28699,7 +28699,7 @@
         <v>0.896551724137931</v>
       </c>
       <c r="Q620" t="n">
-        <v>1.019607843137255</v>
+        <v>1.032679738562091</v>
       </c>
     </row>
     <row r="621">
@@ -28752,7 +28752,7 @@
         <v>0.7272727272727273</v>
       </c>
       <c r="Q621" t="n">
-        <v>0.9821428571428571</v>
+        <v>0.9702380952380951</v>
       </c>
     </row>
     <row r="622">
@@ -28805,7 +28805,7 @@
         <v>0.6896551724137931</v>
       </c>
       <c r="Q622" t="n">
-        <v>0.8135593220338984</v>
+        <v>0.8248587570621468</v>
       </c>
     </row>
     <row r="623">
@@ -28858,7 +28858,7 @@
         <v>0.5384615384615384</v>
       </c>
       <c r="Q623" t="n">
-        <v>0.9423076923076923</v>
+        <v>0.9551282051282051</v>
       </c>
     </row>
     <row r="624">
@@ -28911,7 +28911,7 @@
         <v>0.6923076923076923</v>
       </c>
       <c r="Q624" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9027777777777778</v>
       </c>
     </row>
     <row r="625">
@@ -28960,7 +28960,7 @@
       <c r="O625" t="inlineStr"/>
       <c r="P625" t="inlineStr"/>
       <c r="Q625" t="n">
-        <v>0.8913043478260869</v>
+        <v>0.9130434782608695</v>
       </c>
     </row>
     <row r="626">
@@ -29007,7 +29007,7 @@
       <c r="O626" t="inlineStr"/>
       <c r="P626" t="inlineStr"/>
       <c r="Q626" t="n">
-        <v>1.075</v>
+        <v>1.066666666666667</v>
       </c>
     </row>
     <row r="627">
@@ -29052,7 +29052,7 @@
       <c r="O627" t="inlineStr"/>
       <c r="P627" t="inlineStr"/>
       <c r="Q627" t="n">
-        <v>1.021739130434783</v>
+        <v>0.9927536231884058</v>
       </c>
     </row>
     <row r="628">
@@ -29097,7 +29097,7 @@
       <c r="O628" t="inlineStr"/>
       <c r="P628" t="inlineStr"/>
       <c r="Q628" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.9652777777777778</v>
       </c>
     </row>
     <row r="629">
@@ -29142,7 +29142,7 @@
       <c r="O629" t="inlineStr"/>
       <c r="P629" t="inlineStr"/>
       <c r="Q629" t="n">
-        <v>1.0625</v>
+        <v>1.041666666666667</v>
       </c>
     </row>
     <row r="630">
@@ -29187,7 +29187,7 @@
       <c r="O630" t="inlineStr"/>
       <c r="P630" t="inlineStr"/>
       <c r="Q630" t="n">
-        <v>0.8627450980392157</v>
+        <v>0.9019607843137255</v>
       </c>
     </row>
     <row r="631">
@@ -29275,7 +29275,7 @@
       </c>
       <c r="P632" t="inlineStr"/>
       <c r="Q632" t="n">
-        <v>0.696969696969697</v>
+        <v>0.7171717171717172</v>
       </c>
     </row>
     <row r="633">
@@ -29324,7 +29324,7 @@
       <c r="O633" t="inlineStr"/>
       <c r="P633" t="inlineStr"/>
       <c r="Q633" t="n">
-        <v>1.03448275862069</v>
+        <v>1.011494252873563</v>
       </c>
     </row>
     <row r="634">
@@ -29371,7 +29371,7 @@
       <c r="O634" t="inlineStr"/>
       <c r="P634" t="inlineStr"/>
       <c r="Q634" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.803921568627451</v>
       </c>
     </row>
     <row r="635">
@@ -29467,7 +29467,7 @@
       </c>
       <c r="P636" t="inlineStr"/>
       <c r="Q636" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.9059829059829061</v>
       </c>
     </row>
     <row r="637">
@@ -29573,7 +29573,7 @@
         <v>0.5806451612903226</v>
       </c>
       <c r="Q638" t="n">
-        <v>0.875</v>
+        <v>0.8916666666666666</v>
       </c>
     </row>
     <row r="639">
@@ -29735,7 +29735,7 @@
       </c>
       <c r="P642" t="inlineStr"/>
       <c r="Q642" t="n">
-        <v>0.8813559322033898</v>
+        <v>0.8870056497175141</v>
       </c>
     </row>
     <row r="643">
@@ -29788,7 +29788,7 @@
         <v>0.5813953488372093</v>
       </c>
       <c r="Q643" t="n">
-        <v>0.9838709677419355</v>
+        <v>0.9892473118279569</v>
       </c>
     </row>
     <row r="644">
@@ -29841,7 +29841,7 @@
         <v>0.7352941176470589</v>
       </c>
       <c r="Q644" t="n">
-        <v>0.8840579710144928</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="645">
@@ -29894,7 +29894,7 @@
         <v>0.8064516129032258</v>
       </c>
       <c r="Q645" t="n">
-        <v>0.967741935483871</v>
+        <v>0.9569892473118279</v>
       </c>
     </row>
     <row r="646">
@@ -29947,7 +29947,7 @@
         <v>0.7419354838709677</v>
       </c>
       <c r="Q646" t="n">
-        <v>0.796875</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="647">
@@ -30000,7 +30000,7 @@
         <v>0.5294117647058824</v>
       </c>
       <c r="Q647" t="n">
-        <v>1</v>
+        <v>1.005649717514124</v>
       </c>
     </row>
     <row r="648">
@@ -30053,7 +30053,7 @@
         <v>0.5757575757575758</v>
       </c>
       <c r="Q648" t="n">
-        <v>1</v>
+        <v>0.9945355191256832</v>
       </c>
     </row>
     <row r="649">
@@ -30149,7 +30149,7 @@
       <c r="O650" t="inlineStr"/>
       <c r="P650" t="inlineStr"/>
       <c r="Q650" t="n">
-        <v>0.95</v>
+        <v>0.9555555555555555</v>
       </c>
     </row>
     <row r="651">
@@ -30194,7 +30194,7 @@
       <c r="O651" t="inlineStr"/>
       <c r="P651" t="inlineStr"/>
       <c r="Q651" t="n">
-        <v>1.03448275862069</v>
+        <v>1.028735632183908</v>
       </c>
     </row>
     <row r="652">
@@ -30239,7 +30239,7 @@
       <c r="O652" t="inlineStr"/>
       <c r="P652" t="inlineStr"/>
       <c r="Q652" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.872549019607843</v>
       </c>
     </row>
     <row r="653">
@@ -30284,7 +30284,7 @@
       <c r="O653" t="inlineStr"/>
       <c r="P653" t="inlineStr"/>
       <c r="Q653" t="n">
-        <v>1.014925373134328</v>
+        <v>1.004975124378109</v>
       </c>
     </row>
     <row r="654">
@@ -30329,7 +30329,7 @@
       <c r="O654" t="inlineStr"/>
       <c r="P654" t="inlineStr"/>
       <c r="Q654" t="n">
-        <v>0.8717948717948718</v>
+        <v>0.8931623931623932</v>
       </c>
     </row>
     <row r="655">
@@ -30411,7 +30411,7 @@
       <c r="O656" t="inlineStr"/>
       <c r="P656" t="inlineStr"/>
       <c r="Q656" t="n">
-        <v>0.9705882352941176</v>
+        <v>0.9640522875816993</v>
       </c>
     </row>
     <row r="657">
@@ -30456,7 +30456,7 @@
       <c r="O657" t="inlineStr"/>
       <c r="P657" t="inlineStr"/>
       <c r="Q657" t="n">
-        <v>0.8558558558558559</v>
+        <v>0.8588588588588588</v>
       </c>
     </row>
     <row r="658">
@@ -30501,7 +30501,7 @@
       <c r="O658" t="inlineStr"/>
       <c r="P658" t="inlineStr"/>
       <c r="Q658" t="n">
-        <v>0.970873786407767</v>
+        <v>0.9741100323624595</v>
       </c>
     </row>
     <row r="659">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="P680" t="inlineStr"/>
       <c r="Q680" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8383838383838383</v>
       </c>
     </row>
     <row r="681">
@@ -31140,7 +31140,7 @@
       <c r="O681" t="inlineStr"/>
       <c r="P681" t="inlineStr"/>
       <c r="Q681" t="n">
-        <v>1</v>
+        <v>0.9607843137254901</v>
       </c>
     </row>
     <row r="682">
@@ -31187,7 +31187,7 @@
       <c r="O682" t="inlineStr"/>
       <c r="P682" t="inlineStr"/>
       <c r="Q682" t="n">
-        <v>0.967741935483871</v>
+        <v>1</v>
       </c>
     </row>
     <row r="683">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="P683" t="inlineStr"/>
       <c r="Q683" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.9191919191919192</v>
       </c>
     </row>
     <row r="684">
@@ -31283,7 +31283,7 @@
       </c>
       <c r="P684" t="inlineStr"/>
       <c r="Q684" t="n">
-        <v>1.0625</v>
+        <v>1.020833333333333</v>
       </c>
     </row>
     <row r="685">
@@ -31336,7 +31336,7 @@
         <v>1</v>
       </c>
       <c r="Q685" t="n">
-        <v>1.28125</v>
+        <v>1.270833333333333</v>
       </c>
     </row>
     <row r="686">
@@ -31389,7 +31389,7 @@
         <v>0.75</v>
       </c>
       <c r="Q686" t="n">
-        <v>0.6829268292682927</v>
+        <v>0.6991869918699186</v>
       </c>
     </row>
     <row r="687">
@@ -31551,7 +31551,7 @@
       </c>
       <c r="P690" t="inlineStr"/>
       <c r="Q690" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7986111111111112</v>
       </c>
     </row>
     <row r="691">
@@ -31657,7 +31657,7 @@
         <v>0.3684210526315789</v>
       </c>
       <c r="Q692" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8205128205128205</v>
       </c>
     </row>
     <row r="693">
@@ -31710,7 +31710,7 @@
         <v>1.333333333333333</v>
       </c>
       <c r="Q693" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.7849462365591399</v>
       </c>
     </row>
     <row r="694">
@@ -31763,7 +31763,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="Q694" t="n">
-        <v>1.380952380952381</v>
+        <v>1.365079365079365</v>
       </c>
     </row>
     <row r="695">
@@ -31816,7 +31816,7 @@
         <v>0.24</v>
       </c>
       <c r="Q695" t="n">
-        <v>0.84375</v>
+        <v>0.8229166666666667</v>
       </c>
     </row>
     <row r="696">
@@ -31869,7 +31869,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="Q696" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="697">
@@ -31918,7 +31918,7 @@
       <c r="O697" t="inlineStr"/>
       <c r="P697" t="inlineStr"/>
       <c r="Q697" t="n">
-        <v>1.032258064516129</v>
+        <v>1.053763440860215</v>
       </c>
     </row>
     <row r="698">
@@ -32010,7 +32010,7 @@
       <c r="O699" t="inlineStr"/>
       <c r="P699" t="inlineStr"/>
       <c r="Q699" t="n">
-        <v>0.8490566037735849</v>
+        <v>0.8427672955974842</v>
       </c>
     </row>
     <row r="700">
@@ -32055,7 +32055,7 @@
       <c r="O700" t="inlineStr"/>
       <c r="P700" t="inlineStr"/>
       <c r="Q700" t="n">
-        <v>0.9387755102040817</v>
+        <v>0.9251700680272109</v>
       </c>
     </row>
     <row r="701">
@@ -32100,7 +32100,7 @@
       <c r="O701" t="inlineStr"/>
       <c r="P701" t="inlineStr"/>
       <c r="Q701" t="n">
-        <v>0.8035714285714286</v>
+        <v>0.8273809523809524</v>
       </c>
     </row>
     <row r="702">
@@ -32145,7 +32145,7 @@
       <c r="O702" t="inlineStr"/>
       <c r="P702" t="inlineStr"/>
       <c r="Q702" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.924731182795699</v>
       </c>
     </row>
     <row r="703">
@@ -32233,7 +32233,7 @@
       </c>
       <c r="P704" t="inlineStr"/>
       <c r="Q704" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8383838383838383</v>
       </c>
     </row>
     <row r="705">
@@ -32282,7 +32282,7 @@
       <c r="O705" t="inlineStr"/>
       <c r="P705" t="inlineStr"/>
       <c r="Q705" t="n">
-        <v>1</v>
+        <v>0.9607843137254901</v>
       </c>
     </row>
     <row r="706">
@@ -32329,7 +32329,7 @@
       <c r="O706" t="inlineStr"/>
       <c r="P706" t="inlineStr"/>
       <c r="Q706" t="n">
-        <v>0.967741935483871</v>
+        <v>1</v>
       </c>
     </row>
     <row r="707">
@@ -32376,7 +32376,7 @@
       </c>
       <c r="P707" t="inlineStr"/>
       <c r="Q707" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.9191919191919192</v>
       </c>
     </row>
     <row r="708">
@@ -32425,7 +32425,7 @@
       </c>
       <c r="P708" t="inlineStr"/>
       <c r="Q708" t="n">
-        <v>1.0625</v>
+        <v>1.020833333333333</v>
       </c>
     </row>
     <row r="709">
@@ -32478,7 +32478,7 @@
         <v>1</v>
       </c>
       <c r="Q709" t="n">
-        <v>1.28125</v>
+        <v>1.270833333333333</v>
       </c>
     </row>
     <row r="710">
@@ -32531,7 +32531,7 @@
         <v>0.75</v>
       </c>
       <c r="Q710" t="n">
-        <v>0.6829268292682927</v>
+        <v>0.6991869918699186</v>
       </c>
     </row>
     <row r="711">
@@ -32693,7 +32693,7 @@
       </c>
       <c r="P714" t="inlineStr"/>
       <c r="Q714" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.7986111111111112</v>
       </c>
     </row>
     <row r="715">
@@ -32799,7 +32799,7 @@
         <v>0.3684210526315789</v>
       </c>
       <c r="Q716" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8205128205128205</v>
       </c>
     </row>
     <row r="717">
@@ -32852,7 +32852,7 @@
         <v>1.333333333333333</v>
       </c>
       <c r="Q717" t="n">
-        <v>0.7419354838709677</v>
+        <v>0.7849462365591399</v>
       </c>
     </row>
     <row r="718">
@@ -32905,7 +32905,7 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="Q718" t="n">
-        <v>1.380952380952381</v>
+        <v>1.365079365079365</v>
       </c>
     </row>
     <row r="719">
@@ -32958,7 +32958,7 @@
         <v>0.24</v>
       </c>
       <c r="Q719" t="n">
-        <v>0.84375</v>
+        <v>0.8229166666666667</v>
       </c>
     </row>
     <row r="720">
@@ -33011,7 +33011,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="Q720" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="721">
@@ -33060,7 +33060,7 @@
       <c r="O721" t="inlineStr"/>
       <c r="P721" t="inlineStr"/>
       <c r="Q721" t="n">
-        <v>1.032258064516129</v>
+        <v>1.053763440860215</v>
       </c>
     </row>
     <row r="722">
@@ -33152,7 +33152,7 @@
       <c r="O723" t="inlineStr"/>
       <c r="P723" t="inlineStr"/>
       <c r="Q723" t="n">
-        <v>0.8490566037735849</v>
+        <v>0.8427672955974842</v>
       </c>
     </row>
     <row r="724">
@@ -33197,7 +33197,7 @@
       <c r="O724" t="inlineStr"/>
       <c r="P724" t="inlineStr"/>
       <c r="Q724" t="n">
-        <v>0.9387755102040817</v>
+        <v>0.9251700680272109</v>
       </c>
     </row>
     <row r="725">
@@ -33242,7 +33242,7 @@
       <c r="O725" t="inlineStr"/>
       <c r="P725" t="inlineStr"/>
       <c r="Q725" t="n">
-        <v>0.8035714285714286</v>
+        <v>0.8273809523809524</v>
       </c>
     </row>
     <row r="726">
@@ -33287,7 +33287,7 @@
       <c r="O726" t="inlineStr"/>
       <c r="P726" t="inlineStr"/>
       <c r="Q726" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.924731182795699</v>
       </c>
     </row>
     <row r="727">
@@ -33975,7 +33975,7 @@
       </c>
       <c r="P752" t="inlineStr"/>
       <c r="Q752" t="n">
-        <v>0.948051948051948</v>
+        <v>0.9264069264069263</v>
       </c>
     </row>
     <row r="753">
@@ -34024,7 +34024,7 @@
       <c r="O753" t="inlineStr"/>
       <c r="P753" t="inlineStr"/>
       <c r="Q753" t="n">
-        <v>0.9176470588235294</v>
+        <v>0.9372549019607843</v>
       </c>
     </row>
     <row r="754">
@@ -34071,7 +34071,7 @@
       <c r="O754" t="inlineStr"/>
       <c r="P754" t="inlineStr"/>
       <c r="Q754" t="n">
-        <v>0.9832402234636871</v>
+        <v>0.9739292364990689</v>
       </c>
     </row>
     <row r="755">
@@ -34220,7 +34220,7 @@
         <v>0.9090909090909091</v>
       </c>
       <c r="Q757" t="n">
-        <v>0.9096045197740112</v>
+        <v>0.9227871939736347</v>
       </c>
     </row>
     <row r="758">
@@ -34273,7 +34273,7 @@
         <v>0.9047619047619048</v>
       </c>
       <c r="Q758" t="n">
-        <v>0.9421965317919075</v>
+        <v>0.9499036608863199</v>
       </c>
     </row>
     <row r="759">
@@ -34435,7 +34435,7 @@
       </c>
       <c r="P762" t="inlineStr"/>
       <c r="Q762" t="n">
-        <v>0.9805194805194806</v>
+        <v>0.9783549783549783</v>
       </c>
     </row>
     <row r="763">
@@ -34488,7 +34488,7 @@
         <v>0.8117647058823529</v>
       </c>
       <c r="Q763" t="n">
-        <v>0.9814814814814815</v>
+        <v>0.9753086419753086</v>
       </c>
     </row>
     <row r="764">
@@ -34541,7 +34541,7 @@
         <v>0.7578947368421053</v>
       </c>
       <c r="Q764" t="n">
-        <v>0.927710843373494</v>
+        <v>0.9477911646586346</v>
       </c>
     </row>
     <row r="765">
@@ -34594,7 +34594,7 @@
         <v>0.8222222222222222</v>
       </c>
       <c r="Q765" t="n">
-        <v>1.031055900621118</v>
+        <v>1.020703933747412</v>
       </c>
     </row>
     <row r="766">
@@ -34647,7 +34647,7 @@
         <v>0.8961038961038961</v>
       </c>
       <c r="Q766" t="n">
-        <v>0.9578313253012049</v>
+        <v>0.9437751004016064</v>
       </c>
     </row>
     <row r="767">
@@ -34700,7 +34700,7 @@
         <v>0.8831168831168831</v>
       </c>
       <c r="Q767" t="n">
-        <v>0.9933774834437086</v>
+        <v>0.9977924944812362</v>
       </c>
     </row>
     <row r="768">
@@ -34753,7 +34753,7 @@
         <v>0.935064935064935</v>
       </c>
       <c r="Q768" t="n">
-        <v>0.949685534591195</v>
+        <v>0.9538784067085954</v>
       </c>
     </row>
     <row r="769">
@@ -34802,7 +34802,7 @@
       <c r="O769" t="inlineStr"/>
       <c r="P769" t="inlineStr"/>
       <c r="Q769" t="n">
-        <v>0.9751552795031055</v>
+        <v>0.9792960662525879</v>
       </c>
     </row>
     <row r="770">
@@ -34849,7 +34849,7 @@
       <c r="O770" t="inlineStr"/>
       <c r="P770" t="inlineStr"/>
       <c r="Q770" t="n">
-        <v>1.025</v>
+        <v>1.022916666666667</v>
       </c>
     </row>
     <row r="771">
@@ -34894,7 +34894,7 @@
       <c r="O771" t="inlineStr"/>
       <c r="P771" t="inlineStr"/>
       <c r="Q771" t="n">
-        <v>0.9753086419753086</v>
+        <v>0.977366255144033</v>
       </c>
     </row>
     <row r="772">
@@ -34939,7 +34939,7 @@
       <c r="O772" t="inlineStr"/>
       <c r="P772" t="inlineStr"/>
       <c r="Q772" t="n">
-        <v>1.105263157894737</v>
+        <v>1.094298245614035</v>
       </c>
     </row>
     <row r="773">
@@ -34984,7 +34984,7 @@
       <c r="O773" t="inlineStr"/>
       <c r="P773" t="inlineStr"/>
       <c r="Q773" t="n">
-        <v>0.9202453987730062</v>
+        <v>0.9263803680981595</v>
       </c>
     </row>
     <row r="774">
@@ -35029,7 +35029,7 @@
       <c r="O774" t="inlineStr"/>
       <c r="P774" t="inlineStr"/>
       <c r="Q774" t="n">
-        <v>1.018987341772152</v>
+        <v>1.031645569620253</v>
       </c>
     </row>
     <row r="775">
@@ -35117,7 +35117,7 @@
       </c>
       <c r="P776" t="inlineStr"/>
       <c r="Q776" t="n">
-        <v>0.9791666666666666</v>
+        <v>0.9861111111111112</v>
       </c>
     </row>
     <row r="777">
@@ -35166,7 +35166,7 @@
       <c r="O777" t="inlineStr"/>
       <c r="P777" t="inlineStr"/>
       <c r="Q777" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="778">
@@ -35213,7 +35213,7 @@
       <c r="O778" t="inlineStr"/>
       <c r="P778" t="inlineStr"/>
       <c r="Q778" t="n">
-        <v>0.8163265306122449</v>
+        <v>0.8299319727891156</v>
       </c>
     </row>
     <row r="779">
@@ -35260,7 +35260,7 @@
       </c>
       <c r="P779" t="inlineStr"/>
       <c r="Q779" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.9791666666666666</v>
       </c>
     </row>
     <row r="780">
@@ -35309,7 +35309,7 @@
       </c>
       <c r="P780" t="inlineStr"/>
       <c r="Q780" t="n">
-        <v>0.9076923076923077</v>
+        <v>0.8923076923076924</v>
       </c>
     </row>
     <row r="781">
@@ -35415,7 +35415,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="Q782" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.8201058201058202</v>
       </c>
     </row>
     <row r="783">
@@ -35577,7 +35577,7 @@
       </c>
       <c r="P786" t="inlineStr"/>
       <c r="Q786" t="n">
-        <v>1.117647058823529</v>
+        <v>1.143790849673203</v>
       </c>
     </row>
     <row r="787">
@@ -35630,7 +35630,7 @@
         <v>0.6</v>
       </c>
       <c r="Q787" t="n">
-        <v>1.016129032258065</v>
+        <v>0.9838709677419355</v>
       </c>
     </row>
     <row r="788">
@@ -35683,7 +35683,7 @@
         <v>0.4390243902439024</v>
       </c>
       <c r="Q788" t="n">
-        <v>0.7924528301886793</v>
+        <v>0.779874213836478</v>
       </c>
     </row>
     <row r="789">
@@ -35736,7 +35736,7 @@
         <v>0.5675675675675675</v>
       </c>
       <c r="Q789" t="n">
-        <v>0.8392857142857143</v>
+        <v>0.869047619047619</v>
       </c>
     </row>
     <row r="790">
@@ -35789,7 +35789,7 @@
         <v>0.4418604651162791</v>
       </c>
       <c r="Q790" t="n">
-        <v>0.9423076923076923</v>
+        <v>0.9294871794871794</v>
       </c>
     </row>
     <row r="791">
@@ -35842,7 +35842,7 @@
         <v>0.5625</v>
       </c>
       <c r="Q791" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="792">
@@ -36036,7 +36036,7 @@
       <c r="O795" t="inlineStr"/>
       <c r="P795" t="inlineStr"/>
       <c r="Q795" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.9761904761904762</v>
       </c>
     </row>
     <row r="796">
@@ -36081,7 +36081,7 @@
       <c r="O796" t="inlineStr"/>
       <c r="P796" t="inlineStr"/>
       <c r="Q796" t="n">
-        <v>1</v>
+        <v>0.9603174603174603</v>
       </c>
     </row>
     <row r="797">
@@ -36126,7 +36126,7 @@
       <c r="O797" t="inlineStr"/>
       <c r="P797" t="inlineStr"/>
       <c r="Q797" t="n">
-        <v>0.7804878048780488</v>
+        <v>0.7886178861788619</v>
       </c>
     </row>
     <row r="798">
@@ -36859,7 +36859,7 @@
       </c>
       <c r="P824" t="inlineStr"/>
       <c r="Q824" t="n">
-        <v>0.9425287356321839</v>
+        <v>0.9367816091954023</v>
       </c>
     </row>
     <row r="825">
@@ -36980,7 +36980,7 @@
       </c>
       <c r="P827" t="inlineStr"/>
       <c r="Q827" t="n">
-        <v>0.9647058823529412</v>
+        <v>0.9784313725490197</v>
       </c>
     </row>
     <row r="828">
@@ -37029,7 +37029,7 @@
       </c>
       <c r="P828" t="inlineStr"/>
       <c r="Q828" t="n">
-        <v>1.043010752688172</v>
+        <v>1.026881720430108</v>
       </c>
     </row>
     <row r="829">
@@ -37082,7 +37082,7 @@
         <v>0.73</v>
       </c>
       <c r="Q829" t="n">
-        <v>0.9278350515463918</v>
+        <v>0.9072164948453608</v>
       </c>
     </row>
     <row r="830">
@@ -37135,7 +37135,7 @@
         <v>0.8674698795180723</v>
       </c>
       <c r="Q830" t="n">
-        <v>0.9171270718232044</v>
+        <v>0.9539594843462246</v>
       </c>
     </row>
     <row r="831">
@@ -37350,7 +37350,7 @@
         <v>0.5963302752293578</v>
       </c>
       <c r="Q835" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.9365079365079365</v>
       </c>
     </row>
     <row r="836">
@@ -37403,7 +37403,7 @@
         <v>0.6354166666666666</v>
       </c>
       <c r="Q836" t="n">
-        <v>0.9766081871345029</v>
+        <v>0.9610136452241715</v>
       </c>
     </row>
     <row r="837">
@@ -37456,7 +37456,7 @@
         <v>0.5384615384615384</v>
       </c>
       <c r="Q837" t="n">
-        <v>0.9289940828402367</v>
+        <v>0.9329388560157791</v>
       </c>
     </row>
     <row r="838">
@@ -37509,7 +37509,7 @@
         <v>0.5</v>
       </c>
       <c r="Q838" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9395711500974658</v>
       </c>
     </row>
     <row r="839">
@@ -37562,7 +37562,7 @@
         <v>0.5583333333333333</v>
       </c>
       <c r="Q839" t="n">
-        <v>0.837696335078534</v>
+        <v>0.8516579406631762</v>
       </c>
     </row>
     <row r="840">
@@ -37615,7 +37615,7 @@
         <v>0.4822695035460993</v>
       </c>
       <c r="Q840" t="n">
-        <v>0.9770114942528736</v>
+        <v>0.9693486590038314</v>
       </c>
     </row>
     <row r="841">
@@ -37664,7 +37664,7 @@
       <c r="O841" t="inlineStr"/>
       <c r="P841" t="inlineStr"/>
       <c r="Q841" t="n">
-        <v>0.8844221105527639</v>
+        <v>0.8710217755443886</v>
       </c>
     </row>
     <row r="842">
@@ -37711,7 +37711,7 @@
       <c r="O842" t="inlineStr"/>
       <c r="P842" t="inlineStr"/>
       <c r="Q842" t="n">
-        <v>0.897196261682243</v>
+        <v>0.9096573208722741</v>
       </c>
     </row>
     <row r="843">
@@ -37756,7 +37756,7 @@
       <c r="O843" t="inlineStr"/>
       <c r="P843" t="inlineStr"/>
       <c r="Q843" t="n">
-        <v>0.8836206896551724</v>
+        <v>0.8764367816091955</v>
       </c>
     </row>
     <row r="844">
@@ -37846,7 +37846,7 @@
       <c r="O845" t="inlineStr"/>
       <c r="P845" t="inlineStr"/>
       <c r="Q845" t="n">
-        <v>0.9136363636363637</v>
+        <v>0.9333333333333333</v>
       </c>
     </row>
     <row r="846">
@@ -37891,7 +37891,7 @@
       <c r="O846" t="inlineStr"/>
       <c r="P846" t="inlineStr"/>
       <c r="Q846" t="n">
-        <v>0.9783549783549783</v>
+        <v>0.961038961038961</v>
       </c>
     </row>
     <row r="847">
@@ -38579,7 +38579,7 @@
       </c>
       <c r="P872" t="inlineStr"/>
       <c r="Q872" t="n">
-        <v>0.896551724137931</v>
+        <v>0.8850574712643677</v>
       </c>
     </row>
     <row r="873">
@@ -38628,7 +38628,7 @@
       <c r="O873" t="inlineStr"/>
       <c r="P873" t="inlineStr"/>
       <c r="Q873" t="n">
-        <v>0.8484848484848485</v>
+        <v>0.8636363636363636</v>
       </c>
     </row>
     <row r="874">
@@ -38722,7 +38722,7 @@
       </c>
       <c r="P875" t="inlineStr"/>
       <c r="Q875" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.8970588235294118</v>
       </c>
     </row>
     <row r="876">
@@ -38771,7 +38771,7 @@
       </c>
       <c r="P876" t="inlineStr"/>
       <c r="Q876" t="n">
-        <v>1.046153846153846</v>
+        <v>1.030769230769231</v>
       </c>
     </row>
     <row r="877">
@@ -38877,7 +38877,7 @@
         <v>0.7555555555555555</v>
       </c>
       <c r="Q878" t="n">
-        <v>1</v>
+        <v>1.013157894736842</v>
       </c>
     </row>
     <row r="879">
@@ -39039,7 +39039,7 @@
       </c>
       <c r="P882" t="inlineStr"/>
       <c r="Q882" t="n">
-        <v>0.8865979381443299</v>
+        <v>0.8934707903780069</v>
       </c>
     </row>
     <row r="883">
@@ -39092,7 +39092,7 @@
         <v>0.8837209302325582</v>
       </c>
       <c r="Q883" t="n">
-        <v>0.8876404494382022</v>
+        <v>0.8951310861423222</v>
       </c>
     </row>
     <row r="884">
@@ -39198,7 +39198,7 @@
         <v>0.9047619047619048</v>
       </c>
       <c r="Q885" t="n">
-        <v>1.012987012987013</v>
+        <v>1.008658008658009</v>
       </c>
     </row>
     <row r="886">
@@ -39251,7 +39251,7 @@
         <v>0.8974358974358975</v>
       </c>
       <c r="Q886" t="n">
-        <v>1.037974683544304</v>
+        <v>1.021097046413502</v>
       </c>
     </row>
     <row r="887">
@@ -39304,7 +39304,7 @@
         <v>0.8461538461538461</v>
       </c>
       <c r="Q887" t="n">
-        <v>0.8674698795180723</v>
+        <v>0.8995983935742973</v>
       </c>
     </row>
     <row r="888">
@@ -39357,7 +39357,7 @@
         <v>0.6585365853658537</v>
       </c>
       <c r="Q888" t="n">
-        <v>1.012658227848101</v>
+        <v>1.0042194092827</v>
       </c>
     </row>
     <row r="889">
@@ -39406,7 +39406,7 @@
       <c r="O889" t="inlineStr"/>
       <c r="P889" t="inlineStr"/>
       <c r="Q889" t="n">
-        <v>1</v>
+        <v>0.9875</v>
       </c>
     </row>
     <row r="890">
@@ -39455,7 +39455,7 @@
       <c r="O890" t="inlineStr"/>
       <c r="P890" t="inlineStr"/>
       <c r="Q890" t="n">
-        <v>1</v>
+        <v>0.9875</v>
       </c>
     </row>
     <row r="891">
@@ -39502,7 +39502,7 @@
       <c r="O891" t="inlineStr"/>
       <c r="P891" t="inlineStr"/>
       <c r="Q891" t="n">
-        <v>0.9342105263157895</v>
+        <v>0.9385964912280701</v>
       </c>
     </row>
     <row r="892">
@@ -39547,7 +39547,7 @@
       <c r="O892" t="inlineStr"/>
       <c r="P892" t="inlineStr"/>
       <c r="Q892" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.9772727272727273</v>
       </c>
     </row>
     <row r="893">
@@ -39592,7 +39592,7 @@
       <c r="O893" t="inlineStr"/>
       <c r="P893" t="inlineStr"/>
       <c r="Q893" t="n">
-        <v>1.121951219512195</v>
+        <v>1.08130081300813</v>
       </c>
     </row>
     <row r="894">
@@ -39637,7 +39637,7 @@
       <c r="O894" t="inlineStr"/>
       <c r="P894" t="inlineStr"/>
       <c r="Q894" t="n">
-        <v>1</v>
+        <v>1.007662835249042</v>
       </c>
     </row>
     <row r="895">
@@ -39682,7 +39682,7 @@
       <c r="O895" t="inlineStr"/>
       <c r="P895" t="inlineStr"/>
       <c r="Q895" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8639455782312926</v>
       </c>
     </row>
     <row r="896">
@@ -39891,7 +39891,7 @@
       </c>
       <c r="P900" t="inlineStr"/>
       <c r="Q900" t="n">
-        <v>0.875</v>
+        <v>0.9027777777777778</v>
       </c>
     </row>
     <row r="901">
@@ -39993,7 +39993,7 @@
         <v>1</v>
       </c>
       <c r="Q902" t="n">
-        <v>1.1875</v>
+        <v>1.083333333333333</v>
       </c>
     </row>
     <row r="903">
@@ -40046,7 +40046,7 @@
         <v>1.181818181818182</v>
       </c>
       <c r="Q903" t="n">
-        <v>0.9</v>
+        <v>0.9666666666666666</v>
       </c>
     </row>
     <row r="904">
@@ -40208,7 +40208,7 @@
       </c>
       <c r="P907" t="inlineStr"/>
       <c r="Q907" t="n">
-        <v>0.9</v>
+        <v>0.8916666666666666</v>
       </c>
     </row>
     <row r="908">
@@ -40261,7 +40261,7 @@
         <v>1.2</v>
       </c>
       <c r="Q908" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8431372549019607</v>
       </c>
     </row>
     <row r="909">
@@ -40367,7 +40367,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="Q910" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9126984126984128</v>
       </c>
     </row>
     <row r="911">
@@ -40420,7 +40420,7 @@
         <v>0.6470588235294118</v>
       </c>
       <c r="Q911" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.925925925925926</v>
       </c>
     </row>
     <row r="912">
@@ -40473,7 +40473,7 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="Q912" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9142857142857143</v>
       </c>
     </row>
     <row r="913">
@@ -40526,7 +40526,7 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="Q913" t="n">
-        <v>1.033333333333333</v>
+        <v>1.022222222222222</v>
       </c>
     </row>
     <row r="914">
@@ -40575,7 +40575,7 @@
       <c r="O914" t="inlineStr"/>
       <c r="P914" t="inlineStr"/>
       <c r="Q914" t="n">
-        <v>0.9629629629629629</v>
+        <v>0.9135802469135802</v>
       </c>
     </row>
     <row r="915">
@@ -40622,7 +40622,7 @@
       <c r="O915" t="inlineStr"/>
       <c r="P915" t="inlineStr"/>
       <c r="Q915" t="n">
-        <v>1.115384615384615</v>
+        <v>1.102564102564102</v>
       </c>
     </row>
     <row r="916">
@@ -40667,7 +40667,7 @@
       <c r="O916" t="inlineStr"/>
       <c r="P916" t="inlineStr"/>
       <c r="Q916" t="n">
-        <v>1.103448275862069</v>
+        <v>1.068965517241379</v>
       </c>
     </row>
     <row r="917">
@@ -40712,7 +40712,7 @@
       <c r="O917" t="inlineStr"/>
       <c r="P917" t="inlineStr"/>
       <c r="Q917" t="n">
-        <v>0.78125</v>
+        <v>0.8333333333333333</v>
       </c>
     </row>
     <row r="918">
@@ -40757,7 +40757,7 @@
       <c r="O918" t="inlineStr"/>
       <c r="P918" t="inlineStr"/>
       <c r="Q918" t="n">
-        <v>1.166666666666667</v>
+        <v>1.133333333333333</v>
       </c>
     </row>
     <row r="919">
@@ -40802,7 +40802,7 @@
       <c r="O919" t="inlineStr"/>
       <c r="P919" t="inlineStr"/>
       <c r="Q919" t="n">
-        <v>0.918918918918919</v>
+        <v>0.927927927927928</v>
       </c>
     </row>
     <row r="920">
@@ -41232,7 +41232,7 @@
       </c>
       <c r="P931" t="inlineStr"/>
       <c r="Q931" t="n">
-        <v>0.875</v>
+        <v>0.8333333333333333</v>
       </c>
     </row>
     <row r="932">
@@ -41285,7 +41285,7 @@
         <v>1</v>
       </c>
       <c r="Q932" t="n">
-        <v>0.75</v>
+        <v>0.8333333333333333</v>
       </c>
     </row>
     <row r="933">
@@ -41338,7 +41338,7 @@
         <v>1</v>
       </c>
       <c r="Q933" t="n">
-        <v>1.1</v>
+        <v>1.066666666666667</v>
       </c>
     </row>
     <row r="934">
@@ -41444,7 +41444,7 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="Q935" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.7948717948717949</v>
       </c>
     </row>
     <row r="936">
@@ -41497,7 +41497,7 @@
         <v>0.5</v>
       </c>
       <c r="Q936" t="n">
-        <v>1</v>
+        <v>0.9743589743589743</v>
       </c>
     </row>
     <row r="937">
@@ -41550,7 +41550,7 @@
         <v>0.375</v>
       </c>
       <c r="Q937" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8484848484848485</v>
       </c>
     </row>
     <row r="938">
@@ -41599,7 +41599,7 @@
       <c r="O938" t="inlineStr"/>
       <c r="P938" t="inlineStr"/>
       <c r="Q938" t="n">
-        <v>0.75</v>
+        <v>0.8055555555555555</v>
       </c>
     </row>
     <row r="939">
@@ -41646,7 +41646,7 @@
       <c r="O939" t="inlineStr"/>
       <c r="P939" t="inlineStr"/>
       <c r="Q939" t="n">
-        <v>1</v>
+        <v>0.9629629629629629</v>
       </c>
     </row>
     <row r="940">
@@ -41691,7 +41691,7 @@
       <c r="O940" t="inlineStr"/>
       <c r="P940" t="inlineStr"/>
       <c r="Q940" t="n">
-        <v>1.333333333333333</v>
+        <v>1.222222222222222</v>
       </c>
     </row>
     <row r="941">
@@ -41914,7 +41914,7 @@
       </c>
       <c r="P945" t="inlineStr"/>
       <c r="Q945" t="n">
-        <v>0.875</v>
+        <v>0.8690476190476192</v>
       </c>
     </row>
     <row r="946">
@@ -41963,7 +41963,7 @@
       <c r="O946" t="inlineStr"/>
       <c r="P946" t="inlineStr"/>
       <c r="Q946" t="n">
-        <v>0.9344262295081968</v>
+        <v>0.9289617486338798</v>
       </c>
     </row>
     <row r="947">
@@ -42010,7 +42010,7 @@
       <c r="O947" t="inlineStr"/>
       <c r="P947" t="inlineStr"/>
       <c r="Q947" t="n">
-        <v>0.9206349206349206</v>
+        <v>0.9259259259259258</v>
       </c>
     </row>
     <row r="948">
@@ -42057,7 +42057,7 @@
       </c>
       <c r="P948" t="inlineStr"/>
       <c r="Q948" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.8737373737373738</v>
       </c>
     </row>
     <row r="949">
@@ -42106,7 +42106,7 @@
       </c>
       <c r="P949" t="inlineStr"/>
       <c r="Q949" t="n">
-        <v>0.7538461538461538</v>
+        <v>0.7794871794871795</v>
       </c>
     </row>
     <row r="950">
@@ -42159,7 +42159,7 @@
         <v>0.5454545454545454</v>
       </c>
       <c r="Q950" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.8641975308641975</v>
       </c>
     </row>
     <row r="951">
@@ -42212,7 +42212,7 @@
         <v>0.5</v>
       </c>
       <c r="Q951" t="n">
-        <v>0.8627450980392157</v>
+        <v>0.869281045751634</v>
       </c>
     </row>
     <row r="952">
@@ -42374,7 +42374,7 @@
       </c>
       <c r="P955" t="inlineStr"/>
       <c r="Q955" t="n">
-        <v>0.9818181818181818</v>
+        <v>0.9515151515151514</v>
       </c>
     </row>
     <row r="956">
@@ -42427,7 +42427,7 @@
         <v>0.6388888888888888</v>
       </c>
       <c r="Q956" t="n">
-        <v>0.8</v>
+        <v>0.8222222222222222</v>
       </c>
     </row>
     <row r="957">
@@ -42480,7 +42480,7 @@
         <v>0.5675675675675675</v>
       </c>
       <c r="Q957" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8555555555555556</v>
       </c>
     </row>
     <row r="958">
@@ -42533,7 +42533,7 @@
         <v>0.4210526315789473</v>
       </c>
       <c r="Q958" t="n">
-        <v>0.8867924528301887</v>
+        <v>0.8930817610062893</v>
       </c>
     </row>
     <row r="959">
@@ -42586,7 +42586,7 @@
         <v>0.6451612903225806</v>
       </c>
       <c r="Q959" t="n">
-        <v>0.9122807017543859</v>
+        <v>0.8771929824561403</v>
       </c>
     </row>
     <row r="960">
@@ -42639,7 +42639,7 @@
         <v>0.4705882352941176</v>
       </c>
       <c r="Q960" t="n">
-        <v>0.6851851851851852</v>
+        <v>0.7592592592592593</v>
       </c>
     </row>
     <row r="961">
@@ -42692,7 +42692,7 @@
         <v>0.4</v>
       </c>
       <c r="Q961" t="n">
-        <v>1.145833333333333</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="962">
@@ -42741,7 +42741,7 @@
       <c r="O962" t="inlineStr"/>
       <c r="P962" t="inlineStr"/>
       <c r="Q962" t="n">
-        <v>0.7966101694915254</v>
+        <v>0.7570621468926553</v>
       </c>
     </row>
     <row r="963">
@@ -42788,7 +42788,7 @@
       <c r="O963" t="inlineStr"/>
       <c r="P963" t="inlineStr"/>
       <c r="Q963" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.8226950354609929</v>
       </c>
     </row>
     <row r="964">
@@ -42833,7 +42833,7 @@
       <c r="O964" t="inlineStr"/>
       <c r="P964" t="inlineStr"/>
       <c r="Q964" t="n">
-        <v>1.105263157894737</v>
+        <v>1.052631578947368</v>
       </c>
     </row>
     <row r="965">
@@ -42878,7 +42878,7 @@
       <c r="O965" t="inlineStr"/>
       <c r="P965" t="inlineStr"/>
       <c r="Q965" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9206349206349206</v>
       </c>
     </row>
     <row r="966">
@@ -42968,7 +42968,7 @@
       <c r="O967" t="inlineStr"/>
       <c r="P967" t="inlineStr"/>
       <c r="Q967" t="n">
-        <v>0.9591836734693877</v>
+        <v>0.9319727891156462</v>
       </c>
     </row>
     <row r="968">
@@ -43056,7 +43056,7 @@
       </c>
       <c r="P969" t="inlineStr"/>
       <c r="Q969" t="n">
-        <v>0.8441558441558441</v>
+        <v>0.8484848484848484</v>
       </c>
     </row>
     <row r="970">
@@ -43105,7 +43105,7 @@
       <c r="O970" t="inlineStr"/>
       <c r="P970" t="inlineStr"/>
       <c r="Q970" t="n">
-        <v>0.9375</v>
+        <v>0.9583333333333334</v>
       </c>
     </row>
     <row r="971">
@@ -43152,7 +43152,7 @@
       <c r="O971" t="inlineStr"/>
       <c r="P971" t="inlineStr"/>
       <c r="Q971" t="n">
-        <v>0.9302325581395349</v>
+        <v>0.9031007751937985</v>
       </c>
     </row>
     <row r="972">
@@ -43199,7 +43199,7 @@
       </c>
       <c r="P972" t="inlineStr"/>
       <c r="Q972" t="n">
-        <v>0.9493670886075949</v>
+        <v>0.9704641350210971</v>
       </c>
     </row>
     <row r="973">
@@ -43248,7 +43248,7 @@
       </c>
       <c r="P973" t="inlineStr"/>
       <c r="Q973" t="n">
-        <v>1.035294117647059</v>
+        <v>1.019607843137255</v>
       </c>
     </row>
     <row r="974">
@@ -43301,7 +43301,7 @@
         <v>0.7666666666666667</v>
       </c>
       <c r="Q974" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9372549019607843</v>
       </c>
     </row>
     <row r="975">
@@ -43354,7 +43354,7 @@
         <v>0.4375</v>
       </c>
       <c r="Q975" t="n">
-        <v>0.8863636363636364</v>
+        <v>0.8825757575757577</v>
       </c>
     </row>
     <row r="976">
@@ -43516,7 +43516,7 @@
       </c>
       <c r="P979" t="inlineStr"/>
       <c r="Q979" t="n">
-        <v>0.8850574712643678</v>
+        <v>0.8505747126436781</v>
       </c>
     </row>
     <row r="980">
@@ -43569,7 +43569,7 @@
         <v>0.2716049382716049</v>
       </c>
       <c r="Q980" t="n">
-        <v>0.9578947368421052</v>
+        <v>0.9649122807017544</v>
       </c>
     </row>
     <row r="981">
@@ -43622,7 +43622,7 @@
         <v>0.35</v>
       </c>
       <c r="Q981" t="n">
-        <v>1.008620689655172</v>
+        <v>1.002873563218391</v>
       </c>
     </row>
     <row r="982">
@@ -43675,7 +43675,7 @@
         <v>0.5161290322580645</v>
       </c>
       <c r="Q982" t="n">
-        <v>0.9312977099236641</v>
+        <v>0.9363867684478371</v>
       </c>
     </row>
     <row r="983">
@@ -43728,7 +43728,7 @@
         <v>0.5416666666666666</v>
       </c>
       <c r="Q983" t="n">
-        <v>0.9007633587786259</v>
+        <v>0.8931297709923665</v>
       </c>
     </row>
     <row r="984">
@@ -43781,7 +43781,7 @@
         <v>0.5454545454545454</v>
       </c>
       <c r="Q984" t="n">
-        <v>0.7086614173228346</v>
+        <v>0.7139107611548556</v>
       </c>
     </row>
     <row r="985">
@@ -43834,7 +43834,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="Q985" t="n">
-        <v>0.6019417475728155</v>
+        <v>0.6116504854368932</v>
       </c>
     </row>
     <row r="986">
@@ -43883,7 +43883,7 @@
       <c r="O986" t="inlineStr"/>
       <c r="P986" t="inlineStr"/>
       <c r="Q986" t="n">
-        <v>0.9264705882352942</v>
+        <v>0.9313725490196078</v>
       </c>
     </row>
     <row r="987">
@@ -43930,7 +43930,7 @@
       <c r="O987" t="inlineStr"/>
       <c r="P987" t="inlineStr"/>
       <c r="Q987" t="n">
-        <v>0.9384615384615385</v>
+        <v>0.9487179487179488</v>
       </c>
     </row>
     <row r="988">
@@ -43975,7 +43975,7 @@
       <c r="O988" t="inlineStr"/>
       <c r="P988" t="inlineStr"/>
       <c r="Q988" t="n">
-        <v>1.016666666666667</v>
+        <v>1.022222222222222</v>
       </c>
     </row>
     <row r="989">
@@ -44020,7 +44020,7 @@
       <c r="O989" t="inlineStr"/>
       <c r="P989" t="inlineStr"/>
       <c r="Q989" t="n">
-        <v>1.173076923076923</v>
+        <v>1.115384615384615</v>
       </c>
     </row>
     <row r="990">
@@ -44065,7 +44065,7 @@
       <c r="O990" t="inlineStr"/>
       <c r="P990" t="inlineStr"/>
       <c r="Q990" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.896551724137931</v>
       </c>
     </row>
     <row r="991">
@@ -44110,7 +44110,7 @@
       <c r="O991" t="inlineStr"/>
       <c r="P991" t="inlineStr"/>
       <c r="Q991" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9629629629629629</v>
       </c>
     </row>
     <row r="992">
@@ -44198,7 +44198,7 @@
       </c>
       <c r="P993" t="inlineStr"/>
       <c r="Q993" t="n">
-        <v>0.8</v>
+        <v>0.8060606060606061</v>
       </c>
     </row>
     <row r="994">
@@ -44247,7 +44247,7 @@
       <c r="O994" t="inlineStr"/>
       <c r="P994" t="inlineStr"/>
       <c r="Q994" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8390804597701149</v>
       </c>
     </row>
     <row r="995">
@@ -44296,7 +44296,7 @@
       </c>
       <c r="P995" t="inlineStr"/>
       <c r="Q995" t="n">
-        <v>0.9642857142857143</v>
+        <v>0.9404761904761906</v>
       </c>
     </row>
     <row r="996">
@@ -44345,7 +44345,7 @@
       </c>
       <c r="P996" t="inlineStr"/>
       <c r="Q996" t="n">
-        <v>0.873015873015873</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="997">
@@ -44398,7 +44398,7 @@
         <v>0.6176470588235294</v>
       </c>
       <c r="Q997" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9532163742690057</v>
       </c>
     </row>
     <row r="998">
@@ -44451,7 +44451,7 @@
         <v>1.238095238095238</v>
       </c>
       <c r="Q998" t="n">
-        <v>0.9827586206896551</v>
+        <v>0.9942528735632183</v>
       </c>
     </row>
     <row r="999">
@@ -44504,7 +44504,7 @@
         <v>1.173913043478261</v>
       </c>
       <c r="Q999" t="n">
-        <v>1.226415094339623</v>
+        <v>1.232704402515723</v>
       </c>
     </row>
     <row r="1000">
@@ -44635,7 +44635,7 @@
       </c>
       <c r="P1002" t="inlineStr"/>
       <c r="Q1002" t="n">
-        <v>1.026666666666667</v>
+        <v>1.031111111111111</v>
       </c>
     </row>
     <row r="1003">
@@ -44688,7 +44688,7 @@
         <v>1.133333333333333</v>
       </c>
       <c r="Q1003" t="n">
-        <v>0.8271604938271605</v>
+        <v>0.8436213991769547</v>
       </c>
     </row>
     <row r="1004">
@@ -44794,7 +44794,7 @@
         <v>0.8444444444444444</v>
       </c>
       <c r="Q1005" t="n">
-        <v>0.8354430379746836</v>
+        <v>0.8227848101265823</v>
       </c>
     </row>
     <row r="1006">
@@ -44847,7 +44847,7 @@
         <v>0.7291666666666666</v>
       </c>
       <c r="Q1006" t="n">
-        <v>0.9014084507042254</v>
+        <v>0.9436619718309859</v>
       </c>
     </row>
     <row r="1007">
@@ -44900,7 +44900,7 @@
         <v>0.8205128205128205</v>
       </c>
       <c r="Q1007" t="n">
-        <v>0.9594594594594594</v>
+        <v>0.927927927927928</v>
       </c>
     </row>
     <row r="1008">
@@ -44953,7 +44953,7 @@
         <v>0.575</v>
       </c>
       <c r="Q1008" t="n">
-        <v>0.9032258064516129</v>
+        <v>0.913978494623656</v>
       </c>
     </row>
     <row r="1009">
@@ -45006,7 +45006,7 @@
         <v>0.4871794871794872</v>
       </c>
       <c r="Q1009" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.9682539682539683</v>
       </c>
     </row>
     <row r="1010">
@@ -45055,7 +45055,7 @@
       <c r="O1010" t="inlineStr"/>
       <c r="P1010" t="inlineStr"/>
       <c r="Q1010" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.8923076923076924</v>
       </c>
     </row>
     <row r="1011">
@@ -45102,7 +45102,7 @@
       <c r="O1011" t="inlineStr"/>
       <c r="P1011" t="inlineStr"/>
       <c r="Q1011" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.9611111111111111</v>
       </c>
     </row>
     <row r="1012">
@@ -45147,7 +45147,7 @@
       <c r="O1012" t="inlineStr"/>
       <c r="P1012" t="inlineStr"/>
       <c r="Q1012" t="n">
-        <v>1.035714285714286</v>
+        <v>1.005952380952381</v>
       </c>
     </row>
     <row r="1013">
@@ -45192,7 +45192,7 @@
       <c r="O1013" t="inlineStr"/>
       <c r="P1013" t="inlineStr"/>
       <c r="Q1013" t="n">
-        <v>1.076923076923077</v>
+        <v>1.038461538461539</v>
       </c>
     </row>
     <row r="1014">
@@ -45237,7 +45237,7 @@
       <c r="O1014" t="inlineStr"/>
       <c r="P1014" t="inlineStr"/>
       <c r="Q1014" t="n">
-        <v>0.847457627118644</v>
+        <v>0.8587570621468927</v>
       </c>
     </row>
     <row r="1015">
@@ -45515,7 +45515,7 @@
       <c r="O1020" t="inlineStr"/>
       <c r="P1020" t="inlineStr"/>
       <c r="Q1020" t="n">
-        <v>0.2439024390243902</v>
+        <v>0.2520325203252033</v>
       </c>
     </row>
     <row r="1021">
@@ -45562,7 +45562,7 @@
       </c>
       <c r="P1021" t="inlineStr"/>
       <c r="Q1021" t="n">
-        <v>0.2682926829268293</v>
+        <v>0.2601626016260162</v>
       </c>
     </row>
     <row r="1022">
@@ -45611,7 +45611,7 @@
       </c>
       <c r="P1022" t="inlineStr"/>
       <c r="Q1022" t="n">
-        <v>1</v>
+        <v>0.9918699186991869</v>
       </c>
     </row>
     <row r="1023">
@@ -45664,7 +45664,7 @@
         <v>0.4038461538461539</v>
       </c>
       <c r="Q1023" t="n">
-        <v>0.8297872340425532</v>
+        <v>0.8794326241134752</v>
       </c>
     </row>
     <row r="1024">
@@ -45717,7 +45717,7 @@
         <v>0.84</v>
       </c>
       <c r="Q1024" t="n">
-        <v>0.9130434782608695</v>
+        <v>0.8623188405797101</v>
       </c>
     </row>
     <row r="1025">
@@ -45879,7 +45879,7 @@
       </c>
       <c r="P1028" t="inlineStr"/>
       <c r="Q1028" t="n">
-        <v>1.125</v>
+        <v>1.107142857142857</v>
       </c>
     </row>
     <row r="1029">
@@ -45985,7 +45985,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="Q1030" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="1031">
@@ -46038,7 +46038,7 @@
         <v>0.92</v>
       </c>
       <c r="Q1031" t="n">
-        <v>1</v>
+        <v>0.9743589743589743</v>
       </c>
     </row>
     <row r="1032">
@@ -46091,7 +46091,7 @@
         <v>1.625</v>
       </c>
       <c r="Q1032" t="n">
-        <v>1.113636363636364</v>
+        <v>1.151515151515151</v>
       </c>
     </row>
     <row r="1033">
@@ -46197,7 +46197,7 @@
         <v>1.526315789473684</v>
       </c>
       <c r="Q1034" t="n">
-        <v>1.090909090909091</v>
+        <v>1.068181818181818</v>
       </c>
     </row>
     <row r="1035">
@@ -46293,7 +46293,7 @@
       <c r="O1036" t="inlineStr"/>
       <c r="P1036" t="inlineStr"/>
       <c r="Q1036" t="n">
-        <v>0.7407407407407407</v>
+        <v>0.7345679012345678</v>
       </c>
     </row>
     <row r="1037">
@@ -46338,7 +46338,7 @@
       <c r="O1037" t="inlineStr"/>
       <c r="P1037" t="inlineStr"/>
       <c r="Q1037" t="n">
-        <v>1.046511627906977</v>
+        <v>1.077519379844961</v>
       </c>
     </row>
     <row r="1038">
@@ -46428,7 +46428,7 @@
       <c r="O1039" t="inlineStr"/>
       <c r="P1039" t="inlineStr"/>
       <c r="Q1039" t="n">
-        <v>0.9818181818181818</v>
+        <v>0.9696969696969697</v>
       </c>
     </row>
     <row r="1040">
@@ -46473,7 +46473,7 @@
       <c r="O1040" t="inlineStr"/>
       <c r="P1040" t="inlineStr"/>
       <c r="Q1040" t="n">
-        <v>1</v>
+        <v>1.018518518518519</v>
       </c>
     </row>
     <row r="1041">
@@ -46561,7 +46561,7 @@
       </c>
       <c r="P1042" t="inlineStr"/>
       <c r="Q1042" t="n">
-        <v>0.8108108108108109</v>
+        <v>0.7837837837837838</v>
       </c>
     </row>
     <row r="1043">
@@ -46610,7 +46610,7 @@
       <c r="O1043" t="inlineStr"/>
       <c r="P1043" t="inlineStr"/>
       <c r="Q1043" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.8850574712643677</v>
       </c>
     </row>
     <row r="1044">
@@ -46657,7 +46657,7 @@
       <c r="O1044" t="inlineStr"/>
       <c r="P1044" t="inlineStr"/>
       <c r="Q1044" t="n">
-        <v>0.9375</v>
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="1045">
@@ -46753,7 +46753,7 @@
       </c>
       <c r="P1046" t="inlineStr"/>
       <c r="Q1046" t="n">
-        <v>1.375</v>
+        <v>1.385416666666667</v>
       </c>
     </row>
     <row r="1047">
@@ -46806,7 +46806,7 @@
         <v>0.68</v>
       </c>
       <c r="Q1047" t="n">
-        <v>0.86</v>
+        <v>0.8666666666666667</v>
       </c>
     </row>
     <row r="1048">
@@ -46859,7 +46859,7 @@
         <v>0.5454545454545454</v>
       </c>
       <c r="Q1048" t="n">
-        <v>0.9038461538461539</v>
+        <v>0.9294871794871795</v>
       </c>
     </row>
     <row r="1049">
@@ -46912,7 +46912,7 @@
         <v>0.5454545454545454</v>
       </c>
       <c r="Q1049" t="n">
-        <v>0.9038461538461539</v>
+        <v>0.9294871794871795</v>
       </c>
     </row>
     <row r="1050">
@@ -47074,7 +47074,7 @@
       </c>
       <c r="P1053" t="inlineStr"/>
       <c r="Q1053" t="n">
-        <v>0.7551020408163265</v>
+        <v>0.7482993197278911</v>
       </c>
     </row>
     <row r="1054">
@@ -47127,7 +47127,7 @@
         <v>0.5909090909090909</v>
       </c>
       <c r="Q1054" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.9059829059829061</v>
       </c>
     </row>
     <row r="1055">
@@ -47180,7 +47180,7 @@
         <v>0.4</v>
       </c>
       <c r="Q1055" t="n">
-        <v>1.052631578947368</v>
+        <v>1.06140350877193</v>
       </c>
     </row>
     <row r="1056">
@@ -47233,7 +47233,7 @@
         <v>0.4347826086956522</v>
       </c>
       <c r="Q1056" t="n">
-        <v>0.9302325581395349</v>
+        <v>0.9224806201550387</v>
       </c>
     </row>
     <row r="1057">
@@ -47286,7 +47286,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="Q1057" t="n">
-        <v>0.8717948717948718</v>
+        <v>0.8290598290598291</v>
       </c>
     </row>
     <row r="1058">
@@ -47339,7 +47339,7 @@
         <v>0.631578947368421</v>
       </c>
       <c r="Q1058" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.7450980392156863</v>
       </c>
     </row>
     <row r="1059">
@@ -47392,7 +47392,7 @@
         <v>0.625</v>
       </c>
       <c r="Q1059" t="n">
-        <v>0.7</v>
+        <v>0.6777777777777778</v>
       </c>
     </row>
     <row r="1060">
@@ -47441,7 +47441,7 @@
       <c r="O1060" t="inlineStr"/>
       <c r="P1060" t="inlineStr"/>
       <c r="Q1060" t="n">
-        <v>0.9259259259259259</v>
+        <v>0.9506172839506172</v>
       </c>
     </row>
     <row r="1061">
@@ -47488,7 +47488,7 @@
       <c r="O1061" t="inlineStr"/>
       <c r="P1061" t="inlineStr"/>
       <c r="Q1061" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="1062">
@@ -47533,7 +47533,7 @@
       <c r="O1062" t="inlineStr"/>
       <c r="P1062" t="inlineStr"/>
       <c r="Q1062" t="n">
-        <v>1</v>
+        <v>1.009009009009009</v>
       </c>
     </row>
     <row r="1063">
@@ -47578,7 +47578,7 @@
       <c r="O1063" t="inlineStr"/>
       <c r="P1063" t="inlineStr"/>
       <c r="Q1063" t="n">
-        <v>0.8205128205128205</v>
+        <v>0.8290598290598291</v>
       </c>
     </row>
     <row r="1064">
@@ -47623,7 +47623,7 @@
       <c r="O1064" t="inlineStr"/>
       <c r="P1064" t="inlineStr"/>
       <c r="Q1064" t="n">
-        <v>1.085714285714286</v>
+        <v>1.095238095238095</v>
       </c>
     </row>
     <row r="1065">
@@ -47668,7 +47668,7 @@
       <c r="O1065" t="inlineStr"/>
       <c r="P1065" t="inlineStr"/>
       <c r="Q1065" t="n">
-        <v>0.8918918918918919</v>
+        <v>0.9009009009009009</v>
       </c>
     </row>
     <row r="1066">
@@ -47756,7 +47756,7 @@
       </c>
       <c r="P1067" t="inlineStr"/>
       <c r="Q1067" t="n">
-        <v>0.7291666666666666</v>
+        <v>0.7083333333333334</v>
       </c>
     </row>
     <row r="1068">
@@ -47809,7 +47809,7 @@
         <v>0.5</v>
       </c>
       <c r="Q1068" t="n">
-        <v>0.9666666666666667</v>
+        <v>0.9444444444444445</v>
       </c>
     </row>
     <row r="1069">
@@ -47862,7 +47862,7 @@
         <v>0.4761904761904762</v>
       </c>
       <c r="Q1069" t="n">
-        <v>0.8108108108108109</v>
+        <v>0.8468468468468469</v>
       </c>
     </row>
     <row r="1070">
@@ -47915,7 +47915,7 @@
         <v>0.48</v>
       </c>
       <c r="Q1070" t="n">
-        <v>0.96875</v>
+        <v>0.9166666666666667</v>
       </c>
     </row>
     <row r="1071">
@@ -47968,7 +47968,7 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="Q1071" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.8279569892473118</v>
       </c>
     </row>
     <row r="1072">
@@ -48021,7 +48021,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="Q1072" t="n">
-        <v>1.193548387096774</v>
+        <v>1.129032258064516</v>
       </c>
     </row>
     <row r="1073">
@@ -48127,7 +48127,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="Q1074" t="n">
-        <v>0.625</v>
+        <v>0.6770833333333334</v>
       </c>
     </row>
     <row r="1075">
@@ -48180,7 +48180,7 @@
         <v>0.4230769230769231</v>
       </c>
       <c r="Q1075" t="n">
-        <v>1.037037037037037</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1076">
@@ -48339,7 +48339,7 @@
         <v>0.6551724137931034</v>
       </c>
       <c r="Q1078" t="n">
-        <v>0.8</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="1079">
@@ -48392,7 +48392,7 @@
         <v>0.6896551724137931</v>
       </c>
       <c r="Q1079" t="n">
-        <v>0.9743589743589743</v>
+        <v>0.9572649572649573</v>
       </c>
     </row>
     <row r="1080">
@@ -48445,7 +48445,7 @@
         <v>0.6</v>
       </c>
       <c r="Q1080" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.8484848484848485</v>
       </c>
     </row>
     <row r="1081">
@@ -48498,7 +48498,7 @@
         <v>0.6538461538461539</v>
       </c>
       <c r="Q1081" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="1082">
@@ -48604,7 +48604,7 @@
         <v>0.8421052631578947</v>
       </c>
       <c r="Q1083" t="n">
-        <v>0.8809523809523809</v>
+        <v>0.8968253968253967</v>
       </c>
     </row>
     <row r="1084">
@@ -48700,7 +48700,7 @@
       <c r="O1085" t="inlineStr"/>
       <c r="P1085" t="inlineStr"/>
       <c r="Q1085" t="n">
-        <v>1.194444444444444</v>
+        <v>1.185185185185185</v>
       </c>
     </row>
     <row r="1086">
@@ -48745,7 +48745,7 @@
       <c r="O1086" t="inlineStr"/>
       <c r="P1086" t="inlineStr"/>
       <c r="Q1086" t="n">
-        <v>1.069767441860465</v>
+        <v>1.062015503875969</v>
       </c>
     </row>
     <row r="1087">
@@ -48790,7 +48790,7 @@
       <c r="O1087" t="inlineStr"/>
       <c r="P1087" t="inlineStr"/>
       <c r="Q1087" t="n">
-        <v>0.84</v>
+        <v>0.8466666666666667</v>
       </c>
     </row>
     <row r="1088">
@@ -48835,7 +48835,7 @@
       <c r="O1088" t="inlineStr"/>
       <c r="P1088" t="inlineStr"/>
       <c r="Q1088" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.9513888888888888</v>
       </c>
     </row>
     <row r="1089">
@@ -48968,7 +48968,7 @@
       </c>
       <c r="P1091" t="inlineStr"/>
       <c r="Q1091" t="n">
-        <v>0.821917808219178</v>
+        <v>0.817351598173516</v>
       </c>
     </row>
     <row r="1092">
@@ -49021,7 +49021,7 @@
         <v>0.3870967741935484</v>
       </c>
       <c r="Q1092" t="n">
-        <v>0.9253731343283582</v>
+        <v>0.9054726368159205</v>
       </c>
     </row>
     <row r="1093">
@@ -49074,7 +49074,7 @@
         <v>0.543859649122807</v>
       </c>
       <c r="Q1093" t="n">
-        <v>0.96</v>
+        <v>0.9644444444444443</v>
       </c>
     </row>
     <row r="1094">
@@ -49127,7 +49127,7 @@
         <v>0.6296296296296297</v>
       </c>
       <c r="Q1094" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8333333333333333</v>
       </c>
     </row>
     <row r="1095">
@@ -49180,7 +49180,7 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="Q1095" t="n">
-        <v>0.9125</v>
+        <v>0.8875</v>
       </c>
     </row>
     <row r="1096">
@@ -49233,7 +49233,7 @@
         <v>0.7727272727272727</v>
       </c>
       <c r="Q1096" t="n">
-        <v>0.8505747126436781</v>
+        <v>0.8659003831417624</v>
       </c>
     </row>
     <row r="1097">
@@ -49286,7 +49286,7 @@
         <v>0.75</v>
       </c>
       <c r="Q1097" t="n">
-        <v>0.9493670886075949</v>
+        <v>0.9578059071729959</v>
       </c>
     </row>
     <row r="1098">
@@ -49339,7 +49339,7 @@
         <v>0.6129032258064516</v>
       </c>
       <c r="Q1098" t="n">
-        <v>0.8961038961038961</v>
+        <v>0.8917748917748919</v>
       </c>
     </row>
     <row r="1099">
@@ -49392,7 +49392,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="Q1099" t="n">
-        <v>1</v>
+        <v>1.027027027027027</v>
       </c>
     </row>
     <row r="1100">
@@ -49445,7 +49445,7 @@
         <v>0.6875</v>
       </c>
       <c r="Q1100" t="n">
-        <v>1.038461538461539</v>
+        <v>1.02991452991453</v>
       </c>
     </row>
     <row r="1101">
@@ -49498,7 +49498,7 @@
         <v>1.064516129032258</v>
       </c>
       <c r="Q1101" t="n">
-        <v>1.041095890410959</v>
+        <v>1.050228310502283</v>
       </c>
     </row>
     <row r="1102">
@@ -49551,7 +49551,7 @@
         <v>1</v>
       </c>
       <c r="Q1102" t="n">
-        <v>1.155844155844156</v>
+        <v>1.12987012987013</v>
       </c>
     </row>
     <row r="1103">
@@ -49657,7 +49657,7 @@
         <v>0.84</v>
       </c>
       <c r="Q1104" t="n">
-        <v>0.7981651376146789</v>
+        <v>0.7828746177370031</v>
       </c>
     </row>
     <row r="1105">
@@ -49710,7 +49710,7 @@
         <v>0.8478260869565217</v>
       </c>
       <c r="Q1105" t="n">
-        <v>1.186813186813187</v>
+        <v>1.208791208791209</v>
       </c>
     </row>
     <row r="1106">
@@ -49763,7 +49763,7 @@
         <v>1.176470588235294</v>
       </c>
       <c r="Q1106" t="n">
-        <v>0.6752136752136753</v>
+        <v>0.6780626780626781</v>
       </c>
     </row>
     <row r="1107">
@@ -49816,7 +49816,7 @@
         <v>0.8</v>
       </c>
       <c r="Q1107" t="n">
-        <v>0.9375</v>
+        <v>0.9541666666666666</v>
       </c>
     </row>
     <row r="1108">
@@ -49865,7 +49865,7 @@
       <c r="O1108" t="inlineStr"/>
       <c r="P1108" t="inlineStr"/>
       <c r="Q1108" t="n">
-        <v>1</v>
+        <v>0.9886363636363636</v>
       </c>
     </row>
     <row r="1109">
@@ -49957,7 +49957,7 @@
       <c r="O1110" t="inlineStr"/>
       <c r="P1110" t="inlineStr"/>
       <c r="Q1110" t="n">
-        <v>0.9439252336448598</v>
+        <v>0.9719626168224299</v>
       </c>
     </row>
     <row r="1111">
@@ -50002,7 +50002,7 @@
       <c r="O1111" t="inlineStr"/>
       <c r="P1111" t="inlineStr"/>
       <c r="Q1111" t="n">
-        <v>0.9826086956521739</v>
+        <v>0.9478260869565217</v>
       </c>
     </row>
     <row r="1112">
@@ -50047,7 +50047,7 @@
       <c r="O1112" t="inlineStr"/>
       <c r="P1112" t="inlineStr"/>
       <c r="Q1112" t="n">
-        <v>0.8235294117647058</v>
+        <v>0.8347338935574229</v>
       </c>
     </row>
     <row r="1113">
@@ -50092,7 +50092,7 @@
       <c r="O1113" t="inlineStr"/>
       <c r="P1113" t="inlineStr"/>
       <c r="Q1113" t="n">
-        <v>0.9130434782608695</v>
+        <v>0.9246376811594202</v>
       </c>
     </row>
     <row r="1114">
@@ -50470,7 +50470,7 @@
       </c>
       <c r="P1125" t="inlineStr"/>
       <c r="Q1125" t="n">
-        <v>1.107142857142857</v>
+        <v>1.119047619047619</v>
       </c>
     </row>
     <row r="1126">
@@ -50576,7 +50576,7 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="Q1127" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9111111111111112</v>
       </c>
     </row>
     <row r="1128">
@@ -50629,7 +50629,7 @@
         <v>0.5294117647058824</v>
       </c>
       <c r="Q1128" t="n">
-        <v>0.9642857142857143</v>
+        <v>0.880952380952381</v>
       </c>
     </row>
     <row r="1129">
@@ -50682,7 +50682,7 @@
         <v>0.3888888888888889</v>
       </c>
       <c r="Q1129" t="n">
-        <v>0.9259259259259259</v>
+        <v>1.024691358024691</v>
       </c>
     </row>
     <row r="1130">
@@ -50735,7 +50735,7 @@
         <v>0.5</v>
       </c>
       <c r="Q1130" t="n">
-        <v>1.096774193548387</v>
+        <v>1.021505376344086</v>
       </c>
     </row>
     <row r="1131">
@@ -50788,7 +50788,7 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="Q1131" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.7311827956989247</v>
       </c>
     </row>
     <row r="1132">
@@ -50837,7 +50837,7 @@
       <c r="O1132" t="inlineStr"/>
       <c r="P1132" t="inlineStr"/>
       <c r="Q1132" t="n">
-        <v>0.9523809523809523</v>
+        <v>0.9365079365079365</v>
       </c>
     </row>
     <row r="1133">
@@ -50884,7 +50884,7 @@
       <c r="O1133" t="inlineStr"/>
       <c r="P1133" t="inlineStr"/>
       <c r="Q1133" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="1134">
@@ -50974,7 +50974,7 @@
       <c r="O1135" t="inlineStr"/>
       <c r="P1135" t="inlineStr"/>
       <c r="Q1135" t="n">
-        <v>1.117647058823529</v>
+        <v>1.137254901960784</v>
       </c>
     </row>
     <row r="1136">
@@ -51019,7 +51019,7 @@
       <c r="O1136" t="inlineStr"/>
       <c r="P1136" t="inlineStr"/>
       <c r="Q1136" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.7407407407407407</v>
       </c>
     </row>
     <row r="1137">
@@ -51330,7 +51330,7 @@
       </c>
       <c r="P1145" t="inlineStr"/>
       <c r="Q1145" t="n">
-        <v>2</v>
+        <v>1.666666666666667</v>
       </c>
     </row>
     <row r="1146">
@@ -51554,7 +51554,7 @@
       </c>
       <c r="P1151" t="inlineStr"/>
       <c r="Q1151" t="n">
-        <v>1.4</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="1152">
@@ -51605,7 +51605,7 @@
       </c>
       <c r="P1152" t="inlineStr"/>
       <c r="Q1152" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7777777777777778</v>
       </c>
     </row>
     <row r="1153">
@@ -51656,7 +51656,7 @@
       </c>
       <c r="P1153" t="inlineStr"/>
       <c r="Q1153" t="n">
-        <v>1.25</v>
+        <v>1.083333333333333</v>
       </c>
     </row>
     <row r="1154">
@@ -51758,7 +51758,7 @@
       </c>
       <c r="P1155" t="inlineStr"/>
       <c r="Q1155" t="n">
-        <v>1.25</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="1156">
@@ -51854,7 +51854,7 @@
       <c r="O1157" t="inlineStr"/>
       <c r="P1157" t="inlineStr"/>
       <c r="Q1157" t="n">
-        <v>1</v>
+        <v>0.9523809523809524</v>
       </c>
     </row>
     <row r="1158">
@@ -51899,7 +51899,7 @@
       <c r="O1158" t="inlineStr"/>
       <c r="P1158" t="inlineStr"/>
       <c r="Q1158" t="n">
-        <v>1</v>
+        <v>1.055555555555556</v>
       </c>
     </row>
     <row r="1159">
@@ -51944,7 +51944,7 @@
       <c r="O1159" t="inlineStr"/>
       <c r="P1159" t="inlineStr"/>
       <c r="Q1159" t="n">
-        <v>1</v>
+        <v>0.9444444444444445</v>
       </c>
     </row>
     <row r="1160">
@@ -51989,7 +51989,7 @@
       <c r="O1160" t="inlineStr"/>
       <c r="P1160" t="inlineStr"/>
       <c r="Q1160" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7222222222222222</v>
       </c>
     </row>
     <row r="1161">
@@ -52122,7 +52122,7 @@
       </c>
       <c r="P1163" t="inlineStr"/>
       <c r="Q1163" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="1164">
@@ -52171,7 +52171,7 @@
       <c r="O1164" t="inlineStr"/>
       <c r="P1164" t="inlineStr"/>
       <c r="Q1164" t="n">
-        <v>1.15</v>
+        <v>1.144444444444445</v>
       </c>
     </row>
     <row r="1165">
@@ -52265,7 +52265,7 @@
       </c>
       <c r="P1166" t="inlineStr"/>
       <c r="Q1166" t="n">
-        <v>0.9180327868852459</v>
+        <v>0.9398907103825136</v>
       </c>
     </row>
     <row r="1167">
@@ -52314,7 +52314,7 @@
       </c>
       <c r="P1167" t="inlineStr"/>
       <c r="Q1167" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.9032258064516129</v>
       </c>
     </row>
     <row r="1168">
@@ -52367,7 +52367,7 @@
         <v>0.7045454545454546</v>
       </c>
       <c r="Q1168" t="n">
-        <v>0.8656716417910447</v>
+        <v>0.8955223880597015</v>
       </c>
     </row>
     <row r="1169">
@@ -52420,7 +52420,7 @@
         <v>0.8095238095238095</v>
       </c>
       <c r="Q1169" t="n">
-        <v>0.9672131147540983</v>
+        <v>0.9398907103825136</v>
       </c>
     </row>
     <row r="1170">
@@ -52582,7 +52582,7 @@
       </c>
       <c r="P1173" t="inlineStr"/>
       <c r="Q1173" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.8666666666666667</v>
       </c>
     </row>
     <row r="1174">
@@ -52635,7 +52635,7 @@
         <v>0.7692307692307693</v>
       </c>
       <c r="Q1174" t="n">
-        <v>0.927536231884058</v>
+        <v>0.9468599033816425</v>
       </c>
     </row>
     <row r="1175">
@@ -52688,7 +52688,7 @@
         <v>0.7058823529411765</v>
       </c>
       <c r="Q1175" t="n">
-        <v>1.013333333333333</v>
+        <v>0.9955555555555556</v>
       </c>
     </row>
     <row r="1176">
@@ -52741,7 +52741,7 @@
         <v>0.7647058823529411</v>
       </c>
       <c r="Q1176" t="n">
-        <v>0.9625</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="1177">
@@ -52794,7 +52794,7 @@
         <v>0.7857142857142857</v>
       </c>
       <c r="Q1177" t="n">
-        <v>1.025316455696202</v>
+        <v>1.016877637130802</v>
       </c>
     </row>
     <row r="1178">
@@ -52847,7 +52847,7 @@
         <v>0.9736842105263158</v>
       </c>
       <c r="Q1178" t="n">
-        <v>0.925</v>
+        <v>0.9375</v>
       </c>
     </row>
     <row r="1179">
@@ -52900,7 +52900,7 @@
         <v>0.75</v>
       </c>
       <c r="Q1179" t="n">
-        <v>0.987012987012987</v>
+        <v>0.9783549783549783</v>
       </c>
     </row>
     <row r="1180">
@@ -52949,7 +52949,7 @@
       <c r="O1180" t="inlineStr"/>
       <c r="P1180" t="inlineStr"/>
       <c r="Q1180" t="n">
-        <v>0.8625</v>
+        <v>0.8708333333333333</v>
       </c>
     </row>
     <row r="1181">
@@ -52996,7 +52996,7 @@
       <c r="O1181" t="inlineStr"/>
       <c r="P1181" t="inlineStr"/>
       <c r="Q1181" t="n">
-        <v>1.088235294117647</v>
+        <v>1.068627450980392</v>
       </c>
     </row>
     <row r="1182">
@@ -53041,7 +53041,7 @@
       <c r="O1182" t="inlineStr"/>
       <c r="P1182" t="inlineStr"/>
       <c r="Q1182" t="n">
-        <v>0.9518072289156626</v>
+        <v>0.9718875502008033</v>
       </c>
     </row>
     <row r="1183">
@@ -53086,7 +53086,7 @@
       <c r="O1183" t="inlineStr"/>
       <c r="P1183" t="inlineStr"/>
       <c r="Q1183" t="n">
-        <v>1.12</v>
+        <v>1.088888888888889</v>
       </c>
     </row>
     <row r="1184">
@@ -53131,7 +53131,7 @@
       <c r="O1184" t="inlineStr"/>
       <c r="P1184" t="inlineStr"/>
       <c r="Q1184" t="n">
-        <v>0.9012345679012346</v>
+        <v>0.9259259259259259</v>
       </c>
     </row>
     <row r="1185">
@@ -53176,7 +53176,7 @@
       <c r="O1185" t="inlineStr"/>
       <c r="P1185" t="inlineStr"/>
       <c r="Q1185" t="n">
-        <v>0.9625</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="1186">
@@ -53264,7 +53264,7 @@
       </c>
       <c r="P1187" t="inlineStr"/>
       <c r="Q1187" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="1188">
@@ -53313,7 +53313,7 @@
       <c r="O1188" t="inlineStr"/>
       <c r="P1188" t="inlineStr"/>
       <c r="Q1188" t="n">
-        <v>1.307692307692308</v>
+        <v>1.217948717948718</v>
       </c>
     </row>
     <row r="1189">
@@ -53362,7 +53362,7 @@
       </c>
       <c r="P1189" t="inlineStr"/>
       <c r="Q1189" t="n">
-        <v>1</v>
+        <v>1.009009009009009</v>
       </c>
     </row>
     <row r="1190">
@@ -53411,7 +53411,7 @@
       </c>
       <c r="P1190" t="inlineStr"/>
       <c r="Q1190" t="n">
-        <v>0.8536585365853658</v>
+        <v>0.8617886178861789</v>
       </c>
     </row>
     <row r="1191">
@@ -53517,7 +53517,7 @@
         <v>0.76</v>
       </c>
       <c r="Q1192" t="n">
-        <v>1</v>
+        <v>1.016260162601626</v>
       </c>
     </row>
     <row r="1193">
@@ -53570,7 +53570,7 @@
         <v>0.8518518518518519</v>
       </c>
       <c r="Q1193" t="n">
-        <v>0.9302325581395349</v>
+        <v>0.9147286821705427</v>
       </c>
     </row>
     <row r="1194">
@@ -53701,7 +53701,7 @@
       </c>
       <c r="P1196" t="inlineStr"/>
       <c r="Q1196" t="n">
-        <v>0.9574468085106383</v>
+        <v>0.9503546099290779</v>
       </c>
     </row>
     <row r="1197">
@@ -53754,7 +53754,7 @@
         <v>0.7916666666666666</v>
       </c>
       <c r="Q1197" t="n">
-        <v>0.851063829787234</v>
+        <v>0.8794326241134752</v>
       </c>
     </row>
     <row r="1198">
@@ -53807,7 +53807,7 @@
         <v>0.7307692307692307</v>
       </c>
       <c r="Q1198" t="n">
-        <v>0.9534883720930233</v>
+        <v>0.9224806201550387</v>
       </c>
     </row>
     <row r="1199">
@@ -53860,7 +53860,7 @@
         <v>0.6785714285714286</v>
       </c>
       <c r="Q1199" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.8412698412698413</v>
       </c>
     </row>
     <row r="1200">
@@ -53913,7 +53913,7 @@
         <v>0.6428571428571429</v>
       </c>
       <c r="Q1200" t="n">
-        <v>1.051282051282051</v>
+        <v>1.05982905982906</v>
       </c>
     </row>
     <row r="1201">
@@ -53966,7 +53966,7 @@
         <v>0.6551724137931034</v>
       </c>
       <c r="Q1201" t="n">
-        <v>0.975</v>
+        <v>0.9416666666666668</v>
       </c>
     </row>
     <row r="1202">
@@ -54019,7 +54019,7 @@
         <v>0.7692307692307693</v>
       </c>
       <c r="Q1202" t="n">
-        <v>1.05</v>
+        <v>1.041666666666667</v>
       </c>
     </row>
     <row r="1203">
@@ -54072,7 +54072,7 @@
         <v>0.7692307692307693</v>
       </c>
       <c r="Q1203" t="n">
-        <v>0.9069767441860465</v>
+        <v>0.9302325581395349</v>
       </c>
     </row>
     <row r="1204">
@@ -54121,7 +54121,7 @@
       <c r="O1204" t="inlineStr"/>
       <c r="P1204" t="inlineStr"/>
       <c r="Q1204" t="n">
-        <v>1</v>
+        <v>0.9841269841269842</v>
       </c>
     </row>
     <row r="1205">
@@ -54168,7 +54168,7 @@
       <c r="O1205" t="inlineStr"/>
       <c r="P1205" t="inlineStr"/>
       <c r="Q1205" t="n">
-        <v>0.8372093023255814</v>
+        <v>0.8294573643410852</v>
       </c>
     </row>
     <row r="1206">
@@ -54213,7 +54213,7 @@
       <c r="O1206" t="inlineStr"/>
       <c r="P1206" t="inlineStr"/>
       <c r="Q1206" t="n">
-        <v>0.8717948717948718</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="1207">
@@ -54303,7 +54303,7 @@
       <c r="O1208" t="inlineStr"/>
       <c r="P1208" t="inlineStr"/>
       <c r="Q1208" t="n">
-        <v>1</v>
+        <v>0.992063492063492</v>
       </c>
     </row>
     <row r="1209">
@@ -54348,7 +54348,7 @@
       <c r="O1209" t="inlineStr"/>
       <c r="P1209" t="inlineStr"/>
       <c r="Q1209" t="n">
-        <v>0.9772727272727273</v>
+        <v>0.9848484848484849</v>
       </c>
     </row>
     <row r="1210">
@@ -54436,7 +54436,7 @@
       </c>
       <c r="P1211" t="inlineStr"/>
       <c r="Q1211" t="n">
-        <v>0.8585858585858586</v>
+        <v>0.8569023569023568</v>
       </c>
     </row>
     <row r="1212">
@@ -54542,7 +54542,7 @@
         <v>0.3712121212121212</v>
       </c>
       <c r="Q1213" t="n">
-        <v>0.9113300492610837</v>
+        <v>0.9014778325123153</v>
       </c>
     </row>
     <row r="1214">
@@ -54595,7 +54595,7 @@
         <v>0.3666666666666666</v>
       </c>
       <c r="Q1214" t="n">
-        <v>0.7752293577981652</v>
+        <v>0.7844036697247706</v>
       </c>
     </row>
     <row r="1215">
@@ -54648,7 +54648,7 @@
         <v>0.3697478991596639</v>
       </c>
       <c r="Q1215" t="n">
-        <v>0.8223350253807107</v>
+        <v>0.820642978003384</v>
       </c>
     </row>
     <row r="1216">
@@ -54701,7 +54701,7 @@
         <v>0.3620689655172414</v>
       </c>
       <c r="Q1216" t="n">
-        <v>0.7219251336898396</v>
+        <v>0.7237076648841355</v>
       </c>
     </row>
     <row r="1217">
@@ -54754,7 +54754,7 @@
         <v>0.4513274336283186</v>
       </c>
       <c r="Q1217" t="n">
-        <v>0.8132530120481928</v>
+        <v>0.8253012048192772</v>
       </c>
     </row>
     <row r="1218">
@@ -54807,7 +54807,7 @@
         <v>0.5098039215686274</v>
       </c>
       <c r="Q1218" t="n">
-        <v>0.9415584415584416</v>
+        <v>0.9220779220779221</v>
       </c>
     </row>
     <row r="1219">
@@ -54860,7 +54860,7 @@
         <v>0.6153846153846154</v>
       </c>
       <c r="Q1219" t="n">
-        <v>0.8954248366013072</v>
+        <v>0.917211328976035</v>
       </c>
     </row>
     <row r="1220">
@@ -54913,7 +54913,7 @@
         <v>0.5463917525773195</v>
       </c>
       <c r="Q1220" t="n">
-        <v>1.044025157232704</v>
+        <v>1.031446540880503</v>
       </c>
     </row>
     <row r="1221">
@@ -54966,7 +54966,7 @@
         <v>0.59</v>
       </c>
       <c r="Q1221" t="n">
-        <v>0.8913043478260869</v>
+        <v>0.8840579710144927</v>
       </c>
     </row>
     <row r="1222">
@@ -55019,7 +55019,7 @@
         <v>0.4766355140186916</v>
       </c>
       <c r="Q1222" t="n">
-        <v>0.7944444444444444</v>
+        <v>0.8092592592592592</v>
       </c>
     </row>
     <row r="1223">
@@ -55072,7 +55072,7 @@
         <v>0.4761904761904762</v>
       </c>
       <c r="Q1223" t="n">
-        <v>0.8720930232558139</v>
+        <v>0.881782945736434</v>
       </c>
     </row>
     <row r="1224">
@@ -55121,7 +55121,7 @@
       <c r="O1224" t="inlineStr"/>
       <c r="P1224" t="inlineStr"/>
       <c r="Q1224" t="n">
-        <v>0.9702380952380952</v>
+        <v>0.9464285714285714</v>
       </c>
     </row>
     <row r="1225">
@@ -55168,7 +55168,7 @@
       <c r="O1225" t="inlineStr"/>
       <c r="P1225" t="inlineStr"/>
       <c r="Q1225" t="n">
-        <v>0.8142076502732241</v>
+        <v>0.8342440801457195</v>
       </c>
     </row>
     <row r="1226">
@@ -55213,7 +55213,7 @@
       <c r="O1226" t="inlineStr"/>
       <c r="P1226" t="inlineStr"/>
       <c r="Q1226" t="n">
-        <v>0.9130434782608695</v>
+        <v>0.9089026915113873</v>
       </c>
     </row>
     <row r="1227">
@@ -55260,7 +55260,7 @@
       </c>
       <c r="P1227" t="inlineStr"/>
       <c r="Q1227" t="n">
-        <v>0.9135802469135802</v>
+        <v>0.9074074074074074</v>
       </c>
     </row>
     <row r="1228">
@@ -55307,7 +55307,7 @@
       <c r="O1228" t="inlineStr"/>
       <c r="P1228" t="inlineStr"/>
       <c r="Q1228" t="n">
-        <v>0.8352941176470589</v>
+        <v>0.8294117647058824</v>
       </c>
     </row>
     <row r="1229">
@@ -55354,7 +55354,7 @@
       <c r="O1229" t="inlineStr"/>
       <c r="P1229" t="inlineStr"/>
       <c r="Q1229" t="n">
-        <v>0.884393063583815</v>
+        <v>0.8940269749518304</v>
       </c>
     </row>
     <row r="1230">
@@ -55560,7 +55560,7 @@
       </c>
       <c r="P1235" t="inlineStr"/>
       <c r="Q1235" t="n">
-        <v>0.9705882352941176</v>
+        <v>0.9509803921568628</v>
       </c>
     </row>
     <row r="1236">
@@ -55613,7 +55613,7 @@
         <v>0.7931034482758621</v>
       </c>
       <c r="Q1236" t="n">
-        <v>0.9545454545454546</v>
+        <v>0.9797979797979799</v>
       </c>
     </row>
     <row r="1237">
@@ -55666,7 +55666,7 @@
         <v>0.5714285714285714</v>
       </c>
       <c r="Q1237" t="n">
-        <v>1.013888888888889</v>
+        <v>0.9861111111111112</v>
       </c>
     </row>
     <row r="1238">
@@ -55719,7 +55719,7 @@
         <v>0.5185185185185185</v>
       </c>
       <c r="Q1238" t="n">
-        <v>0.9036144578313253</v>
+        <v>0.9116465863453815</v>
       </c>
     </row>
     <row r="1239">
@@ -55772,7 +55772,7 @@
         <v>0.5178571428571429</v>
       </c>
       <c r="Q1239" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.8901960784313726</v>
       </c>
     </row>
     <row r="1240">
@@ -55825,7 +55825,7 @@
         <v>0.5882352941176471</v>
       </c>
       <c r="Q1240" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9254901960784314</v>
       </c>
     </row>
     <row r="1241">
@@ -55878,7 +55878,7 @@
         <v>0.6590909090909091</v>
       </c>
       <c r="Q1241" t="n">
-        <v>0.8850574712643678</v>
+        <v>0.9042145593869733</v>
       </c>
     </row>
     <row r="1242">
@@ -55931,7 +55931,7 @@
         <v>0.7674418604651163</v>
       </c>
       <c r="Q1242" t="n">
-        <v>0.875</v>
+        <v>0.8541666666666666</v>
       </c>
     </row>
     <row r="1243">
@@ -55984,7 +55984,7 @@
         <v>0.7209302325581395</v>
       </c>
       <c r="Q1243" t="n">
-        <v>0.881578947368421</v>
+        <v>0.9035087719298246</v>
       </c>
     </row>
     <row r="1244">
@@ -56090,7 +56090,7 @@
         <v>0.5932203389830508</v>
       </c>
       <c r="Q1245" t="n">
-        <v>0.9347826086956522</v>
+        <v>0.9202898550724639</v>
       </c>
     </row>
     <row r="1246">
@@ -56143,7 +56143,7 @@
         <v>0.5</v>
       </c>
       <c r="Q1246" t="n">
-        <v>0.8222222222222222</v>
+        <v>0.8407407407407408</v>
       </c>
     </row>
     <row r="1247">
@@ -56196,7 +56196,7 @@
         <v>0.6557377049180327</v>
       </c>
       <c r="Q1247" t="n">
-        <v>0.9247311827956989</v>
+        <v>0.9175627240143369</v>
       </c>
     </row>
     <row r="1248">
@@ -56249,7 +56249,7 @@
         <v>0.5492957746478874</v>
       </c>
       <c r="Q1248" t="n">
-        <v>0.9148936170212766</v>
+        <v>0.9184397163120567</v>
       </c>
     </row>
     <row r="1249">
@@ -56302,7 +56302,7 @@
         <v>0.75</v>
       </c>
       <c r="Q1249" t="n">
-        <v>0.900990099009901</v>
+        <v>0.8976897689768978</v>
       </c>
     </row>
     <row r="1250">
@@ -56408,7 +56408,7 @@
         <v>0.78125</v>
       </c>
       <c r="Q1251" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9242424242424243</v>
       </c>
     </row>
     <row r="1252">
@@ -56457,7 +56457,7 @@
       <c r="O1252" t="inlineStr"/>
       <c r="P1252" t="inlineStr"/>
       <c r="Q1252" t="n">
-        <v>0.981651376146789</v>
+        <v>0.963302752293578</v>
       </c>
     </row>
     <row r="1253">
@@ -56504,7 +56504,7 @@
       <c r="O1253" t="inlineStr"/>
       <c r="P1253" t="inlineStr"/>
       <c r="Q1253" t="n">
-        <v>0.9375</v>
+        <v>0.9583333333333334</v>
       </c>
     </row>
     <row r="1254">
@@ -56549,7 +56549,7 @@
       <c r="O1254" t="inlineStr"/>
       <c r="P1254" t="inlineStr"/>
       <c r="Q1254" t="n">
-        <v>0.9834710743801653</v>
+        <v>0.9779614325068872</v>
       </c>
     </row>
     <row r="1255">
@@ -56594,7 +56594,7 @@
       <c r="O1255" t="inlineStr"/>
       <c r="P1255" t="inlineStr"/>
       <c r="Q1255" t="n">
-        <v>0.9112903225806451</v>
+        <v>0.913978494623656</v>
       </c>
     </row>
     <row r="1256">
@@ -56639,7 +56639,7 @@
       <c r="O1256" t="inlineStr"/>
       <c r="P1256" t="inlineStr"/>
       <c r="Q1256" t="n">
-        <v>1.034188034188034</v>
+        <v>1.031339031339031</v>
       </c>
     </row>
     <row r="1257">
@@ -56684,7 +56684,7 @@
       <c r="O1257" t="inlineStr"/>
       <c r="P1257" t="inlineStr"/>
       <c r="Q1257" t="n">
-        <v>0.904</v>
+        <v>0.9226666666666667</v>
       </c>
     </row>
     <row r="1258">
@@ -57112,7 +57112,7 @@
       </c>
       <c r="P1271" t="inlineStr"/>
       <c r="Q1271" t="n">
-        <v>0.9578947368421052</v>
+        <v>0.9508771929824561</v>
       </c>
     </row>
     <row r="1272">
@@ -57165,7 +57165,7 @@
         <v>0.703125</v>
       </c>
       <c r="Q1272" t="n">
-        <v>0.9901960784313726</v>
+        <v>1.003267973856209</v>
       </c>
     </row>
     <row r="1273">
@@ -57218,7 +57218,7 @@
         <v>0.7962962962962963</v>
       </c>
       <c r="Q1273" t="n">
-        <v>0.8932038834951457</v>
+        <v>0.9158576051779935</v>
       </c>
     </row>
     <row r="1274">
@@ -57271,7 +57271,7 @@
         <v>0.8823529411764706</v>
       </c>
       <c r="Q1274" t="n">
-        <v>1.08</v>
+        <v>1.033333333333333</v>
       </c>
     </row>
     <row r="1275">
@@ -57324,7 +57324,7 @@
         <v>0.8545454545454545</v>
       </c>
       <c r="Q1275" t="n">
-        <v>0.5887850467289719</v>
+        <v>0.6230529595015577</v>
       </c>
     </row>
     <row r="1276">
@@ -57373,7 +57373,7 @@
       <c r="O1276" t="inlineStr"/>
       <c r="P1276" t="inlineStr"/>
       <c r="Q1276" t="n">
-        <v>1.569444444444444</v>
+        <v>1.564814814814815</v>
       </c>
     </row>
     <row r="1277">
@@ -57420,7 +57420,7 @@
       <c r="O1277" t="inlineStr"/>
       <c r="P1277" t="inlineStr"/>
       <c r="Q1277" t="n">
-        <v>0.8</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="1278">
@@ -57465,7 +57465,7 @@
       <c r="O1278" t="inlineStr"/>
       <c r="P1278" t="inlineStr"/>
       <c r="Q1278" t="n">
-        <v>0.9565217391304348</v>
+        <v>0.9652173913043478</v>
       </c>
     </row>
     <row r="1279">
@@ -57510,7 +57510,7 @@
       <c r="O1279" t="inlineStr"/>
       <c r="P1279" t="inlineStr"/>
       <c r="Q1279" t="n">
-        <v>1.241379310344828</v>
+        <v>1.235632183908046</v>
       </c>
     </row>
     <row r="1280">
@@ -57555,7 +57555,7 @@
       <c r="O1280" t="inlineStr"/>
       <c r="P1280" t="inlineStr"/>
       <c r="Q1280" t="n">
-        <v>0.7643312101910829</v>
+        <v>0.7664543524416136</v>
       </c>
     </row>
     <row r="1281">
@@ -57600,7 +57600,7 @@
       <c r="O1281" t="inlineStr"/>
       <c r="P1281" t="inlineStr"/>
       <c r="Q1281" t="n">
-        <v>0.8840579710144928</v>
+        <v>0.8913043478260869</v>
       </c>
     </row>
     <row r="1282">
@@ -57688,7 +57688,7 @@
       </c>
       <c r="P1283" t="inlineStr"/>
       <c r="Q1283" t="n">
-        <v>0.6976744186046512</v>
+        <v>0.7054263565891473</v>
       </c>
     </row>
     <row r="1284">
@@ -57737,7 +57737,7 @@
       <c r="O1284" t="inlineStr"/>
       <c r="P1284" t="inlineStr"/>
       <c r="Q1284" t="n">
-        <v>1</v>
+        <v>1.010416666666667</v>
       </c>
     </row>
     <row r="1285">
@@ -57784,7 +57784,7 @@
       <c r="O1285" t="inlineStr"/>
       <c r="P1285" t="inlineStr"/>
       <c r="Q1285" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.784313725490196</v>
       </c>
     </row>
     <row r="1286">
@@ -57880,7 +57880,7 @@
       </c>
       <c r="P1287" t="inlineStr"/>
       <c r="Q1287" t="n">
-        <v>1.038461538461539</v>
+        <v>1.025641025641026</v>
       </c>
     </row>
     <row r="1288">
@@ -57933,7 +57933,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="Q1288" t="n">
-        <v>0.8387096774193549</v>
+        <v>0.8602150537634409</v>
       </c>
     </row>
     <row r="1289">
@@ -57986,7 +57986,7 @@
         <v>0.9166666666666666</v>
       </c>
       <c r="Q1289" t="n">
-        <v>1</v>
+        <v>1.011494252873563</v>
       </c>
     </row>
     <row r="1290">
@@ -58148,7 +58148,7 @@
       </c>
       <c r="P1293" t="inlineStr"/>
       <c r="Q1293" t="n">
-        <v>1</v>
+        <v>1.041666666666667</v>
       </c>
     </row>
     <row r="1294">
@@ -58201,7 +58201,7 @@
         <v>1</v>
       </c>
       <c r="Q1294" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="1295">
@@ -58254,7 +58254,7 @@
         <v>1</v>
       </c>
       <c r="Q1295" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.4047619047619047</v>
       </c>
     </row>
     <row r="1296">
@@ -58307,7 +58307,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="Q1296" t="n">
-        <v>1.666666666666667</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1297">
@@ -58360,7 +58360,7 @@
         <v>0.3125</v>
       </c>
       <c r="Q1297" t="n">
-        <v>1.3</v>
+        <v>1.266666666666667</v>
       </c>
     </row>
     <row r="1298">
@@ -58515,7 +58515,7 @@
       <c r="O1300" t="inlineStr"/>
       <c r="P1300" t="inlineStr"/>
       <c r="Q1300" t="n">
-        <v>1.111111111111111</v>
+        <v>1.185185185185185</v>
       </c>
     </row>
     <row r="1301">
@@ -58562,7 +58562,7 @@
       <c r="O1301" t="inlineStr"/>
       <c r="P1301" t="inlineStr"/>
       <c r="Q1301" t="n">
-        <v>1.333333333333333</v>
+        <v>1.277777777777778</v>
       </c>
     </row>
     <row r="1302">
@@ -58607,7 +58607,7 @@
       <c r="O1302" t="inlineStr"/>
       <c r="P1302" t="inlineStr"/>
       <c r="Q1302" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9298245614035089</v>
       </c>
     </row>
     <row r="1303">
@@ -58652,7 +58652,7 @@
       <c r="O1303" t="inlineStr"/>
       <c r="P1303" t="inlineStr"/>
       <c r="Q1303" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.6231884057971014</v>
       </c>
     </row>
     <row r="1304">
@@ -58742,7 +58742,7 @@
       <c r="O1305" t="inlineStr"/>
       <c r="P1305" t="inlineStr"/>
       <c r="Q1305" t="n">
-        <v>1.071428571428571</v>
+        <v>1.238095238095238</v>
       </c>
     </row>
     <row r="1306">
@@ -58828,7 +58828,7 @@
       </c>
       <c r="P1307" t="inlineStr"/>
       <c r="Q1307" t="n">
-        <v>0.9310344827586207</v>
+        <v>0.9425287356321839</v>
       </c>
     </row>
     <row r="1308">
@@ -58881,7 +58881,7 @@
         <v>1.166666666666667</v>
       </c>
       <c r="Q1308" t="n">
-        <v>1.041666666666667</v>
+        <v>1.027777777777778</v>
       </c>
     </row>
     <row r="1309">
@@ -58934,7 +58934,7 @@
         <v>0.5</v>
       </c>
       <c r="Q1309" t="n">
-        <v>1.181818181818182</v>
+        <v>1.212121212121212</v>
       </c>
     </row>
     <row r="1310">
@@ -59171,7 +59171,7 @@
         <v>0.9411764705882353</v>
       </c>
       <c r="Q1314" t="n">
-        <v>1.051282051282051</v>
+        <v>1.034188034188034</v>
       </c>
     </row>
     <row r="1315">
@@ -59224,7 +59224,7 @@
         <v>0.9047619047619048</v>
       </c>
       <c r="Q1315" t="n">
-        <v>0.9302325581395349</v>
+        <v>0.937984496124031</v>
       </c>
     </row>
     <row r="1316">
@@ -59277,7 +59277,7 @@
         <v>0.7727272727272727</v>
       </c>
       <c r="Q1316" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="1317">
@@ -59383,7 +59383,7 @@
         <v>0.5769230769230769</v>
       </c>
       <c r="Q1318" t="n">
-        <v>0.3404255319148936</v>
+        <v>0.3262411347517731</v>
       </c>
     </row>
     <row r="1319">
@@ -59489,7 +59489,7 @@
         <v>0.6086956521739131</v>
       </c>
       <c r="Q1320" t="n">
-        <v>1.166666666666667</v>
+        <v>1.194444444444445</v>
       </c>
     </row>
     <row r="1321">
@@ -59542,7 +59542,7 @@
         <v>0.5769230769230769</v>
       </c>
       <c r="Q1321" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.6274509803921567</v>
       </c>
     </row>
     <row r="1322">
@@ -59595,7 +59595,7 @@
         <v>0.6206896551724138</v>
       </c>
       <c r="Q1322" t="n">
-        <v>1.071428571428571</v>
+        <v>0.9523809523809523</v>
       </c>
     </row>
     <row r="1323">
@@ -59648,7 +59648,7 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="Q1323" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.648148148148148</v>
       </c>
     </row>
     <row r="1324">
@@ -59697,7 +59697,7 @@
       <c r="O1324" t="inlineStr"/>
       <c r="P1324" t="inlineStr"/>
       <c r="Q1324" t="n">
-        <v>1.25</v>
+        <v>1.166666666666667</v>
       </c>
     </row>
     <row r="1325">
@@ -59744,7 +59744,7 @@
       <c r="O1325" t="inlineStr"/>
       <c r="P1325" t="inlineStr"/>
       <c r="Q1325" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.9122807017543859</v>
       </c>
     </row>
     <row r="1326">
@@ -59879,7 +59879,7 @@
       <c r="O1328" t="inlineStr"/>
       <c r="P1328" t="inlineStr"/>
       <c r="Q1328" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.9333333333333333</v>
       </c>
     </row>
     <row r="1329">
@@ -59924,7 +59924,7 @@
       <c r="O1329" t="inlineStr"/>
       <c r="P1329" t="inlineStr"/>
       <c r="Q1329" t="n">
-        <v>1.076923076923077</v>
+        <v>1.051282051282051</v>
       </c>
     </row>
     <row r="1330">
@@ -60118,7 +60118,7 @@
         <v>0.25</v>
       </c>
       <c r="Q1333" t="n">
-        <v>0.7837837837837838</v>
+        <v>0.8108108108108109</v>
       </c>
     </row>
     <row r="1334">
@@ -60171,7 +60171,7 @@
         <v>0.4</v>
       </c>
       <c r="Q1334" t="n">
-        <v>0.8409090909090909</v>
+        <v>0.8030303030303031</v>
       </c>
     </row>
     <row r="1335">
@@ -60224,7 +60224,7 @@
         <v>0.5526315789473685</v>
       </c>
       <c r="Q1335" t="n">
-        <v>0.9743589743589743</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1336">
@@ -60277,7 +60277,7 @@
         <v>0.8125</v>
       </c>
       <c r="Q1336" t="n">
-        <v>0.9347826086956522</v>
+        <v>0.8985507246376813</v>
       </c>
     </row>
     <row r="1337">
@@ -60330,7 +60330,7 @@
         <v>0.7</v>
       </c>
       <c r="Q1337" t="n">
-        <v>0.9019607843137255</v>
+        <v>0.9281045751633986</v>
       </c>
     </row>
     <row r="1338">
@@ -60383,7 +60383,7 @@
         <v>0.6428571428571429</v>
       </c>
       <c r="Q1338" t="n">
-        <v>0.9206349206349206</v>
+        <v>0.91005291005291</v>
       </c>
     </row>
     <row r="1339">
@@ -60436,7 +60436,7 @@
         <v>0.6744186046511628</v>
       </c>
       <c r="Q1339" t="n">
-        <v>0.8787878787878788</v>
+        <v>0.8939393939393939</v>
       </c>
     </row>
     <row r="1340">
@@ -60489,7 +60489,7 @@
         <v>0.7209302325581395</v>
       </c>
       <c r="Q1340" t="n">
-        <v>0.8428571428571429</v>
+        <v>0.8619047619047618</v>
       </c>
     </row>
     <row r="1341">
@@ -60542,7 +60542,7 @@
         <v>0.8947368421052632</v>
       </c>
       <c r="Q1341" t="n">
-        <v>1.028169014084507</v>
+        <v>1.018779342723005</v>
       </c>
     </row>
     <row r="1342">
@@ -60595,7 +60595,7 @@
         <v>0.7435897435897436</v>
       </c>
       <c r="Q1342" t="n">
-        <v>0.9154929577464789</v>
+        <v>0.9295774647887324</v>
       </c>
     </row>
     <row r="1343">
@@ -60648,7 +60648,7 @@
         <v>0.8611111111111112</v>
       </c>
       <c r="Q1343" t="n">
-        <v>0.9863013698630136</v>
+        <v>0.9908675799086757</v>
       </c>
     </row>
     <row r="1344">
@@ -60701,7 +60701,7 @@
         <v>0.8260869565217391</v>
       </c>
       <c r="Q1344" t="n">
-        <v>1.013157894736842</v>
+        <v>0.9912280701754386</v>
       </c>
     </row>
     <row r="1345">
@@ -60754,7 +60754,7 @@
         <v>0.8823529411764706</v>
       </c>
       <c r="Q1345" t="n">
-        <v>0.8915662650602409</v>
+        <v>0.9156626506024096</v>
       </c>
     </row>
     <row r="1346">
@@ -60807,7 +60807,7 @@
         <v>0.8958333333333334</v>
       </c>
       <c r="Q1346" t="n">
-        <v>0.9886363636363636</v>
+        <v>0.9924242424242423</v>
       </c>
     </row>
     <row r="1347">
@@ -60860,7 +60860,7 @@
         <v>0.7674418604651163</v>
       </c>
       <c r="Q1347" t="n">
-        <v>0.9767441860465116</v>
+        <v>0.9612403100775194</v>
       </c>
     </row>
     <row r="1348">
@@ -60909,7 +60909,7 @@
       <c r="O1348" t="inlineStr"/>
       <c r="P1348" t="inlineStr"/>
       <c r="Q1348" t="n">
-        <v>0.9156626506024096</v>
+        <v>0.9076305220883534</v>
       </c>
     </row>
     <row r="1349">
@@ -60956,7 +60956,7 @@
       <c r="O1349" t="inlineStr"/>
       <c r="P1349" t="inlineStr"/>
       <c r="Q1349" t="n">
-        <v>0.8</v>
+        <v>0.8313725490196079</v>
       </c>
     </row>
     <row r="1350">
@@ -61001,7 +61001,7 @@
       <c r="O1350" t="inlineStr"/>
       <c r="P1350" t="inlineStr"/>
       <c r="Q1350" t="n">
-        <v>0.9726027397260274</v>
+        <v>0.9771689497716894</v>
       </c>
     </row>
     <row r="1351">
@@ -61046,7 +61046,7 @@
       <c r="O1351" t="inlineStr"/>
       <c r="P1351" t="inlineStr"/>
       <c r="Q1351" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9351851851851851</v>
       </c>
     </row>
     <row r="1352">
@@ -61091,7 +61091,7 @@
       <c r="O1352" t="inlineStr"/>
       <c r="P1352" t="inlineStr"/>
       <c r="Q1352" t="n">
-        <v>1.082191780821918</v>
+        <v>1.077625570776256</v>
       </c>
     </row>
     <row r="1353">
@@ -61136,7 +61136,7 @@
       <c r="O1353" t="inlineStr"/>
       <c r="P1353" t="inlineStr"/>
       <c r="Q1353" t="n">
-        <v>1.043956043956044</v>
+        <v>1.018315018315018</v>
       </c>
     </row>
     <row r="1354">
@@ -61224,7 +61224,7 @@
       </c>
       <c r="P1355" t="inlineStr"/>
       <c r="Q1355" t="n">
-        <v>0.9830508474576272</v>
+        <v>1.022598870056497</v>
       </c>
     </row>
     <row r="1356">
@@ -61273,7 +61273,7 @@
       <c r="O1356" t="inlineStr"/>
       <c r="P1356" t="inlineStr"/>
       <c r="Q1356" t="n">
-        <v>0.9117647058823529</v>
+        <v>0.8823529411764706</v>
       </c>
     </row>
     <row r="1357">
@@ -61320,7 +61320,7 @@
       <c r="O1357" t="inlineStr"/>
       <c r="P1357" t="inlineStr"/>
       <c r="Q1357" t="n">
-        <v>0.9743589743589743</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1358">
@@ -61367,7 +61367,7 @@
       </c>
       <c r="P1358" t="inlineStr"/>
       <c r="Q1358" t="n">
-        <v>0.9418604651162791</v>
+        <v>0.9069767441860465</v>
       </c>
     </row>
     <row r="1359">
@@ -61416,7 +61416,7 @@
       </c>
       <c r="P1359" t="inlineStr"/>
       <c r="Q1359" t="n">
-        <v>0.8863636363636364</v>
+        <v>0.9053030303030304</v>
       </c>
     </row>
     <row r="1360">
@@ -61522,7 +61522,7 @@
         <v>0.6727272727272727</v>
       </c>
       <c r="Q1361" t="n">
-        <v>0.9176470588235294</v>
+        <v>0.9333333333333332</v>
       </c>
     </row>
     <row r="1362">
@@ -61684,7 +61684,7 @@
       </c>
       <c r="P1365" t="inlineStr"/>
       <c r="Q1365" t="n">
-        <v>0.8297872340425532</v>
+        <v>0.8687943262411348</v>
       </c>
     </row>
     <row r="1366">
@@ -61737,7 +61737,7 @@
         <v>0.8222222222222222</v>
       </c>
       <c r="Q1366" t="n">
-        <v>1.048192771084337</v>
+        <v>1.016064257028112</v>
       </c>
     </row>
     <row r="1367">
@@ -61790,7 +61790,7 @@
         <v>0.6326530612244898</v>
       </c>
       <c r="Q1367" t="n">
-        <v>1.010989010989011</v>
+        <v>1.007326007326007</v>
       </c>
     </row>
     <row r="1368">
@@ -61843,7 +61843,7 @@
         <v>0.5576923076923077</v>
       </c>
       <c r="Q1368" t="n">
-        <v>0.9278350515463918</v>
+        <v>0.9381443298969072</v>
       </c>
     </row>
     <row r="1369">
@@ -61896,7 +61896,7 @@
         <v>0.5769230769230769</v>
       </c>
       <c r="Q1369" t="n">
-        <v>0.9375</v>
+        <v>0.9409722222222222</v>
       </c>
     </row>
     <row r="1370">
@@ -61949,7 +61949,7 @@
         <v>0.7678571428571429</v>
       </c>
       <c r="Q1370" t="n">
-        <v>0.95</v>
+        <v>0.9533333333333333</v>
       </c>
     </row>
     <row r="1371">
@@ -62002,7 +62002,7 @@
         <v>0.8</v>
       </c>
       <c r="Q1371" t="n">
-        <v>0.9702970297029703</v>
+        <v>0.9603960396039604</v>
       </c>
     </row>
     <row r="1372">
@@ -62051,7 +62051,7 @@
       <c r="O1372" t="inlineStr"/>
       <c r="P1372" t="inlineStr"/>
       <c r="Q1372" t="n">
-        <v>0.970873786407767</v>
+        <v>0.9741100323624595</v>
       </c>
     </row>
     <row r="1373">
@@ -62098,7 +62098,7 @@
       <c r="O1373" t="inlineStr"/>
       <c r="P1373" t="inlineStr"/>
       <c r="Q1373" t="n">
-        <v>0.9504950495049505</v>
+        <v>0.9372937293729373</v>
       </c>
     </row>
     <row r="1374">
@@ -62143,7 +62143,7 @@
       <c r="O1374" t="inlineStr"/>
       <c r="P1374" t="inlineStr"/>
       <c r="Q1374" t="n">
-        <v>0.865979381443299</v>
+        <v>0.8694158075601374</v>
       </c>
     </row>
     <row r="1375">
@@ -62188,7 +62188,7 @@
       <c r="O1375" t="inlineStr"/>
       <c r="P1375" t="inlineStr"/>
       <c r="Q1375" t="n">
-        <v>0.9375</v>
+        <v>0.9513888888888888</v>
       </c>
     </row>
     <row r="1376">
@@ -62233,7 +62233,7 @@
       <c r="O1376" t="inlineStr"/>
       <c r="P1376" t="inlineStr"/>
       <c r="Q1376" t="n">
-        <v>0.9541284403669725</v>
+        <v>0.9785932721712537</v>
       </c>
     </row>
     <row r="1377">
@@ -62278,7 +62278,7 @@
       <c r="O1377" t="inlineStr"/>
       <c r="P1377" t="inlineStr"/>
       <c r="Q1377" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9287749287749287</v>
       </c>
     </row>
     <row r="1378">
@@ -62415,7 +62415,7 @@
       <c r="O1380" t="inlineStr"/>
       <c r="P1380" t="inlineStr"/>
       <c r="Q1380" t="n">
-        <v>0.9795918367346939</v>
+        <v>0.9727891156462585</v>
       </c>
     </row>
     <row r="1381">
@@ -62462,7 +62462,7 @@
       <c r="O1381" t="inlineStr"/>
       <c r="P1381" t="inlineStr"/>
       <c r="Q1381" t="n">
-        <v>0.9591836734693877</v>
+        <v>0.9455782312925171</v>
       </c>
     </row>
     <row r="1382">
@@ -62509,7 +62509,7 @@
       </c>
       <c r="P1382" t="inlineStr"/>
       <c r="Q1382" t="n">
-        <v>1.019607843137255</v>
+        <v>1.03921568627451</v>
       </c>
     </row>
     <row r="1383">
@@ -62558,7 +62558,7 @@
       </c>
       <c r="P1383" t="inlineStr"/>
       <c r="Q1383" t="n">
-        <v>0.9107142857142857</v>
+        <v>0.8988095238095238</v>
       </c>
     </row>
     <row r="1384">
@@ -62611,7 +62611,7 @@
         <v>0.8</v>
       </c>
       <c r="Q1384" t="n">
-        <v>0.9272727272727272</v>
+        <v>0.9515151515151515</v>
       </c>
     </row>
     <row r="1385">
@@ -62826,7 +62826,7 @@
       </c>
       <c r="P1389" t="inlineStr"/>
       <c r="Q1389" t="n">
-        <v>0.9661016949152542</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1390">
@@ -62879,7 +62879,7 @@
         <v>1.108108108108108</v>
       </c>
       <c r="Q1390" t="n">
-        <v>1.061538461538462</v>
+        <v>1.030769230769231</v>
       </c>
     </row>
     <row r="1391">
@@ -62932,7 +62932,7 @@
         <v>1.243243243243243</v>
       </c>
       <c r="Q1391" t="n">
-        <v>0.9305555555555556</v>
+        <v>0.925925925925926</v>
       </c>
     </row>
     <row r="1392">
@@ -63038,7 +63038,7 @@
         <v>0.631578947368421</v>
       </c>
       <c r="Q1393" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.897119341563786</v>
       </c>
     </row>
     <row r="1394">
@@ -63091,7 +63091,7 @@
         <v>0.5833333333333334</v>
       </c>
       <c r="Q1394" t="n">
-        <v>0.9135802469135802</v>
+        <v>0.9218106995884774</v>
       </c>
     </row>
     <row r="1395">
@@ -63144,7 +63144,7 @@
         <v>0.8888888888888888</v>
       </c>
       <c r="Q1395" t="n">
-        <v>0.863013698630137</v>
+        <v>0.8949771689497716</v>
       </c>
     </row>
     <row r="1396">
@@ -63240,7 +63240,7 @@
       <c r="O1397" t="inlineStr"/>
       <c r="P1397" t="inlineStr"/>
       <c r="Q1397" t="n">
-        <v>1.117647058823529</v>
+        <v>1.104575163398693</v>
       </c>
     </row>
     <row r="1398">
@@ -63285,7 +63285,7 @@
       <c r="O1398" t="inlineStr"/>
       <c r="P1398" t="inlineStr"/>
       <c r="Q1398" t="n">
-        <v>1.102040816326531</v>
+        <v>1.034013605442177</v>
       </c>
     </row>
     <row r="1399">
@@ -63330,7 +63330,7 @@
       <c r="O1399" t="inlineStr"/>
       <c r="P1399" t="inlineStr"/>
       <c r="Q1399" t="n">
-        <v>0.9387755102040817</v>
+        <v>0.9523809523809523</v>
       </c>
     </row>
     <row r="1400">
@@ -63375,7 +63375,7 @@
       <c r="O1400" t="inlineStr"/>
       <c r="P1400" t="inlineStr"/>
       <c r="Q1400" t="n">
-        <v>0.9230769230769231</v>
+        <v>0.9551282051282051</v>
       </c>
     </row>
     <row r="1401">
@@ -63420,7 +63420,7 @@
       <c r="O1401" t="inlineStr"/>
       <c r="P1401" t="inlineStr"/>
       <c r="Q1401" t="n">
-        <v>0.9814814814814815</v>
+        <v>0.95679012345679</v>
       </c>
     </row>
     <row r="1402">
@@ -63508,7 +63508,7 @@
       </c>
       <c r="P1403" t="inlineStr"/>
       <c r="Q1403" t="n">
-        <v>0.9457364341085271</v>
+        <v>0.9509043927648578</v>
       </c>
     </row>
     <row r="1404">
@@ -63557,7 +63557,7 @@
       <c r="O1404" t="inlineStr"/>
       <c r="P1404" t="inlineStr"/>
       <c r="Q1404" t="n">
-        <v>0.8985507246376812</v>
+        <v>0.8937198067632851</v>
       </c>
     </row>
     <row r="1405">
@@ -63651,7 +63651,7 @@
       </c>
       <c r="P1406" t="inlineStr"/>
       <c r="Q1406" t="n">
-        <v>0.8731343283582089</v>
+        <v>0.8706467661691542</v>
       </c>
     </row>
     <row r="1407">
@@ -63700,7 +63700,7 @@
       </c>
       <c r="P1407" t="inlineStr"/>
       <c r="Q1407" t="n">
-        <v>0.8805970149253731</v>
+        <v>0.8830845771144279</v>
       </c>
     </row>
     <row r="1408">
@@ -63753,7 +63753,7 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="Q1408" t="n">
-        <v>0.8432835820895522</v>
+        <v>0.8756218905472638</v>
       </c>
     </row>
     <row r="1409">
@@ -63806,7 +63806,7 @@
         <v>0.7123287671232876</v>
       </c>
       <c r="Q1409" t="n">
-        <v>1.067226890756303</v>
+        <v>1.025210084033613</v>
       </c>
     </row>
     <row r="1410">
@@ -63968,7 +63968,7 @@
       </c>
       <c r="P1413" t="inlineStr"/>
       <c r="Q1413" t="n">
-        <v>0.9186991869918699</v>
+        <v>0.9512195121951219</v>
       </c>
     </row>
     <row r="1414">
@@ -64021,7 +64021,7 @@
         <v>0.8356164383561644</v>
       </c>
       <c r="Q1414" t="n">
-        <v>1.0703125</v>
+        <v>1.057291666666667</v>
       </c>
     </row>
     <row r="1415">
@@ -64074,7 +64074,7 @@
         <v>0.8026315789473685</v>
       </c>
       <c r="Q1415" t="n">
-        <v>0.9926470588235294</v>
+        <v>0.9681372549019607</v>
       </c>
     </row>
     <row r="1416">
@@ -64127,7 +64127,7 @@
         <v>0.8028169014084507</v>
       </c>
       <c r="Q1416" t="n">
-        <v>0.9084507042253521</v>
+        <v>0.9295774647887324</v>
       </c>
     </row>
     <row r="1417">
@@ -64180,7 +64180,7 @@
         <v>0.7901234567901234</v>
       </c>
       <c r="Q1417" t="n">
-        <v>0.9154929577464789</v>
+        <v>0.8732394366197183</v>
       </c>
     </row>
     <row r="1418">
@@ -64233,7 +64233,7 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="Q1418" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8712643678160921</v>
       </c>
     </row>
     <row r="1419">
@@ -64286,7 +64286,7 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="Q1419" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8712643678160921</v>
       </c>
     </row>
     <row r="1420">
@@ -64339,7 +64339,7 @@
         <v>0.75</v>
       </c>
       <c r="Q1420" t="n">
-        <v>0.8936170212765957</v>
+        <v>0.8959810874704492</v>
       </c>
     </row>
     <row r="1421">
@@ -64392,7 +64392,7 @@
         <v>0.75</v>
       </c>
       <c r="Q1421" t="n">
-        <v>0.8936170212765957</v>
+        <v>0.8959810874704492</v>
       </c>
     </row>
     <row r="1422">
@@ -64441,7 +64441,7 @@
       <c r="O1422" t="inlineStr"/>
       <c r="P1422" t="inlineStr"/>
       <c r="Q1422" t="n">
-        <v>0.9929078014184397</v>
+        <v>0.9976359338061465</v>
       </c>
     </row>
     <row r="1423">
@@ -64490,7 +64490,7 @@
       <c r="O1423" t="inlineStr"/>
       <c r="P1423" t="inlineStr"/>
       <c r="Q1423" t="n">
-        <v>0.9929078014184397</v>
+        <v>0.9976359338061465</v>
       </c>
     </row>
     <row r="1424">
@@ -64537,7 +64537,7 @@
       <c r="O1424" t="inlineStr"/>
       <c r="P1424" t="inlineStr"/>
       <c r="Q1424" t="n">
-        <v>0.9415584415584416</v>
+        <v>0.935064935064935</v>
       </c>
     </row>
     <row r="1425">
@@ -64582,7 +64582,7 @@
       <c r="O1425" t="inlineStr"/>
       <c r="P1425" t="inlineStr"/>
       <c r="Q1425" t="n">
-        <v>0.9602649006622517</v>
+        <v>0.9536423841059603</v>
       </c>
     </row>
     <row r="1426">
@@ -64627,7 +64627,7 @@
       <c r="O1426" t="inlineStr"/>
       <c r="P1426" t="inlineStr"/>
       <c r="Q1426" t="n">
-        <v>0.9411764705882353</v>
+        <v>0.9694989106753813</v>
       </c>
     </row>
     <row r="1427">
@@ -64672,7 +64672,7 @@
       <c r="O1427" t="inlineStr"/>
       <c r="P1427" t="inlineStr"/>
       <c r="Q1427" t="n">
-        <v>1.09375</v>
+        <v>1.06875</v>
       </c>
     </row>
     <row r="1428">
@@ -64717,7 +64717,7 @@
       <c r="O1428" t="inlineStr"/>
       <c r="P1428" t="inlineStr"/>
       <c r="Q1428" t="n">
-        <v>0.9782608695652174</v>
+        <v>0.9836956521739131</v>
       </c>
     </row>
     <row r="1429">
@@ -64805,7 +64805,7 @@
       </c>
       <c r="P1430" t="inlineStr"/>
       <c r="Q1430" t="n">
-        <v>1.062937062937063</v>
+        <v>1.044289044289044</v>
       </c>
     </row>
     <row r="1431">
@@ -64858,7 +64858,7 @@
         <v>0.8461538461538461</v>
       </c>
       <c r="Q1431" t="n">
-        <v>0.9785714285714285</v>
+        <v>0.9880952380952381</v>
       </c>
     </row>
     <row r="1432">
@@ -64911,7 +64911,7 @@
         <v>0.8405797101449275</v>
       </c>
       <c r="Q1432" t="n">
-        <v>0.9935064935064936</v>
+        <v>0.974025974025974</v>
       </c>
     </row>
     <row r="1433">
@@ -64964,7 +64964,7 @@
         <v>0.6385542168674698</v>
       </c>
       <c r="Q1433" t="n">
-        <v>0.89375</v>
+        <v>0.9104166666666667</v>
       </c>
     </row>
     <row r="1434">
@@ -65017,7 +65017,7 @@
         <v>0.8</v>
       </c>
       <c r="Q1434" t="n">
-        <v>0.9240506329113924</v>
+        <v>0.9282700421940928</v>
       </c>
     </row>
     <row r="1435">
@@ -65070,7 +65070,7 @@
         <v>0.9047619047619048</v>
       </c>
       <c r="Q1435" t="n">
-        <v>0.9490445859872612</v>
+        <v>0.959660297239915</v>
       </c>
     </row>
     <row r="1436">
@@ -65123,7 +65123,7 @@
         <v>1.026315789473684</v>
       </c>
       <c r="Q1436" t="n">
-        <v>1.050314465408805</v>
+        <v>1.044025157232704</v>
       </c>
     </row>
     <row r="1437">
@@ -65176,7 +65176,7 @@
         <v>1.115942028985507</v>
       </c>
       <c r="Q1437" t="n">
-        <v>0.9685534591194969</v>
+        <v>0.9622641509433962</v>
       </c>
     </row>
     <row r="1438">
@@ -65229,7 +65229,7 @@
         <v>1.296875</v>
       </c>
       <c r="Q1438" t="n">
-        <v>1.123376623376623</v>
+        <v>1.119047619047619</v>
       </c>
     </row>
     <row r="1439">
@@ -65335,7 +65335,7 @@
         <v>1.26984126984127</v>
       </c>
       <c r="Q1440" t="n">
-        <v>0.841025641025641</v>
+        <v>0.8632478632478633</v>
       </c>
     </row>
     <row r="1441">
@@ -65388,7 +65388,7 @@
         <v>1.103448275862069</v>
       </c>
       <c r="Q1441" t="n">
-        <v>1.134969325153374</v>
+        <v>1.132924335378323</v>
       </c>
     </row>
     <row r="1442">
@@ -65441,7 +65441,7 @@
         <v>1.175438596491228</v>
       </c>
       <c r="Q1442" t="n">
-        <v>1.062857142857143</v>
+        <v>1.043809523809524</v>
       </c>
     </row>
     <row r="1443">
@@ -65494,7 +65494,7 @@
         <v>1.207547169811321</v>
       </c>
       <c r="Q1443" t="n">
-        <v>0.9719101123595506</v>
+        <v>0.9906367041198503</v>
       </c>
     </row>
     <row r="1444">
@@ -65547,7 +65547,7 @@
         <v>1.358490566037736</v>
       </c>
       <c r="Q1444" t="n">
-        <v>0.9939759036144579</v>
+        <v>1.006024096385542</v>
       </c>
     </row>
     <row r="1445">
@@ -65600,7 +65600,7 @@
         <v>1.049180327868853</v>
       </c>
       <c r="Q1445" t="n">
-        <v>1.173076923076923</v>
+        <v>1.143162393162393</v>
       </c>
     </row>
     <row r="1446">
@@ -65653,7 +65653,7 @@
         <v>1.03030303030303</v>
       </c>
       <c r="Q1446" t="n">
-        <v>0.9887005649717514</v>
+        <v>0.9943502824858758</v>
       </c>
     </row>
     <row r="1447">
@@ -65702,7 +65702,7 @@
       <c r="O1447" t="inlineStr"/>
       <c r="P1447" t="inlineStr"/>
       <c r="Q1447" t="n">
-        <v>1.058479532163743</v>
+        <v>1.048732943469786</v>
       </c>
     </row>
     <row r="1448">
@@ -65749,7 +65749,7 @@
       <c r="O1448" t="inlineStr"/>
       <c r="P1448" t="inlineStr"/>
       <c r="Q1448" t="n">
-        <v>0.8757062146892656</v>
+        <v>0.8851224105461393</v>
       </c>
     </row>
     <row r="1449">
@@ -65794,7 +65794,7 @@
       <c r="O1449" t="inlineStr"/>
       <c r="P1449" t="inlineStr"/>
       <c r="Q1449" t="n">
-        <v>1</v>
+        <v>0.9937888198757764</v>
       </c>
     </row>
     <row r="1450">
@@ -65839,7 +65839,7 @@
       <c r="O1450" t="inlineStr"/>
       <c r="P1450" t="inlineStr"/>
       <c r="Q1450" t="n">
-        <v>1.105590062111801</v>
+        <v>1.118012422360248</v>
       </c>
     </row>
     <row r="1451">
@@ -65884,7 +65884,7 @@
       <c r="O1451" t="inlineStr"/>
       <c r="P1451" t="inlineStr"/>
       <c r="Q1451" t="n">
-        <v>1.005882352941176</v>
+        <v>0.9843137254901961</v>
       </c>
     </row>
     <row r="1452">
@@ -65929,7 +65929,7 @@
       <c r="O1452" t="inlineStr"/>
       <c r="P1452" t="inlineStr"/>
       <c r="Q1452" t="n">
-        <v>0.9135135135135135</v>
+        <v>0.9297297297297298</v>
       </c>
     </row>
     <row r="1453">
